--- a/corrections/corrections.xlsx
+++ b/corrections/corrections.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Desktop\wow_vo_webui\corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D43FA5F-F777-49F7-A63B-429F6E1D92E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8D6992-44B1-4E87-B5BF-E3E57FFAE444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="quest" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="129">
   <si>
     <t>source</t>
   </si>
@@ -850,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56545B79-22C0-4057-A076-1E697524330B}">
-  <dimension ref="A1:F1123"/>
+  <dimension ref="A1:F1121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3323,7 +3323,7 @@
     </row>
     <row r="308" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B308">
-        <v>6187</v>
+        <v>7496</v>
       </c>
       <c r="E308">
         <v>0</v>
@@ -3331,7 +3331,7 @@
     </row>
     <row r="309" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B309">
-        <v>7496</v>
+        <v>7782</v>
       </c>
       <c r="E309">
         <v>0</v>
@@ -3339,7 +3339,7 @@
     </row>
     <row r="310" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B310">
-        <v>7782</v>
+        <v>7495</v>
       </c>
       <c r="E310">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     </row>
     <row r="311" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B311">
-        <v>6186</v>
+        <v>7781</v>
       </c>
       <c r="E311">
         <v>0</v>
@@ -3355,23 +3355,23 @@
     </row>
     <row r="312" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B312">
-        <v>7495</v>
+        <v>10623</v>
       </c>
       <c r="E312">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B313">
-        <v>7781</v>
+        <v>10621</v>
       </c>
       <c r="E313">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B314">
-        <v>10623</v>
+        <v>10755</v>
       </c>
       <c r="E314">
         <v>1</v>
@@ -3379,7 +3379,7 @@
     </row>
     <row r="315" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B315">
-        <v>10621</v>
+        <v>10797</v>
       </c>
       <c r="E315">
         <v>1</v>
@@ -3387,7 +3387,7 @@
     </row>
     <row r="316" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B316">
-        <v>10755</v>
+        <v>10940</v>
       </c>
       <c r="E316">
         <v>1</v>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="317" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B317">
-        <v>10797</v>
+        <v>10941</v>
       </c>
       <c r="E317">
         <v>1</v>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="318" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B318">
-        <v>10940</v>
+        <v>11002</v>
       </c>
       <c r="E318">
         <v>1</v>
@@ -3411,7 +3411,7 @@
     </row>
     <row r="319" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B319">
-        <v>10941</v>
+        <v>11003</v>
       </c>
       <c r="E319">
         <v>1</v>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="320" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B320">
-        <v>11002</v>
+        <v>11041</v>
       </c>
       <c r="E320">
         <v>1</v>
@@ -3427,7 +3427,7 @@
     </row>
     <row r="321" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B321">
-        <v>11003</v>
+        <v>11081</v>
       </c>
       <c r="E321">
         <v>1</v>
@@ -3435,7 +3435,7 @@
     </row>
     <row r="322" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B322">
-        <v>11041</v>
+        <v>11178</v>
       </c>
       <c r="E322">
         <v>1</v>
@@ -3443,7 +3443,7 @@
     </row>
     <row r="323" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B323">
-        <v>11081</v>
+        <v>11185</v>
       </c>
       <c r="E323">
         <v>1</v>
@@ -3451,7 +3451,7 @@
     </row>
     <row r="324" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B324">
-        <v>11178</v>
+        <v>11400</v>
       </c>
       <c r="E324">
         <v>1</v>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="325" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B325">
-        <v>11185</v>
+        <v>11419</v>
       </c>
       <c r="E325">
         <v>1</v>
@@ -3467,7 +3467,7 @@
     </row>
     <row r="326" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B326">
-        <v>11400</v>
+        <v>11531</v>
       </c>
       <c r="E326">
         <v>1</v>
@@ -3475,23 +3475,23 @@
     </row>
     <row r="327" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B327">
-        <v>11419</v>
+        <v>1454</v>
       </c>
       <c r="E327">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B328">
-        <v>11531</v>
+        <v>1455</v>
       </c>
       <c r="E328">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B329">
-        <v>1454</v>
+        <v>3122</v>
       </c>
       <c r="E329">
         <v>0</v>
@@ -3499,7 +3499,7 @@
     </row>
     <row r="330" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B330">
-        <v>1455</v>
+        <v>3121</v>
       </c>
       <c r="E330">
         <v>0</v>
@@ -3507,7 +3507,7 @@
     </row>
     <row r="331" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B331">
-        <v>3122</v>
+        <v>1465</v>
       </c>
       <c r="E331">
         <v>0</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B332">
-        <v>3121</v>
+        <v>24914</v>
       </c>
       <c r="E332">
         <v>0</v>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B333">
-        <v>1465</v>
+        <v>254</v>
       </c>
       <c r="E333">
         <v>0</v>
@@ -3531,7 +3531,7 @@
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B334">
-        <v>24914</v>
+        <v>1526</v>
       </c>
       <c r="E334">
         <v>0</v>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B335">
-        <v>254</v>
+        <v>1527</v>
       </c>
       <c r="E335">
         <v>0</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B336">
-        <v>1526</v>
+        <v>1268</v>
       </c>
       <c r="E336">
         <v>0</v>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B337">
-        <v>1527</v>
+        <v>1284</v>
       </c>
       <c r="E337">
         <v>0</v>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B338">
-        <v>1268</v>
+        <v>11732</v>
       </c>
       <c r="E338">
         <v>0</v>
@@ -3571,7 +3571,7 @@
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B339">
-        <v>1284</v>
+        <v>11734</v>
       </c>
       <c r="E339">
         <v>0</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B340">
-        <v>11732</v>
+        <v>11735</v>
       </c>
       <c r="E340">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B341">
-        <v>11734</v>
+        <v>11736</v>
       </c>
       <c r="E341">
         <v>0</v>
@@ -3595,7 +3595,7 @@
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B342">
-        <v>11735</v>
+        <v>11737</v>
       </c>
       <c r="E342">
         <v>0</v>
@@ -3603,7 +3603,7 @@
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B343">
-        <v>11736</v>
+        <v>11738</v>
       </c>
       <c r="E343">
         <v>0</v>
@@ -3611,7 +3611,7 @@
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B344">
-        <v>11737</v>
+        <v>11739</v>
       </c>
       <c r="E344">
         <v>0</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B345">
-        <v>11738</v>
+        <v>11740</v>
       </c>
       <c r="E345">
         <v>0</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B346">
-        <v>11739</v>
+        <v>11741</v>
       </c>
       <c r="E346">
         <v>0</v>
@@ -3635,7 +3635,7 @@
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B347">
-        <v>11740</v>
+        <v>11742</v>
       </c>
       <c r="E347">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B348">
-        <v>11741</v>
+        <v>11743</v>
       </c>
       <c r="E348">
         <v>0</v>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B349">
-        <v>11742</v>
+        <v>11744</v>
       </c>
       <c r="E349">
         <v>0</v>
@@ -3659,7 +3659,7 @@
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B350">
-        <v>11743</v>
+        <v>11745</v>
       </c>
       <c r="E350">
         <v>0</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B351">
-        <v>11744</v>
+        <v>11746</v>
       </c>
       <c r="E351">
         <v>0</v>
@@ -3675,7 +3675,7 @@
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B352">
-        <v>11745</v>
+        <v>11747</v>
       </c>
       <c r="E352">
         <v>0</v>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B353">
-        <v>11746</v>
+        <v>11748</v>
       </c>
       <c r="E353">
         <v>0</v>
@@ -3691,7 +3691,7 @@
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B354">
-        <v>11747</v>
+        <v>11749</v>
       </c>
       <c r="E354">
         <v>0</v>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B355">
-        <v>11748</v>
+        <v>11750</v>
       </c>
       <c r="E355">
         <v>0</v>
@@ -3707,7 +3707,7 @@
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B356">
-        <v>11749</v>
+        <v>11751</v>
       </c>
       <c r="E356">
         <v>0</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B357">
-        <v>11750</v>
+        <v>11752</v>
       </c>
       <c r="E357">
         <v>0</v>
@@ -3723,7 +3723,7 @@
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B358">
-        <v>11751</v>
+        <v>11753</v>
       </c>
       <c r="E358">
         <v>0</v>
@@ -3731,7 +3731,7 @@
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B359">
-        <v>11752</v>
+        <v>11754</v>
       </c>
       <c r="E359">
         <v>0</v>
@@ -3739,7 +3739,7 @@
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B360">
-        <v>11753</v>
+        <v>11755</v>
       </c>
       <c r="E360">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B361">
-        <v>11754</v>
+        <v>11756</v>
       </c>
       <c r="E361">
         <v>0</v>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B362">
-        <v>11755</v>
+        <v>11757</v>
       </c>
       <c r="E362">
         <v>0</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B363">
-        <v>11756</v>
+        <v>11758</v>
       </c>
       <c r="E363">
         <v>0</v>
@@ -3771,7 +3771,7 @@
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B364">
-        <v>11757</v>
+        <v>11759</v>
       </c>
       <c r="E364">
         <v>0</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B365">
-        <v>11758</v>
+        <v>11760</v>
       </c>
       <c r="E365">
         <v>0</v>
@@ -3787,7 +3787,7 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B366">
-        <v>11759</v>
+        <v>11761</v>
       </c>
       <c r="E366">
         <v>0</v>
@@ -3795,7 +3795,7 @@
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B367">
-        <v>11760</v>
+        <v>11762</v>
       </c>
       <c r="E367">
         <v>0</v>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B368">
-        <v>11761</v>
+        <v>11763</v>
       </c>
       <c r="E368">
         <v>0</v>
@@ -3811,7 +3811,7 @@
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B369">
-        <v>11762</v>
+        <v>11764</v>
       </c>
       <c r="E369">
         <v>0</v>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B370">
-        <v>11763</v>
+        <v>11765</v>
       </c>
       <c r="E370">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B371">
-        <v>11764</v>
+        <v>11799</v>
       </c>
       <c r="E371">
         <v>0</v>
@@ -3835,7 +3835,7 @@
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B372">
-        <v>11765</v>
+        <v>11800</v>
       </c>
       <c r="E372">
         <v>0</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B373">
-        <v>11799</v>
+        <v>11801</v>
       </c>
       <c r="E373">
         <v>0</v>
@@ -3851,7 +3851,7 @@
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B374">
-        <v>11800</v>
+        <v>11802</v>
       </c>
       <c r="E374">
         <v>0</v>
@@ -3859,7 +3859,7 @@
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B375">
-        <v>11801</v>
+        <v>11803</v>
       </c>
       <c r="E375">
         <v>0</v>
@@ -3867,7 +3867,7 @@
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B376">
-        <v>11802</v>
+        <v>11766</v>
       </c>
       <c r="E376">
         <v>0</v>
@@ -3875,7 +3875,7 @@
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B377">
-        <v>11803</v>
+        <v>11767</v>
       </c>
       <c r="E377">
         <v>0</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B378">
-        <v>11766</v>
+        <v>11768</v>
       </c>
       <c r="E378">
         <v>0</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B379">
-        <v>11767</v>
+        <v>11769</v>
       </c>
       <c r="E379">
         <v>0</v>
@@ -3899,7 +3899,7 @@
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B380">
-        <v>11768</v>
+        <v>11770</v>
       </c>
       <c r="E380">
         <v>0</v>
@@ -3907,7 +3907,7 @@
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B381">
-        <v>11769</v>
+        <v>11771</v>
       </c>
       <c r="E381">
         <v>0</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B382">
-        <v>11770</v>
+        <v>11772</v>
       </c>
       <c r="E382">
         <v>0</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B383">
-        <v>11771</v>
+        <v>11773</v>
       </c>
       <c r="E383">
         <v>0</v>
@@ -3931,7 +3931,7 @@
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B384">
-        <v>11772</v>
+        <v>11774</v>
       </c>
       <c r="E384">
         <v>0</v>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B385">
-        <v>11773</v>
+        <v>11775</v>
       </c>
       <c r="E385">
         <v>0</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B386">
-        <v>11774</v>
+        <v>11776</v>
       </c>
       <c r="E386">
         <v>0</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B387">
-        <v>11775</v>
+        <v>11777</v>
       </c>
       <c r="E387">
         <v>0</v>
@@ -3963,7 +3963,7 @@
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B388">
-        <v>11776</v>
+        <v>11778</v>
       </c>
       <c r="E388">
         <v>0</v>
@@ -3971,7 +3971,7 @@
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B389">
-        <v>11777</v>
+        <v>11779</v>
       </c>
       <c r="E389">
         <v>0</v>
@@ -3979,7 +3979,7 @@
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B390">
-        <v>11778</v>
+        <v>11780</v>
       </c>
       <c r="E390">
         <v>0</v>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B391">
-        <v>11779</v>
+        <v>11781</v>
       </c>
       <c r="E391">
         <v>0</v>
@@ -3995,7 +3995,7 @@
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B392">
-        <v>11780</v>
+        <v>11782</v>
       </c>
       <c r="E392">
         <v>0</v>
@@ -4003,7 +4003,7 @@
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B393">
-        <v>11781</v>
+        <v>11783</v>
       </c>
       <c r="E393">
         <v>0</v>
@@ -4011,7 +4011,7 @@
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B394">
-        <v>11782</v>
+        <v>11784</v>
       </c>
       <c r="E394">
         <v>0</v>
@@ -4019,7 +4019,7 @@
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B395">
-        <v>11783</v>
+        <v>11785</v>
       </c>
       <c r="E395">
         <v>0</v>
@@ -4027,7 +4027,7 @@
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B396">
-        <v>11784</v>
+        <v>11786</v>
       </c>
       <c r="E396">
         <v>0</v>
@@ -4035,7 +4035,7 @@
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B397">
-        <v>11785</v>
+        <v>11787</v>
       </c>
       <c r="E397">
         <v>0</v>
@@ -4043,7 +4043,7 @@
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B398">
-        <v>11786</v>
+        <v>12331</v>
       </c>
       <c r="E398">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B399">
-        <v>11787</v>
+        <v>12345</v>
       </c>
       <c r="E399">
         <v>0</v>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B400">
-        <v>12331</v>
+        <v>12332</v>
       </c>
       <c r="E400">
         <v>0</v>
@@ -4067,7 +4067,7 @@
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B401">
-        <v>12345</v>
+        <v>12333</v>
       </c>
       <c r="E401">
         <v>0</v>
@@ -4075,7 +4075,7 @@
     </row>
     <row r="402" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B402">
-        <v>12332</v>
+        <v>12334</v>
       </c>
       <c r="E402">
         <v>0</v>
@@ -4083,7 +4083,7 @@
     </row>
     <row r="403" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B403">
-        <v>12333</v>
+        <v>12335</v>
       </c>
       <c r="E403">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     </row>
     <row r="404" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B404">
-        <v>12334</v>
+        <v>12336</v>
       </c>
       <c r="E404">
         <v>0</v>
@@ -4099,7 +4099,7 @@
     </row>
     <row r="405" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B405">
-        <v>12335</v>
+        <v>12337</v>
       </c>
       <c r="E405">
         <v>0</v>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="406" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B406">
-        <v>12336</v>
+        <v>12338</v>
       </c>
       <c r="E406">
         <v>0</v>
@@ -4115,7 +4115,7 @@
     </row>
     <row r="407" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B407">
-        <v>12337</v>
+        <v>12339</v>
       </c>
       <c r="E407">
         <v>0</v>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="408" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B408">
-        <v>12338</v>
+        <v>12343</v>
       </c>
       <c r="E408">
         <v>0</v>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="409" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B409">
-        <v>12339</v>
+        <v>12341</v>
       </c>
       <c r="E409">
         <v>0</v>
@@ -4139,7 +4139,7 @@
     </row>
     <row r="410" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B410">
-        <v>12343</v>
+        <v>12342</v>
       </c>
       <c r="E410">
         <v>0</v>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="411" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B411">
-        <v>12341</v>
+        <v>12340</v>
       </c>
       <c r="E411">
         <v>0</v>
@@ -4155,7 +4155,7 @@
     </row>
     <row r="412" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B412">
-        <v>12342</v>
+        <v>12344</v>
       </c>
       <c r="E412">
         <v>0</v>
@@ -4163,7 +4163,7 @@
     </row>
     <row r="413" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B413">
-        <v>12340</v>
+        <v>12346</v>
       </c>
       <c r="E413">
         <v>0</v>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="414" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B414">
-        <v>12344</v>
+        <v>12347</v>
       </c>
       <c r="E414">
         <v>0</v>
@@ -4179,7 +4179,7 @@
     </row>
     <row r="415" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B415">
-        <v>12346</v>
+        <v>12348</v>
       </c>
       <c r="E415">
         <v>0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="416" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B416">
-        <v>12347</v>
+        <v>12349</v>
       </c>
       <c r="E416">
         <v>0</v>
@@ -4195,7 +4195,7 @@
     </row>
     <row r="417" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B417">
-        <v>12348</v>
+        <v>12350</v>
       </c>
       <c r="E417">
         <v>0</v>
@@ -4203,7 +4203,7 @@
     </row>
     <row r="418" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B418">
-        <v>12349</v>
+        <v>12351</v>
       </c>
       <c r="E418">
         <v>0</v>
@@ -4211,7 +4211,7 @@
     </row>
     <row r="419" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B419">
-        <v>12350</v>
+        <v>12352</v>
       </c>
       <c r="E419">
         <v>0</v>
@@ -4219,7 +4219,7 @@
     </row>
     <row r="420" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B420">
-        <v>12351</v>
+        <v>12353</v>
       </c>
       <c r="E420">
         <v>0</v>
@@ -4227,7 +4227,7 @@
     </row>
     <row r="421" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B421">
-        <v>12352</v>
+        <v>12354</v>
       </c>
       <c r="E421">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="422" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B422">
-        <v>12353</v>
+        <v>12355</v>
       </c>
       <c r="E422">
         <v>0</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="423" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B423">
-        <v>12354</v>
+        <v>12356</v>
       </c>
       <c r="E423">
         <v>0</v>
@@ -4251,7 +4251,7 @@
     </row>
     <row r="424" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B424">
-        <v>12355</v>
+        <v>12357</v>
       </c>
       <c r="E424">
         <v>0</v>
@@ -4259,7 +4259,7 @@
     </row>
     <row r="425" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B425">
-        <v>12356</v>
+        <v>12358</v>
       </c>
       <c r="E425">
         <v>0</v>
@@ -4267,7 +4267,7 @@
     </row>
     <row r="426" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B426">
-        <v>12357</v>
+        <v>12359</v>
       </c>
       <c r="E426">
         <v>0</v>
@@ -4275,7 +4275,7 @@
     </row>
     <row r="427" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B427">
-        <v>12358</v>
+        <v>12360</v>
       </c>
       <c r="E427">
         <v>0</v>
@@ -4283,7 +4283,7 @@
     </row>
     <row r="428" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B428">
-        <v>12359</v>
+        <v>12361</v>
       </c>
       <c r="E428">
         <v>0</v>
@@ -4291,7 +4291,7 @@
     </row>
     <row r="429" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B429">
-        <v>12360</v>
+        <v>12362</v>
       </c>
       <c r="E429">
         <v>0</v>
@@ -4299,7 +4299,7 @@
     </row>
     <row r="430" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B430">
-        <v>12361</v>
+        <v>12363</v>
       </c>
       <c r="E430">
         <v>0</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="431" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B431">
-        <v>12362</v>
+        <v>12364</v>
       </c>
       <c r="E431">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     </row>
     <row r="432" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B432">
-        <v>12363</v>
+        <v>12365</v>
       </c>
       <c r="E432">
         <v>0</v>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="433" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B433">
-        <v>12364</v>
+        <v>12366</v>
       </c>
       <c r="E433">
         <v>0</v>
@@ -4331,7 +4331,7 @@
     </row>
     <row r="434" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B434">
-        <v>12365</v>
+        <v>12367</v>
       </c>
       <c r="E434">
         <v>0</v>
@@ -4339,7 +4339,7 @@
     </row>
     <row r="435" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B435">
-        <v>12366</v>
+        <v>12368</v>
       </c>
       <c r="E435">
         <v>0</v>
@@ -4347,7 +4347,7 @@
     </row>
     <row r="436" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B436">
-        <v>12367</v>
+        <v>12369</v>
       </c>
       <c r="E436">
         <v>0</v>
@@ -4355,7 +4355,7 @@
     </row>
     <row r="437" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B437">
-        <v>12368</v>
+        <v>12370</v>
       </c>
       <c r="E437">
         <v>0</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="438" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B438">
-        <v>12369</v>
+        <v>12371</v>
       </c>
       <c r="E438">
         <v>0</v>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="439" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B439">
-        <v>12370</v>
+        <v>12373</v>
       </c>
       <c r="E439">
         <v>0</v>
@@ -4379,7 +4379,7 @@
     </row>
     <row r="440" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B440">
-        <v>12371</v>
+        <v>12374</v>
       </c>
       <c r="E440">
         <v>0</v>
@@ -4387,7 +4387,7 @@
     </row>
     <row r="441" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B441">
-        <v>12373</v>
+        <v>12375</v>
       </c>
       <c r="E441">
         <v>0</v>
@@ -4395,7 +4395,7 @@
     </row>
     <row r="442" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B442">
-        <v>12374</v>
+        <v>12376</v>
       </c>
       <c r="E442">
         <v>0</v>
@@ -4403,7 +4403,7 @@
     </row>
     <row r="443" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B443">
-        <v>12375</v>
+        <v>12377</v>
       </c>
       <c r="E443">
         <v>0</v>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="444" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B444">
-        <v>12376</v>
+        <v>12378</v>
       </c>
       <c r="E444">
         <v>0</v>
@@ -4419,7 +4419,7 @@
     </row>
     <row r="445" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B445">
-        <v>12377</v>
+        <v>12379</v>
       </c>
       <c r="E445">
         <v>0</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="446" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B446">
-        <v>12378</v>
+        <v>12380</v>
       </c>
       <c r="E446">
         <v>0</v>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="447" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B447">
-        <v>12379</v>
+        <v>12381</v>
       </c>
       <c r="E447">
         <v>0</v>
@@ -4443,7 +4443,7 @@
     </row>
     <row r="448" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B448">
-        <v>12380</v>
+        <v>12382</v>
       </c>
       <c r="E448">
         <v>0</v>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="449" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B449">
-        <v>12381</v>
+        <v>12383</v>
       </c>
       <c r="E449">
         <v>0</v>
@@ -4459,7 +4459,7 @@
     </row>
     <row r="450" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B450">
-        <v>12382</v>
+        <v>12384</v>
       </c>
       <c r="E450">
         <v>0</v>
@@ -4467,7 +4467,7 @@
     </row>
     <row r="451" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B451">
-        <v>12383</v>
+        <v>12385</v>
       </c>
       <c r="E451">
         <v>0</v>
@@ -4475,7 +4475,7 @@
     </row>
     <row r="452" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B452">
-        <v>12384</v>
+        <v>12386</v>
       </c>
       <c r="E452">
         <v>0</v>
@@ -4483,7 +4483,7 @@
     </row>
     <row r="453" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B453">
-        <v>12385</v>
+        <v>12387</v>
       </c>
       <c r="E453">
         <v>0</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="454" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B454">
-        <v>12386</v>
+        <v>12388</v>
       </c>
       <c r="E454">
         <v>0</v>
@@ -4499,7 +4499,7 @@
     </row>
     <row r="455" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B455">
-        <v>12387</v>
+        <v>12389</v>
       </c>
       <c r="E455">
         <v>0</v>
@@ -4507,7 +4507,7 @@
     </row>
     <row r="456" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B456">
-        <v>12388</v>
+        <v>12390</v>
       </c>
       <c r="E456">
         <v>0</v>
@@ -4515,7 +4515,7 @@
     </row>
     <row r="457" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B457">
-        <v>12389</v>
+        <v>12391</v>
       </c>
       <c r="E457">
         <v>0</v>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="458" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B458">
-        <v>12390</v>
+        <v>12392</v>
       </c>
       <c r="E458">
         <v>0</v>
@@ -4531,7 +4531,7 @@
     </row>
     <row r="459" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B459">
-        <v>12391</v>
+        <v>12393</v>
       </c>
       <c r="E459">
         <v>0</v>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="460" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B460">
-        <v>12392</v>
+        <v>12394</v>
       </c>
       <c r="E460">
         <v>0</v>
@@ -4547,7 +4547,7 @@
     </row>
     <row r="461" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B461">
-        <v>12393</v>
+        <v>12395</v>
       </c>
       <c r="E461">
         <v>0</v>
@@ -4555,7 +4555,7 @@
     </row>
     <row r="462" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B462">
-        <v>12394</v>
+        <v>12396</v>
       </c>
       <c r="E462">
         <v>0</v>
@@ -4563,7 +4563,7 @@
     </row>
     <row r="463" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B463">
-        <v>12395</v>
+        <v>12397</v>
       </c>
       <c r="E463">
         <v>0</v>
@@ -4571,7 +4571,7 @@
     </row>
     <row r="464" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B464">
-        <v>12396</v>
+        <v>12398</v>
       </c>
       <c r="E464">
         <v>0</v>
@@ -4579,7 +4579,7 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B465">
-        <v>12397</v>
+        <v>12399</v>
       </c>
       <c r="E465">
         <v>0</v>
@@ -4587,7 +4587,7 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B466">
-        <v>12398</v>
+        <v>12400</v>
       </c>
       <c r="E466">
         <v>0</v>
@@ -4595,7 +4595,7 @@
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B467">
-        <v>12399</v>
+        <v>12401</v>
       </c>
       <c r="E467">
         <v>0</v>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B468">
-        <v>12400</v>
+        <v>12402</v>
       </c>
       <c r="E468">
         <v>0</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B469">
-        <v>12401</v>
+        <v>12403</v>
       </c>
       <c r="E469">
         <v>0</v>
@@ -4619,7 +4619,7 @@
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B470">
-        <v>12402</v>
+        <v>12404</v>
       </c>
       <c r="E470">
         <v>0</v>
@@ -4627,7 +4627,7 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B471">
-        <v>12403</v>
+        <v>12406</v>
       </c>
       <c r="E471">
         <v>0</v>
@@ -4635,7 +4635,7 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B472">
-        <v>12404</v>
+        <v>12407</v>
       </c>
       <c r="E472">
         <v>0</v>
@@ -4643,7 +4643,7 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B473">
-        <v>12406</v>
+        <v>12408</v>
       </c>
       <c r="E473">
         <v>0</v>
@@ -4651,26 +4651,32 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B474">
-        <v>12407</v>
+        <v>12409</v>
       </c>
       <c r="E474">
         <v>0</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>86</v>
+      </c>
       <c r="B475">
-        <v>12408</v>
-      </c>
-      <c r="E475">
-        <v>0</v>
+        <v>9538</v>
+      </c>
+      <c r="D475" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>88</v>
+      </c>
       <c r="B476">
-        <v>12409</v>
-      </c>
-      <c r="E476">
-        <v>0</v>
+        <v>10428</v>
+      </c>
+      <c r="D476" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
@@ -4678,32 +4684,32 @@
         <v>86</v>
       </c>
       <c r="B477">
-        <v>9538</v>
+        <v>9539</v>
       </c>
       <c r="D477" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B478">
-        <v>10428</v>
+        <v>9540</v>
       </c>
       <c r="D478" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B479">
-        <v>9539</v>
-      </c>
-      <c r="D479" t="s">
-        <v>90</v>
+        <v>6564</v>
+      </c>
+      <c r="E479">
+        <v>0</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
@@ -4711,76 +4717,79 @@
         <v>86</v>
       </c>
       <c r="B480">
-        <v>9540</v>
-      </c>
-      <c r="D480" t="s">
-        <v>91</v>
+        <v>9438</v>
+      </c>
+      <c r="E480">
+        <v>1</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B481">
-        <v>6564</v>
-      </c>
-      <c r="E481">
-        <v>0</v>
+        <v>10294</v>
+      </c>
+      <c r="D481" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B482">
-        <v>9438</v>
-      </c>
-      <c r="E482">
-        <v>1</v>
+        <v>10838</v>
+      </c>
+      <c r="D482" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B483">
-        <v>10294</v>
+        <v>9820</v>
       </c>
       <c r="D483" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B484">
-        <v>10838</v>
+        <v>10210</v>
       </c>
       <c r="D484" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B485">
-        <v>9820</v>
+        <v>9544</v>
       </c>
       <c r="D485" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B486">
-        <v>10210</v>
-      </c>
-      <c r="D486" t="s">
-        <v>95</v>
+        <v>9576</v>
+      </c>
+      <c r="E486">
+        <v>1</v>
+      </c>
+      <c r="F486" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -4788,46 +4797,43 @@
         <v>86</v>
       </c>
       <c r="B487">
-        <v>9544</v>
+        <v>10216</v>
       </c>
       <c r="D487" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B488">
-        <v>9576</v>
-      </c>
-      <c r="E488">
-        <v>1</v>
-      </c>
-      <c r="F488" t="s">
-        <v>12</v>
+        <v>10845</v>
+      </c>
+      <c r="D488" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B489">
-        <v>10216</v>
+        <v>9870</v>
       </c>
       <c r="D489" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B490">
-        <v>10845</v>
+        <v>9859</v>
       </c>
       <c r="D490" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -4835,54 +4841,54 @@
         <v>88</v>
       </c>
       <c r="B491">
-        <v>9870</v>
+        <v>9865</v>
       </c>
       <c r="D491" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B492">
-        <v>9859</v>
+        <v>10134</v>
       </c>
       <c r="D492" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B493">
-        <v>9865</v>
+        <v>9636</v>
       </c>
       <c r="D493" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B494">
-        <v>10134</v>
+        <v>9923</v>
       </c>
       <c r="D494" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B495">
-        <v>9636</v>
+        <v>9869</v>
       </c>
       <c r="D495" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -4890,10 +4896,10 @@
         <v>88</v>
       </c>
       <c r="B496">
-        <v>9923</v>
+        <v>10009</v>
       </c>
       <c r="D496" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
@@ -4901,10 +4907,10 @@
         <v>88</v>
       </c>
       <c r="B497">
-        <v>9869</v>
+        <v>10010</v>
       </c>
       <c r="D497" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
@@ -4912,37 +4918,31 @@
         <v>88</v>
       </c>
       <c r="B498">
-        <v>10009</v>
+        <v>10703</v>
       </c>
       <c r="D498" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A499" t="s">
-        <v>88</v>
-      </c>
       <c r="B499">
-        <v>10010</v>
-      </c>
-      <c r="D499" t="s">
-        <v>106</v>
+        <v>10212</v>
+      </c>
+      <c r="E499">
+        <v>1</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A500" t="s">
-        <v>88</v>
-      </c>
       <c r="B500">
-        <v>10703</v>
-      </c>
-      <c r="D500" t="s">
-        <v>108</v>
+        <v>9627</v>
+      </c>
+      <c r="E500">
+        <v>1</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B501">
-        <v>10212</v>
+        <v>9441</v>
       </c>
       <c r="E501">
         <v>1</v>
@@ -4950,63 +4950,63 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B502">
-        <v>9627</v>
+        <v>24612</v>
       </c>
       <c r="E502">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B503">
-        <v>9441</v>
+        <v>9626</v>
       </c>
       <c r="E503">
         <v>1</v>
-      </c>
-    </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B504">
-        <v>24612</v>
-      </c>
-      <c r="E504">
-        <v>2</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B505">
-        <v>9626</v>
+        <v>10592</v>
       </c>
       <c r="E505">
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B507">
-        <v>10592</v>
-      </c>
-      <c r="E507">
-        <v>1</v>
+    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B510">
+        <v>2963</v>
+      </c>
+      <c r="E510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B511">
+        <v>1155</v>
+      </c>
+      <c r="E511">
+        <v>0</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B512">
-        <v>2963</v>
+        <v>11222</v>
       </c>
       <c r="E512">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B513">
-        <v>1155</v>
+        <v>11142</v>
       </c>
       <c r="E513">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B514">
-        <v>11222</v>
+        <v>11141</v>
       </c>
       <c r="E514">
         <v>1</v>
@@ -5014,51 +5014,45 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B515">
-        <v>11142</v>
+        <v>11223</v>
       </c>
       <c r="E515">
         <v>1</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>86</v>
+      </c>
       <c r="B516">
-        <v>11141</v>
+        <v>1393</v>
       </c>
       <c r="E516">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B517">
-        <v>11223</v>
+        <v>5924</v>
       </c>
       <c r="E517">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A518" t="s">
-        <v>86</v>
-      </c>
       <c r="B518">
-        <v>1393</v>
+        <v>5927</v>
       </c>
       <c r="E518">
         <v>0</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B519">
-        <v>5924</v>
-      </c>
       <c r="E519">
         <v>0</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B520">
-        <v>5927</v>
-      </c>
       <c r="E520">
         <v>0</v>
       </c>
@@ -5080,22 +5074,28 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E524">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B525">
+        <v>7810</v>
+      </c>
       <c r="E525">
         <v>0</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B526">
+        <v>8183</v>
+      </c>
       <c r="E526">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B527">
-        <v>7810</v>
+        <v>8311</v>
       </c>
       <c r="E527">
         <v>0</v>
@@ -5103,65 +5103,65 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B528">
-        <v>8183</v>
+        <v>8312</v>
       </c>
       <c r="E528">
         <v>0</v>
       </c>
     </row>
     <row r="529" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B529">
-        <v>8311</v>
-      </c>
       <c r="E529">
         <v>0</v>
       </c>
     </row>
     <row r="530" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B530">
-        <v>8312</v>
-      </c>
       <c r="E530">
         <v>0</v>
       </c>
     </row>
     <row r="531" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B531">
+        <v>8367</v>
+      </c>
       <c r="E531">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="532" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="E532">
         <v>0</v>
       </c>
     </row>
     <row r="533" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B533">
-        <v>8367</v>
+        <v>8446</v>
       </c>
       <c r="E533">
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B535">
-        <v>8446</v>
-      </c>
-      <c r="E535">
+    <row r="534" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B534">
+        <v>8495</v>
+      </c>
+      <c r="E534">
         <v>0</v>
       </c>
     </row>
     <row r="536" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B536">
-        <v>8495</v>
+        <v>8493</v>
       </c>
       <c r="E536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B537">
+        <v>8492</v>
+      </c>
+      <c r="E537">
         <v>0</v>
       </c>
     </row>
     <row r="538" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B538">
-        <v>8493</v>
+        <v>8498</v>
       </c>
       <c r="E538">
         <v>0</v>
@@ -5169,7 +5169,7 @@
     </row>
     <row r="539" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B539">
-        <v>8492</v>
+        <v>8497</v>
       </c>
       <c r="E539">
         <v>0</v>
@@ -5177,7 +5177,7 @@
     </row>
     <row r="540" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B540">
-        <v>8498</v>
+        <v>8496</v>
       </c>
       <c r="E540">
         <v>0</v>
@@ -5185,7 +5185,7 @@
     </row>
     <row r="541" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B541">
-        <v>8497</v>
+        <v>8499</v>
       </c>
       <c r="E541">
         <v>0</v>
@@ -5193,7 +5193,7 @@
     </row>
     <row r="542" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B542">
-        <v>8496</v>
+        <v>8500</v>
       </c>
       <c r="E542">
         <v>0</v>
@@ -5201,7 +5201,7 @@
     </row>
     <row r="543" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B543">
-        <v>8499</v>
+        <v>8501</v>
       </c>
       <c r="E543">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="544" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B544">
-        <v>8500</v>
+        <v>8502</v>
       </c>
       <c r="E544">
         <v>0</v>
@@ -5217,7 +5217,7 @@
     </row>
     <row r="545" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B545">
-        <v>8501</v>
+        <v>8503</v>
       </c>
       <c r="E545">
         <v>0</v>
@@ -5225,7 +5225,7 @@
     </row>
     <row r="546" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B546">
-        <v>8502</v>
+        <v>8504</v>
       </c>
       <c r="E546">
         <v>0</v>
@@ -5233,7 +5233,7 @@
     </row>
     <row r="547" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B547">
-        <v>8503</v>
+        <v>8505</v>
       </c>
       <c r="E547">
         <v>0</v>
@@ -5241,7 +5241,7 @@
     </row>
     <row r="548" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B548">
-        <v>8504</v>
+        <v>8506</v>
       </c>
       <c r="E548">
         <v>0</v>
@@ -5249,7 +5249,7 @@
     </row>
     <row r="549" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B549">
-        <v>8505</v>
+        <v>8507</v>
       </c>
       <c r="E549">
         <v>0</v>
@@ -5257,7 +5257,7 @@
     </row>
     <row r="550" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B550">
-        <v>8506</v>
+        <v>8508</v>
       </c>
       <c r="E550">
         <v>0</v>
@@ -5265,7 +5265,7 @@
     </row>
     <row r="551" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B551">
-        <v>8507</v>
+        <v>8509</v>
       </c>
       <c r="E551">
         <v>0</v>
@@ -5273,23 +5273,15 @@
     </row>
     <row r="552" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B552">
-        <v>8508</v>
+        <v>8510</v>
       </c>
       <c r="E552">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="553" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B553">
-        <v>8509</v>
-      </c>
-      <c r="E553">
         <v>0</v>
       </c>
     </row>
     <row r="554" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B554">
-        <v>8510</v>
+        <v>8512</v>
       </c>
       <c r="E554">
         <v>0</v>
@@ -5297,15 +5289,23 @@
     </row>
     <row r="556" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B556">
-        <v>8512</v>
+        <v>8514</v>
       </c>
       <c r="E556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="557" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B557">
+        <v>8515</v>
+      </c>
+      <c r="E557">
         <v>0</v>
       </c>
     </row>
     <row r="558" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B558">
-        <v>8514</v>
+        <v>8516</v>
       </c>
       <c r="E558">
         <v>0</v>
@@ -5313,7 +5313,7 @@
     </row>
     <row r="559" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B559">
-        <v>8515</v>
+        <v>8517</v>
       </c>
       <c r="E559">
         <v>0</v>
@@ -5321,7 +5321,7 @@
     </row>
     <row r="560" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B560">
-        <v>8516</v>
+        <v>8518</v>
       </c>
       <c r="E560">
         <v>0</v>
@@ -5329,7 +5329,7 @@
     </row>
     <row r="561" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B561">
-        <v>8517</v>
+        <v>8519</v>
       </c>
       <c r="E561">
         <v>0</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="562" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B562">
-        <v>8518</v>
+        <v>8520</v>
       </c>
       <c r="E562">
         <v>0</v>
@@ -5345,7 +5345,7 @@
     </row>
     <row r="563" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B563">
-        <v>8519</v>
+        <v>8521</v>
       </c>
       <c r="E563">
         <v>0</v>
@@ -5353,7 +5353,7 @@
     </row>
     <row r="564" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B564">
-        <v>8520</v>
+        <v>8522</v>
       </c>
       <c r="E564">
         <v>0</v>
@@ -5361,7 +5361,7 @@
     </row>
     <row r="565" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B565">
-        <v>8521</v>
+        <v>8523</v>
       </c>
       <c r="E565">
         <v>0</v>
@@ -5369,7 +5369,7 @@
     </row>
     <row r="566" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B566">
-        <v>8522</v>
+        <v>8524</v>
       </c>
       <c r="E566">
         <v>0</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="567" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B567">
-        <v>8523</v>
+        <v>8525</v>
       </c>
       <c r="E567">
         <v>0</v>
@@ -5385,7 +5385,7 @@
     </row>
     <row r="568" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B568">
-        <v>8524</v>
+        <v>8526</v>
       </c>
       <c r="E568">
         <v>0</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="569" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B569">
-        <v>8525</v>
+        <v>8527</v>
       </c>
       <c r="E569">
         <v>0</v>
@@ -5401,7 +5401,7 @@
     </row>
     <row r="570" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B570">
-        <v>8526</v>
+        <v>8528</v>
       </c>
       <c r="E570">
         <v>0</v>
@@ -5409,7 +5409,7 @@
     </row>
     <row r="571" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B571">
-        <v>8527</v>
+        <v>8529</v>
       </c>
       <c r="E571">
         <v>0</v>
@@ -5417,7 +5417,7 @@
     </row>
     <row r="572" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B572">
-        <v>8528</v>
+        <v>8530</v>
       </c>
       <c r="E572">
         <v>0</v>
@@ -5425,7 +5425,7 @@
     </row>
     <row r="573" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B573">
-        <v>8529</v>
+        <v>8531</v>
       </c>
       <c r="E573">
         <v>0</v>
@@ -5433,7 +5433,7 @@
     </row>
     <row r="574" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B574">
-        <v>8530</v>
+        <v>8532</v>
       </c>
       <c r="E574">
         <v>0</v>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="575" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B575">
-        <v>8531</v>
+        <v>8533</v>
       </c>
       <c r="E575">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     </row>
     <row r="576" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B576">
-        <v>8532</v>
+        <v>8537</v>
       </c>
       <c r="E576">
         <v>0</v>
@@ -5457,7 +5457,7 @@
     </row>
     <row r="577" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B577">
-        <v>8533</v>
+        <v>8535</v>
       </c>
       <c r="E577">
         <v>0</v>
@@ -5465,7 +5465,7 @@
     </row>
     <row r="578" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B578">
-        <v>8537</v>
+        <v>8538</v>
       </c>
       <c r="E578">
         <v>0</v>
@@ -5473,7 +5473,7 @@
     </row>
     <row r="579" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B579">
-        <v>8535</v>
+        <v>8540</v>
       </c>
       <c r="E579">
         <v>0</v>
@@ -5481,7 +5481,7 @@
     </row>
     <row r="580" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B580">
-        <v>8538</v>
+        <v>8544</v>
       </c>
       <c r="E580">
         <v>0</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="581" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B581">
-        <v>8540</v>
+        <v>8545</v>
       </c>
       <c r="E581">
         <v>0</v>
@@ -5497,7 +5497,7 @@
     </row>
     <row r="582" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B582">
-        <v>8544</v>
+        <v>8546</v>
       </c>
       <c r="E582">
         <v>0</v>
@@ -5505,7 +5505,7 @@
     </row>
     <row r="583" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B583">
-        <v>8545</v>
+        <v>8549</v>
       </c>
       <c r="E583">
         <v>0</v>
@@ -5513,7 +5513,7 @@
     </row>
     <row r="584" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B584">
-        <v>8546</v>
+        <v>8550</v>
       </c>
       <c r="E584">
         <v>0</v>
@@ -5521,7 +5521,7 @@
     </row>
     <row r="585" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B585">
-        <v>8549</v>
+        <v>8556</v>
       </c>
       <c r="E585">
         <v>0</v>
@@ -5529,7 +5529,7 @@
     </row>
     <row r="586" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B586">
-        <v>8550</v>
+        <v>8557</v>
       </c>
       <c r="E586">
         <v>0</v>
@@ -5537,7 +5537,7 @@
     </row>
     <row r="587" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B587">
-        <v>8556</v>
+        <v>8558</v>
       </c>
       <c r="E587">
         <v>0</v>
@@ -5545,7 +5545,7 @@
     </row>
     <row r="588" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B588">
-        <v>8557</v>
+        <v>8559</v>
       </c>
       <c r="E588">
         <v>0</v>
@@ -5553,7 +5553,7 @@
     </row>
     <row r="589" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B589">
-        <v>8558</v>
+        <v>8560</v>
       </c>
       <c r="E589">
         <v>0</v>
@@ -5561,7 +5561,7 @@
     </row>
     <row r="590" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B590">
-        <v>8559</v>
+        <v>8561</v>
       </c>
       <c r="E590">
         <v>0</v>
@@ -5569,7 +5569,7 @@
     </row>
     <row r="591" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B591">
-        <v>8560</v>
+        <v>8562</v>
       </c>
       <c r="E591">
         <v>0</v>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="592" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B592">
-        <v>8561</v>
+        <v>8575</v>
       </c>
       <c r="E592">
         <v>0</v>
@@ -5585,7 +5585,7 @@
     </row>
     <row r="593" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B593">
-        <v>8562</v>
+        <v>8580</v>
       </c>
       <c r="E593">
         <v>0</v>
@@ -5593,7 +5593,7 @@
     </row>
     <row r="594" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B594">
-        <v>8575</v>
+        <v>8581</v>
       </c>
       <c r="E594">
         <v>0</v>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="595" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B595">
-        <v>8580</v>
+        <v>8582</v>
       </c>
       <c r="E595">
         <v>0</v>
@@ -5609,7 +5609,7 @@
     </row>
     <row r="596" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B596">
-        <v>8581</v>
+        <v>8583</v>
       </c>
       <c r="E596">
         <v>0</v>
@@ -5617,7 +5617,7 @@
     </row>
     <row r="597" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B597">
-        <v>8582</v>
+        <v>8588</v>
       </c>
       <c r="E597">
         <v>0</v>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="598" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B598">
-        <v>8583</v>
+        <v>8589</v>
       </c>
       <c r="E598">
         <v>0</v>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="599" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B599">
-        <v>8588</v>
+        <v>8590</v>
       </c>
       <c r="E599">
         <v>0</v>
@@ -5641,7 +5641,7 @@
     </row>
     <row r="600" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B600">
-        <v>8589</v>
+        <v>8591</v>
       </c>
       <c r="E600">
         <v>0</v>
@@ -5649,7 +5649,7 @@
     </row>
     <row r="601" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B601">
-        <v>8590</v>
+        <v>8592</v>
       </c>
       <c r="E601">
         <v>0</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="602" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B602">
-        <v>8591</v>
+        <v>8593</v>
       </c>
       <c r="E602">
         <v>0</v>
@@ -5665,7 +5665,7 @@
     </row>
     <row r="603" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B603">
-        <v>8592</v>
+        <v>8594</v>
       </c>
       <c r="E603">
         <v>0</v>
@@ -5673,7 +5673,7 @@
     </row>
     <row r="604" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B604">
-        <v>8593</v>
+        <v>8595</v>
       </c>
       <c r="E604">
         <v>0</v>
@@ -5681,7 +5681,7 @@
     </row>
     <row r="605" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B605">
-        <v>8594</v>
+        <v>8596</v>
       </c>
       <c r="E605">
         <v>0</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="606" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B606">
-        <v>8595</v>
+        <v>8600</v>
       </c>
       <c r="E606">
         <v>0</v>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="607" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B607">
-        <v>8596</v>
+        <v>8601</v>
       </c>
       <c r="E607">
         <v>0</v>
@@ -5705,7 +5705,7 @@
     </row>
     <row r="608" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B608">
-        <v>8600</v>
+        <v>8602</v>
       </c>
       <c r="E608">
         <v>0</v>
@@ -5713,7 +5713,7 @@
     </row>
     <row r="609" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B609">
-        <v>8601</v>
+        <v>8603</v>
       </c>
       <c r="E609">
         <v>0</v>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="610" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B610">
-        <v>8602</v>
+        <v>8604</v>
       </c>
       <c r="E610">
         <v>0</v>
@@ -5729,7 +5729,7 @@
     </row>
     <row r="611" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B611">
-        <v>8603</v>
+        <v>8605</v>
       </c>
       <c r="E611">
         <v>0</v>
@@ -5737,7 +5737,7 @@
     </row>
     <row r="612" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B612">
-        <v>8604</v>
+        <v>8607</v>
       </c>
       <c r="E612">
         <v>0</v>
@@ -5745,7 +5745,7 @@
     </row>
     <row r="613" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B613">
-        <v>8605</v>
+        <v>8608</v>
       </c>
       <c r="E613">
         <v>0</v>
@@ -5753,7 +5753,7 @@
     </row>
     <row r="614" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B614">
-        <v>8607</v>
+        <v>8609</v>
       </c>
       <c r="E614">
         <v>0</v>
@@ -5761,7 +5761,7 @@
     </row>
     <row r="615" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B615">
-        <v>8608</v>
+        <v>8610</v>
       </c>
       <c r="E615">
         <v>0</v>
@@ -5769,7 +5769,7 @@
     </row>
     <row r="616" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B616">
-        <v>8609</v>
+        <v>8611</v>
       </c>
       <c r="E616">
         <v>0</v>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="617" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B617">
-        <v>8610</v>
+        <v>8612</v>
       </c>
       <c r="E617">
         <v>0</v>
@@ -5785,7 +5785,7 @@
     </row>
     <row r="618" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B618">
-        <v>8611</v>
+        <v>8613</v>
       </c>
       <c r="E618">
         <v>0</v>
@@ -5793,7 +5793,7 @@
     </row>
     <row r="619" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B619">
-        <v>8612</v>
+        <v>8614</v>
       </c>
       <c r="E619">
         <v>0</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="620" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B620">
-        <v>8613</v>
+        <v>8615</v>
       </c>
       <c r="E620">
         <v>0</v>
@@ -5809,7 +5809,7 @@
     </row>
     <row r="621" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B621">
-        <v>8614</v>
+        <v>8616</v>
       </c>
       <c r="E621">
         <v>0</v>
@@ -5817,7 +5817,7 @@
     </row>
     <row r="622" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B622">
-        <v>8615</v>
+        <v>8619</v>
       </c>
       <c r="E622">
         <v>0</v>
@@ -5825,7 +5825,7 @@
     </row>
     <row r="623" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B623">
-        <v>8616</v>
+        <v>8621</v>
       </c>
       <c r="E623">
         <v>0</v>
@@ -5833,7 +5833,7 @@
     </row>
     <row r="624" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B624">
-        <v>8619</v>
+        <v>8622</v>
       </c>
       <c r="E624">
         <v>0</v>
@@ -5841,7 +5841,7 @@
     </row>
     <row r="625" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B625">
-        <v>8621</v>
+        <v>8623</v>
       </c>
       <c r="E625">
         <v>0</v>
@@ -5849,7 +5849,7 @@
     </row>
     <row r="626" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B626">
-        <v>8622</v>
+        <v>8624</v>
       </c>
       <c r="E626">
         <v>0</v>
@@ -5857,7 +5857,7 @@
     </row>
     <row r="627" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B627">
-        <v>8623</v>
+        <v>8625</v>
       </c>
       <c r="E627">
         <v>0</v>
@@ -5865,7 +5865,7 @@
     </row>
     <row r="628" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B628">
-        <v>8624</v>
+        <v>8626</v>
       </c>
       <c r="E628">
         <v>0</v>
@@ -5873,7 +5873,7 @@
     </row>
     <row r="629" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B629">
-        <v>8625</v>
+        <v>8627</v>
       </c>
       <c r="E629">
         <v>0</v>
@@ -5881,7 +5881,7 @@
     </row>
     <row r="630" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B630">
-        <v>8626</v>
+        <v>8628</v>
       </c>
       <c r="E630">
         <v>0</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="631" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B631">
-        <v>8627</v>
+        <v>8629</v>
       </c>
       <c r="E631">
         <v>0</v>
@@ -5897,7 +5897,7 @@
     </row>
     <row r="632" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B632">
-        <v>8628</v>
+        <v>8630</v>
       </c>
       <c r="E632">
         <v>0</v>
@@ -5905,7 +5905,7 @@
     </row>
     <row r="633" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B633">
-        <v>8629</v>
+        <v>8631</v>
       </c>
       <c r="E633">
         <v>0</v>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="634" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B634">
-        <v>8630</v>
+        <v>8632</v>
       </c>
       <c r="E634">
         <v>0</v>
@@ -5921,7 +5921,7 @@
     </row>
     <row r="635" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B635">
-        <v>8631</v>
+        <v>8633</v>
       </c>
       <c r="E635">
         <v>0</v>
@@ -5929,7 +5929,7 @@
     </row>
     <row r="636" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B636">
-        <v>8632</v>
+        <v>8634</v>
       </c>
       <c r="E636">
         <v>0</v>
@@ -5937,7 +5937,7 @@
     </row>
     <row r="637" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B637">
-        <v>8633</v>
+        <v>8635</v>
       </c>
       <c r="E637">
         <v>0</v>
@@ -5945,7 +5945,7 @@
     </row>
     <row r="638" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B638">
-        <v>8634</v>
+        <v>8636</v>
       </c>
       <c r="E638">
         <v>0</v>
@@ -5953,7 +5953,7 @@
     </row>
     <row r="639" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B639">
-        <v>8635</v>
+        <v>8637</v>
       </c>
       <c r="E639">
         <v>0</v>
@@ -5961,7 +5961,7 @@
     </row>
     <row r="640" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B640">
-        <v>8636</v>
+        <v>8638</v>
       </c>
       <c r="E640">
         <v>0</v>
@@ -5969,7 +5969,7 @@
     </row>
     <row r="641" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B641">
-        <v>8637</v>
+        <v>8639</v>
       </c>
       <c r="E641">
         <v>0</v>
@@ -5977,7 +5977,7 @@
     </row>
     <row r="642" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B642">
-        <v>8638</v>
+        <v>8640</v>
       </c>
       <c r="E642">
         <v>0</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="643" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B643">
-        <v>8639</v>
+        <v>8641</v>
       </c>
       <c r="E643">
         <v>0</v>
@@ -5993,7 +5993,7 @@
     </row>
     <row r="644" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B644">
-        <v>8640</v>
+        <v>8642</v>
       </c>
       <c r="E644">
         <v>0</v>
@@ -6001,7 +6001,7 @@
     </row>
     <row r="645" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B645">
-        <v>8641</v>
+        <v>8643</v>
       </c>
       <c r="E645">
         <v>0</v>
@@ -6009,7 +6009,7 @@
     </row>
     <row r="646" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B646">
-        <v>8642</v>
+        <v>8644</v>
       </c>
       <c r="E646">
         <v>0</v>
@@ -6017,7 +6017,7 @@
     </row>
     <row r="647" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B647">
-        <v>8643</v>
+        <v>8645</v>
       </c>
       <c r="E647">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     </row>
     <row r="648" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B648">
-        <v>8644</v>
+        <v>8646</v>
       </c>
       <c r="E648">
         <v>0</v>
@@ -6033,7 +6033,7 @@
     </row>
     <row r="649" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B649">
-        <v>8645</v>
+        <v>8647</v>
       </c>
       <c r="E649">
         <v>0</v>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="650" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B650">
-        <v>8646</v>
+        <v>8648</v>
       </c>
       <c r="E650">
         <v>0</v>
@@ -6049,7 +6049,7 @@
     </row>
     <row r="651" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B651">
-        <v>8647</v>
+        <v>8649</v>
       </c>
       <c r="E651">
         <v>0</v>
@@ -6057,7 +6057,7 @@
     </row>
     <row r="652" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B652">
-        <v>8648</v>
+        <v>8650</v>
       </c>
       <c r="E652">
         <v>0</v>
@@ -6065,7 +6065,7 @@
     </row>
     <row r="653" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B653">
-        <v>8649</v>
+        <v>8651</v>
       </c>
       <c r="E653">
         <v>0</v>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="654" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B654">
-        <v>8650</v>
+        <v>8652</v>
       </c>
       <c r="E654">
         <v>0</v>
@@ -6081,7 +6081,7 @@
     </row>
     <row r="655" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B655">
-        <v>8651</v>
+        <v>8653</v>
       </c>
       <c r="E655">
         <v>0</v>
@@ -6089,7 +6089,7 @@
     </row>
     <row r="656" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B656">
-        <v>8652</v>
+        <v>8654</v>
       </c>
       <c r="E656">
         <v>0</v>
@@ -6097,7 +6097,7 @@
     </row>
     <row r="657" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B657">
-        <v>8653</v>
+        <v>8655</v>
       </c>
       <c r="E657">
         <v>0</v>
@@ -6105,7 +6105,7 @@
     </row>
     <row r="658" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B658">
-        <v>8654</v>
+        <v>8656</v>
       </c>
       <c r="E658">
         <v>0</v>
@@ -6113,7 +6113,7 @@
     </row>
     <row r="659" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B659">
-        <v>8655</v>
+        <v>8657</v>
       </c>
       <c r="E659">
         <v>0</v>
@@ -6121,7 +6121,7 @@
     </row>
     <row r="660" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B660">
-        <v>8656</v>
+        <v>8658</v>
       </c>
       <c r="E660">
         <v>0</v>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="661" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B661">
-        <v>8657</v>
+        <v>8659</v>
       </c>
       <c r="E661">
         <v>0</v>
@@ -6137,7 +6137,7 @@
     </row>
     <row r="662" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B662">
-        <v>8658</v>
+        <v>8660</v>
       </c>
       <c r="E662">
         <v>0</v>
@@ -6145,7 +6145,7 @@
     </row>
     <row r="663" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B663">
-        <v>8659</v>
+        <v>8661</v>
       </c>
       <c r="E663">
         <v>0</v>
@@ -6153,7 +6153,7 @@
     </row>
     <row r="664" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B664">
-        <v>8660</v>
+        <v>8662</v>
       </c>
       <c r="E664">
         <v>0</v>
@@ -6161,7 +6161,7 @@
     </row>
     <row r="665" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B665">
-        <v>8661</v>
+        <v>8663</v>
       </c>
       <c r="E665">
         <v>0</v>
@@ -6169,7 +6169,7 @@
     </row>
     <row r="666" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B666">
-        <v>8662</v>
+        <v>8664</v>
       </c>
       <c r="E666">
         <v>0</v>
@@ -6177,7 +6177,7 @@
     </row>
     <row r="667" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B667">
-        <v>8663</v>
+        <v>8665</v>
       </c>
       <c r="E667">
         <v>0</v>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="668" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B668">
-        <v>8664</v>
+        <v>8666</v>
       </c>
       <c r="E668">
         <v>0</v>
@@ -6193,7 +6193,7 @@
     </row>
     <row r="669" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B669">
-        <v>8665</v>
+        <v>8667</v>
       </c>
       <c r="E669">
         <v>0</v>
@@ -6201,7 +6201,7 @@
     </row>
     <row r="670" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B670">
-        <v>8666</v>
+        <v>8668</v>
       </c>
       <c r="E670">
         <v>0</v>
@@ -6209,7 +6209,7 @@
     </row>
     <row r="671" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B671">
-        <v>8667</v>
+        <v>8669</v>
       </c>
       <c r="E671">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="672" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B672">
-        <v>8668</v>
+        <v>8670</v>
       </c>
       <c r="E672">
         <v>0</v>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="673" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B673">
-        <v>8669</v>
+        <v>8671</v>
       </c>
       <c r="E673">
         <v>0</v>
@@ -6233,7 +6233,7 @@
     </row>
     <row r="674" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B674">
-        <v>8670</v>
+        <v>8672</v>
       </c>
       <c r="E674">
         <v>0</v>
@@ -6241,7 +6241,7 @@
     </row>
     <row r="675" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B675">
-        <v>8671</v>
+        <v>8673</v>
       </c>
       <c r="E675">
         <v>0</v>
@@ -6249,7 +6249,7 @@
     </row>
     <row r="676" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B676">
-        <v>8672</v>
+        <v>8674</v>
       </c>
       <c r="E676">
         <v>0</v>
@@ -6257,7 +6257,7 @@
     </row>
     <row r="677" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B677">
-        <v>8673</v>
+        <v>8675</v>
       </c>
       <c r="E677">
         <v>0</v>
@@ -6265,7 +6265,7 @@
     </row>
     <row r="678" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B678">
-        <v>8674</v>
+        <v>8676</v>
       </c>
       <c r="E678">
         <v>0</v>
@@ -6273,7 +6273,7 @@
     </row>
     <row r="679" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B679">
-        <v>8675</v>
+        <v>8677</v>
       </c>
       <c r="E679">
         <v>0</v>
@@ -6281,7 +6281,7 @@
     </row>
     <row r="680" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B680">
-        <v>8676</v>
+        <v>8678</v>
       </c>
       <c r="E680">
         <v>0</v>
@@ -6289,7 +6289,7 @@
     </row>
     <row r="681" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B681">
-        <v>8677</v>
+        <v>8679</v>
       </c>
       <c r="E681">
         <v>0</v>
@@ -6297,7 +6297,7 @@
     </row>
     <row r="682" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B682">
-        <v>8678</v>
+        <v>8680</v>
       </c>
       <c r="E682">
         <v>0</v>
@@ -6305,7 +6305,7 @@
     </row>
     <row r="683" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B683">
-        <v>8679</v>
+        <v>8681</v>
       </c>
       <c r="E683">
         <v>0</v>
@@ -6313,7 +6313,7 @@
     </row>
     <row r="684" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B684">
-        <v>8680</v>
+        <v>8682</v>
       </c>
       <c r="E684">
         <v>0</v>
@@ -6321,7 +6321,7 @@
     </row>
     <row r="685" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B685">
-        <v>8681</v>
+        <v>8683</v>
       </c>
       <c r="E685">
         <v>0</v>
@@ -6329,7 +6329,7 @@
     </row>
     <row r="686" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B686">
-        <v>8682</v>
+        <v>8684</v>
       </c>
       <c r="E686">
         <v>0</v>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="687" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B687">
-        <v>8683</v>
+        <v>8685</v>
       </c>
       <c r="E687">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     </row>
     <row r="688" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B688">
-        <v>8684</v>
+        <v>8686</v>
       </c>
       <c r="E688">
         <v>0</v>
@@ -6353,7 +6353,7 @@
     </row>
     <row r="689" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B689">
-        <v>8685</v>
+        <v>8687</v>
       </c>
       <c r="E689">
         <v>0</v>
@@ -6361,7 +6361,7 @@
     </row>
     <row r="690" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B690">
-        <v>8686</v>
+        <v>8688</v>
       </c>
       <c r="E690">
         <v>0</v>
@@ -6369,7 +6369,7 @@
     </row>
     <row r="691" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B691">
-        <v>8687</v>
+        <v>8689</v>
       </c>
       <c r="E691">
         <v>0</v>
@@ -6377,7 +6377,7 @@
     </row>
     <row r="692" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B692">
-        <v>8688</v>
+        <v>8690</v>
       </c>
       <c r="E692">
         <v>0</v>
@@ -6385,7 +6385,7 @@
     </row>
     <row r="693" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B693">
-        <v>8689</v>
+        <v>8691</v>
       </c>
       <c r="E693">
         <v>0</v>
@@ -6393,7 +6393,7 @@
     </row>
     <row r="694" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B694">
-        <v>8690</v>
+        <v>8692</v>
       </c>
       <c r="E694">
         <v>0</v>
@@ -6401,7 +6401,7 @@
     </row>
     <row r="695" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B695">
-        <v>8691</v>
+        <v>8693</v>
       </c>
       <c r="E695">
         <v>0</v>
@@ -6409,7 +6409,7 @@
     </row>
     <row r="696" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B696">
-        <v>8692</v>
+        <v>8694</v>
       </c>
       <c r="E696">
         <v>0</v>
@@ -6417,7 +6417,7 @@
     </row>
     <row r="697" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B697">
-        <v>8693</v>
+        <v>8695</v>
       </c>
       <c r="E697">
         <v>0</v>
@@ -6425,7 +6425,7 @@
     </row>
     <row r="698" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B698">
-        <v>8694</v>
+        <v>8696</v>
       </c>
       <c r="E698">
         <v>0</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="699" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B699">
-        <v>8695</v>
+        <v>8697</v>
       </c>
       <c r="E699">
         <v>0</v>
@@ -6441,7 +6441,7 @@
     </row>
     <row r="700" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B700">
-        <v>8696</v>
+        <v>8698</v>
       </c>
       <c r="E700">
         <v>0</v>
@@ -6449,31 +6449,31 @@
     </row>
     <row r="701" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B701">
-        <v>8697</v>
+        <v>8699</v>
       </c>
       <c r="E701">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="702" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B702">
-        <v>8698</v>
-      </c>
-      <c r="E702">
         <v>0</v>
       </c>
     </row>
     <row r="703" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B703">
-        <v>8699</v>
+        <v>8701</v>
       </c>
       <c r="E703">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B704">
+        <v>8702</v>
+      </c>
+      <c r="E704">
         <v>0</v>
       </c>
     </row>
     <row r="705" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B705">
-        <v>8701</v>
+        <v>8703</v>
       </c>
       <c r="E705">
         <v>0</v>
@@ -6481,7 +6481,7 @@
     </row>
     <row r="706" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B706">
-        <v>8702</v>
+        <v>8704</v>
       </c>
       <c r="E706">
         <v>0</v>
@@ -6489,7 +6489,7 @@
     </row>
     <row r="707" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B707">
-        <v>8703</v>
+        <v>8705</v>
       </c>
       <c r="E707">
         <v>0</v>
@@ -6497,7 +6497,7 @@
     </row>
     <row r="708" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B708">
-        <v>8704</v>
+        <v>8706</v>
       </c>
       <c r="E708">
         <v>0</v>
@@ -6505,7 +6505,7 @@
     </row>
     <row r="709" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B709">
-        <v>8705</v>
+        <v>8707</v>
       </c>
       <c r="E709">
         <v>0</v>
@@ -6513,7 +6513,7 @@
     </row>
     <row r="710" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B710">
-        <v>8706</v>
+        <v>8708</v>
       </c>
       <c r="E710">
         <v>0</v>
@@ -6521,7 +6521,7 @@
     </row>
     <row r="711" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B711">
-        <v>8707</v>
+        <v>8709</v>
       </c>
       <c r="E711">
         <v>0</v>
@@ -6529,7 +6529,7 @@
     </row>
     <row r="712" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B712">
-        <v>8708</v>
+        <v>8710</v>
       </c>
       <c r="E712">
         <v>0</v>
@@ -6537,7 +6537,7 @@
     </row>
     <row r="713" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B713">
-        <v>8709</v>
+        <v>8711</v>
       </c>
       <c r="E713">
         <v>0</v>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="714" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B714">
-        <v>8710</v>
+        <v>8712</v>
       </c>
       <c r="E714">
         <v>0</v>
@@ -6553,7 +6553,7 @@
     </row>
     <row r="715" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B715">
-        <v>8711</v>
+        <v>8713</v>
       </c>
       <c r="E715">
         <v>0</v>
@@ -6561,7 +6561,7 @@
     </row>
     <row r="716" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B716">
-        <v>8712</v>
+        <v>8714</v>
       </c>
       <c r="E716">
         <v>0</v>
@@ -6569,7 +6569,7 @@
     </row>
     <row r="717" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B717">
-        <v>8713</v>
+        <v>8715</v>
       </c>
       <c r="E717">
         <v>0</v>
@@ -6577,7 +6577,7 @@
     </row>
     <row r="718" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B718">
-        <v>8714</v>
+        <v>8716</v>
       </c>
       <c r="E718">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     </row>
     <row r="719" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B719">
-        <v>8715</v>
+        <v>8717</v>
       </c>
       <c r="E719">
         <v>0</v>
@@ -6593,7 +6593,7 @@
     </row>
     <row r="720" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B720">
-        <v>8716</v>
+        <v>8718</v>
       </c>
       <c r="E720">
         <v>0</v>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="721" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B721">
-        <v>8717</v>
+        <v>8719</v>
       </c>
       <c r="E721">
         <v>0</v>
@@ -6609,7 +6609,7 @@
     </row>
     <row r="722" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B722">
-        <v>8718</v>
+        <v>8720</v>
       </c>
       <c r="E722">
         <v>0</v>
@@ -6617,7 +6617,7 @@
     </row>
     <row r="723" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B723">
-        <v>8719</v>
+        <v>8721</v>
       </c>
       <c r="E723">
         <v>0</v>
@@ -6625,7 +6625,7 @@
     </row>
     <row r="724" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B724">
-        <v>8720</v>
+        <v>8722</v>
       </c>
       <c r="E724">
         <v>0</v>
@@ -6633,7 +6633,7 @@
     </row>
     <row r="725" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B725">
-        <v>8721</v>
+        <v>8723</v>
       </c>
       <c r="E725">
         <v>0</v>
@@ -6641,7 +6641,7 @@
     </row>
     <row r="726" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B726">
-        <v>8722</v>
+        <v>8724</v>
       </c>
       <c r="E726">
         <v>0</v>
@@ -6649,7 +6649,7 @@
     </row>
     <row r="727" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B727">
-        <v>8723</v>
+        <v>8725</v>
       </c>
       <c r="E727">
         <v>0</v>
@@ -6657,7 +6657,7 @@
     </row>
     <row r="728" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B728">
-        <v>8724</v>
+        <v>8726</v>
       </c>
       <c r="E728">
         <v>0</v>
@@ -6665,7 +6665,7 @@
     </row>
     <row r="729" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B729">
-        <v>8725</v>
+        <v>8727</v>
       </c>
       <c r="E729">
         <v>0</v>
@@ -6673,7 +6673,7 @@
     </row>
     <row r="730" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B730">
-        <v>8726</v>
+        <v>8731</v>
       </c>
       <c r="E730">
         <v>0</v>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="731" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B731">
-        <v>8727</v>
+        <v>8732</v>
       </c>
       <c r="E731">
         <v>0</v>
@@ -6689,7 +6689,7 @@
     </row>
     <row r="732" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B732">
-        <v>8731</v>
+        <v>8740</v>
       </c>
       <c r="E732">
         <v>0</v>
@@ -6697,7 +6697,7 @@
     </row>
     <row r="733" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B733">
-        <v>8732</v>
+        <v>8745</v>
       </c>
       <c r="E733">
         <v>0</v>
@@ -6705,7 +6705,7 @@
     </row>
     <row r="734" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B734">
-        <v>8740</v>
+        <v>8780</v>
       </c>
       <c r="E734">
         <v>0</v>
@@ -6713,7 +6713,7 @@
     </row>
     <row r="735" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B735">
-        <v>8745</v>
+        <v>8789</v>
       </c>
       <c r="E735">
         <v>0</v>
@@ -6721,7 +6721,7 @@
     </row>
     <row r="736" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B736">
-        <v>8780</v>
+        <v>8790</v>
       </c>
       <c r="E736">
         <v>0</v>
@@ -6729,7 +6729,7 @@
     </row>
     <row r="737" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B737">
-        <v>8789</v>
+        <v>8792</v>
       </c>
       <c r="E737">
         <v>0</v>
@@ -6737,7 +6737,7 @@
     </row>
     <row r="738" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B738">
-        <v>8790</v>
+        <v>8793</v>
       </c>
       <c r="E738">
         <v>0</v>
@@ -6745,7 +6745,7 @@
     </row>
     <row r="739" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B739">
-        <v>8792</v>
+        <v>8794</v>
       </c>
       <c r="E739">
         <v>0</v>
@@ -6753,7 +6753,7 @@
     </row>
     <row r="740" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B740">
-        <v>8793</v>
+        <v>8795</v>
       </c>
       <c r="E740">
         <v>0</v>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="741" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B741">
-        <v>8794</v>
+        <v>8796</v>
       </c>
       <c r="E741">
         <v>0</v>
@@ -6769,7 +6769,7 @@
     </row>
     <row r="742" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B742">
-        <v>8795</v>
+        <v>8797</v>
       </c>
       <c r="E742">
         <v>0</v>
@@ -6777,7 +6777,7 @@
     </row>
     <row r="743" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B743">
-        <v>8796</v>
+        <v>8800</v>
       </c>
       <c r="E743">
         <v>0</v>
@@ -6785,7 +6785,7 @@
     </row>
     <row r="744" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B744">
-        <v>8797</v>
+        <v>8811</v>
       </c>
       <c r="E744">
         <v>0</v>
@@ -6793,7 +6793,7 @@
     </row>
     <row r="745" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B745">
-        <v>8800</v>
+        <v>8812</v>
       </c>
       <c r="E745">
         <v>0</v>
@@ -6801,7 +6801,7 @@
     </row>
     <row r="746" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B746">
-        <v>8811</v>
+        <v>8813</v>
       </c>
       <c r="E746">
         <v>0</v>
@@ -6809,7 +6809,7 @@
     </row>
     <row r="747" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B747">
-        <v>8812</v>
+        <v>8814</v>
       </c>
       <c r="E747">
         <v>0</v>
@@ -6817,7 +6817,7 @@
     </row>
     <row r="748" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B748">
-        <v>8813</v>
+        <v>8815</v>
       </c>
       <c r="E748">
         <v>0</v>
@@ -6825,7 +6825,7 @@
     </row>
     <row r="749" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B749">
-        <v>8814</v>
+        <v>8816</v>
       </c>
       <c r="E749">
         <v>0</v>
@@ -6833,7 +6833,7 @@
     </row>
     <row r="750" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B750">
-        <v>8815</v>
+        <v>8817</v>
       </c>
       <c r="E750">
         <v>0</v>
@@ -6841,7 +6841,7 @@
     </row>
     <row r="751" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B751">
-        <v>8816</v>
+        <v>8818</v>
       </c>
       <c r="E751">
         <v>0</v>
@@ -6849,7 +6849,7 @@
     </row>
     <row r="752" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B752">
-        <v>8817</v>
+        <v>8819</v>
       </c>
       <c r="E752">
         <v>0</v>
@@ -6857,7 +6857,7 @@
     </row>
     <row r="753" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B753">
-        <v>8818</v>
+        <v>8820</v>
       </c>
       <c r="E753">
         <v>0</v>
@@ -6865,7 +6865,7 @@
     </row>
     <row r="754" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B754">
-        <v>8819</v>
+        <v>8821</v>
       </c>
       <c r="E754">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     </row>
     <row r="755" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B755">
-        <v>8820</v>
+        <v>8822</v>
       </c>
       <c r="E755">
         <v>0</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="756" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B756">
-        <v>8821</v>
+        <v>8823</v>
       </c>
       <c r="E756">
         <v>0</v>
@@ -6889,7 +6889,7 @@
     </row>
     <row r="757" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B757">
-        <v>8822</v>
+        <v>8824</v>
       </c>
       <c r="E757">
         <v>0</v>
@@ -6897,7 +6897,7 @@
     </row>
     <row r="758" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B758">
-        <v>8823</v>
+        <v>8825</v>
       </c>
       <c r="E758">
         <v>0</v>
@@ -6905,7 +6905,7 @@
     </row>
     <row r="759" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B759">
-        <v>8824</v>
+        <v>8826</v>
       </c>
       <c r="E759">
         <v>0</v>
@@ -6913,7 +6913,7 @@
     </row>
     <row r="760" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B760">
-        <v>8825</v>
+        <v>8827</v>
       </c>
       <c r="E760">
         <v>0</v>
@@ -6921,7 +6921,7 @@
     </row>
     <row r="761" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B761">
-        <v>8826</v>
+        <v>8828</v>
       </c>
       <c r="E761">
         <v>0</v>
@@ -6929,7 +6929,7 @@
     </row>
     <row r="762" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B762">
-        <v>8827</v>
+        <v>8829</v>
       </c>
       <c r="E762">
         <v>0</v>
@@ -6937,7 +6937,7 @@
     </row>
     <row r="763" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B763">
-        <v>8828</v>
+        <v>8830</v>
       </c>
       <c r="E763">
         <v>0</v>
@@ -6945,7 +6945,7 @@
     </row>
     <row r="764" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B764">
-        <v>8829</v>
+        <v>8831</v>
       </c>
       <c r="E764">
         <v>0</v>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="765" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B765">
-        <v>8830</v>
+        <v>8832</v>
       </c>
       <c r="E765">
         <v>0</v>
@@ -6961,7 +6961,7 @@
     </row>
     <row r="766" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B766">
-        <v>8831</v>
+        <v>8833</v>
       </c>
       <c r="E766">
         <v>0</v>
@@ -6969,7 +6969,7 @@
     </row>
     <row r="767" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B767">
-        <v>8832</v>
+        <v>8834</v>
       </c>
       <c r="E767">
         <v>0</v>
@@ -6977,7 +6977,7 @@
     </row>
     <row r="768" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B768">
-        <v>8833</v>
+        <v>8835</v>
       </c>
       <c r="E768">
         <v>0</v>
@@ -6985,7 +6985,7 @@
     </row>
     <row r="769" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B769">
-        <v>8834</v>
+        <v>8836</v>
       </c>
       <c r="E769">
         <v>0</v>
@@ -6993,7 +6993,7 @@
     </row>
     <row r="770" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B770">
-        <v>8835</v>
+        <v>8837</v>
       </c>
       <c r="E770">
         <v>0</v>
@@ -7001,7 +7001,7 @@
     </row>
     <row r="771" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B771">
-        <v>8836</v>
+        <v>8838</v>
       </c>
       <c r="E771">
         <v>0</v>
@@ -7009,7 +7009,7 @@
     </row>
     <row r="772" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B772">
-        <v>8837</v>
+        <v>8839</v>
       </c>
       <c r="E772">
         <v>0</v>
@@ -7017,7 +7017,7 @@
     </row>
     <row r="773" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B773">
-        <v>8838</v>
+        <v>8840</v>
       </c>
       <c r="E773">
         <v>0</v>
@@ -7025,7 +7025,7 @@
     </row>
     <row r="774" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B774">
-        <v>8839</v>
+        <v>8841</v>
       </c>
       <c r="E774">
         <v>0</v>
@@ -7033,7 +7033,7 @@
     </row>
     <row r="775" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B775">
-        <v>8840</v>
+        <v>8842</v>
       </c>
       <c r="E775">
         <v>0</v>
@@ -7041,7 +7041,7 @@
     </row>
     <row r="776" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B776">
-        <v>8841</v>
+        <v>8843</v>
       </c>
       <c r="E776">
         <v>0</v>
@@ -7049,7 +7049,7 @@
     </row>
     <row r="777" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B777">
-        <v>8842</v>
+        <v>8844</v>
       </c>
       <c r="E777">
         <v>0</v>
@@ -7057,7 +7057,7 @@
     </row>
     <row r="778" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B778">
-        <v>8843</v>
+        <v>8845</v>
       </c>
       <c r="E778">
         <v>0</v>
@@ -7065,7 +7065,7 @@
     </row>
     <row r="779" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B779">
-        <v>8844</v>
+        <v>8846</v>
       </c>
       <c r="E779">
         <v>0</v>
@@ -7073,7 +7073,7 @@
     </row>
     <row r="780" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B780">
-        <v>8845</v>
+        <v>8857</v>
       </c>
       <c r="E780">
         <v>0</v>
@@ -7081,7 +7081,7 @@
     </row>
     <row r="781" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B781">
-        <v>8846</v>
+        <v>8858</v>
       </c>
       <c r="E781">
         <v>0</v>
@@ -7089,7 +7089,7 @@
     </row>
     <row r="782" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B782">
-        <v>8857</v>
+        <v>8859</v>
       </c>
       <c r="E782">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     </row>
     <row r="783" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B783">
-        <v>8858</v>
+        <v>8860</v>
       </c>
       <c r="E783">
         <v>0</v>
@@ -7105,7 +7105,7 @@
     </row>
     <row r="784" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B784">
-        <v>8859</v>
+        <v>8861</v>
       </c>
       <c r="E784">
         <v>0</v>
@@ -7113,7 +7113,7 @@
     </row>
     <row r="785" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B785">
-        <v>8860</v>
+        <v>8862</v>
       </c>
       <c r="E785">
         <v>0</v>
@@ -7121,7 +7121,7 @@
     </row>
     <row r="786" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B786">
-        <v>8861</v>
+        <v>8863</v>
       </c>
       <c r="E786">
         <v>0</v>
@@ -7129,7 +7129,7 @@
     </row>
     <row r="787" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B787">
-        <v>8862</v>
+        <v>8864</v>
       </c>
       <c r="E787">
         <v>0</v>
@@ -7137,7 +7137,7 @@
     </row>
     <row r="788" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B788">
-        <v>8863</v>
+        <v>8865</v>
       </c>
       <c r="E788">
         <v>0</v>
@@ -7145,7 +7145,7 @@
     </row>
     <row r="789" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B789">
-        <v>8864</v>
+        <v>8866</v>
       </c>
       <c r="E789">
         <v>0</v>
@@ -7153,7 +7153,7 @@
     </row>
     <row r="790" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B790">
-        <v>8865</v>
+        <v>8867</v>
       </c>
       <c r="E790">
         <v>0</v>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="791" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B791">
-        <v>8866</v>
+        <v>8868</v>
       </c>
       <c r="E791">
         <v>0</v>
@@ -7169,7 +7169,7 @@
     </row>
     <row r="792" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B792">
-        <v>8867</v>
+        <v>8870</v>
       </c>
       <c r="E792">
         <v>0</v>
@@ -7177,7 +7177,7 @@
     </row>
     <row r="793" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B793">
-        <v>8868</v>
+        <v>8871</v>
       </c>
       <c r="E793">
         <v>0</v>
@@ -7185,7 +7185,7 @@
     </row>
     <row r="794" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B794">
-        <v>8870</v>
+        <v>8872</v>
       </c>
       <c r="E794">
         <v>0</v>
@@ -7193,7 +7193,7 @@
     </row>
     <row r="795" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B795">
-        <v>8871</v>
+        <v>8873</v>
       </c>
       <c r="E795">
         <v>0</v>
@@ -7201,7 +7201,7 @@
     </row>
     <row r="796" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B796">
-        <v>8872</v>
+        <v>8874</v>
       </c>
       <c r="E796">
         <v>0</v>
@@ -7209,7 +7209,7 @@
     </row>
     <row r="797" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B797">
-        <v>8873</v>
+        <v>8875</v>
       </c>
       <c r="E797">
         <v>0</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="798" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B798">
-        <v>8874</v>
+        <v>8876</v>
       </c>
       <c r="E798">
         <v>0</v>
@@ -7225,7 +7225,7 @@
     </row>
     <row r="799" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B799">
-        <v>8875</v>
+        <v>8877</v>
       </c>
       <c r="E799">
         <v>0</v>
@@ -7233,7 +7233,7 @@
     </row>
     <row r="800" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B800">
-        <v>8876</v>
+        <v>8878</v>
       </c>
       <c r="E800">
         <v>0</v>
@@ -7241,7 +7241,7 @@
     </row>
     <row r="801" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B801">
-        <v>8877</v>
+        <v>8879</v>
       </c>
       <c r="E801">
         <v>0</v>
@@ -7249,7 +7249,7 @@
     </row>
     <row r="802" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B802">
-        <v>8878</v>
+        <v>8880</v>
       </c>
       <c r="E802">
         <v>0</v>
@@ -7257,7 +7257,7 @@
     </row>
     <row r="803" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B803">
-        <v>8879</v>
+        <v>8881</v>
       </c>
       <c r="E803">
         <v>0</v>
@@ -7265,7 +7265,7 @@
     </row>
     <row r="804" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B804">
-        <v>8880</v>
+        <v>8882</v>
       </c>
       <c r="E804">
         <v>0</v>
@@ -7273,7 +7273,7 @@
     </row>
     <row r="805" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B805">
-        <v>8881</v>
+        <v>8883</v>
       </c>
       <c r="E805">
         <v>0</v>
@@ -7281,7 +7281,7 @@
     </row>
     <row r="806" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B806">
-        <v>8882</v>
+        <v>8899</v>
       </c>
       <c r="E806">
         <v>0</v>
@@ -7289,7 +7289,7 @@
     </row>
     <row r="807" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B807">
-        <v>8883</v>
+        <v>8900</v>
       </c>
       <c r="E807">
         <v>0</v>
@@ -7297,7 +7297,7 @@
     </row>
     <row r="808" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B808">
-        <v>8899</v>
+        <v>8901</v>
       </c>
       <c r="E808">
         <v>0</v>
@@ -7305,7 +7305,7 @@
     </row>
     <row r="809" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B809">
-        <v>8900</v>
+        <v>8902</v>
       </c>
       <c r="E809">
         <v>0</v>
@@ -7313,7 +7313,7 @@
     </row>
     <row r="810" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B810">
-        <v>8901</v>
+        <v>8903</v>
       </c>
       <c r="E810">
         <v>0</v>
@@ -7321,7 +7321,7 @@
     </row>
     <row r="811" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B811">
-        <v>8902</v>
+        <v>8904</v>
       </c>
       <c r="E811">
         <v>0</v>
@@ -7329,7 +7329,7 @@
     </row>
     <row r="812" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B812">
-        <v>8903</v>
+        <v>8905</v>
       </c>
       <c r="E812">
         <v>0</v>
@@ -7337,7 +7337,7 @@
     </row>
     <row r="813" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B813">
-        <v>8904</v>
+        <v>8906</v>
       </c>
       <c r="E813">
         <v>0</v>
@@ -7345,7 +7345,7 @@
     </row>
     <row r="814" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B814">
-        <v>8905</v>
+        <v>8907</v>
       </c>
       <c r="E814">
         <v>0</v>
@@ -7353,7 +7353,7 @@
     </row>
     <row r="815" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B815">
-        <v>8906</v>
+        <v>8908</v>
       </c>
       <c r="E815">
         <v>0</v>
@@ -7361,7 +7361,7 @@
     </row>
     <row r="816" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B816">
-        <v>8907</v>
+        <v>8909</v>
       </c>
       <c r="E816">
         <v>0</v>
@@ -7369,7 +7369,7 @@
     </row>
     <row r="817" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B817">
-        <v>8908</v>
+        <v>8910</v>
       </c>
       <c r="E817">
         <v>0</v>
@@ -7377,7 +7377,7 @@
     </row>
     <row r="818" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B818">
-        <v>8909</v>
+        <v>8911</v>
       </c>
       <c r="E818">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="819" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B819">
-        <v>8910</v>
+        <v>8912</v>
       </c>
       <c r="E819">
         <v>0</v>
@@ -7393,7 +7393,7 @@
     </row>
     <row r="820" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B820">
-        <v>8911</v>
+        <v>8913</v>
       </c>
       <c r="E820">
         <v>0</v>
@@ -7401,7 +7401,7 @@
     </row>
     <row r="821" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B821">
-        <v>8912</v>
+        <v>8914</v>
       </c>
       <c r="E821">
         <v>0</v>
@@ -7409,7 +7409,7 @@
     </row>
     <row r="822" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B822">
-        <v>8913</v>
+        <v>8915</v>
       </c>
       <c r="E822">
         <v>0</v>
@@ -7417,7 +7417,7 @@
     </row>
     <row r="823" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B823">
-        <v>8914</v>
+        <v>8916</v>
       </c>
       <c r="E823">
         <v>0</v>
@@ -7425,7 +7425,7 @@
     </row>
     <row r="824" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B824">
-        <v>8915</v>
+        <v>8917</v>
       </c>
       <c r="E824">
         <v>0</v>
@@ -7433,7 +7433,7 @@
     </row>
     <row r="825" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B825">
-        <v>8916</v>
+        <v>8918</v>
       </c>
       <c r="E825">
         <v>0</v>
@@ -7441,7 +7441,7 @@
     </row>
     <row r="826" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B826">
-        <v>8917</v>
+        <v>8919</v>
       </c>
       <c r="E826">
         <v>0</v>
@@ -7449,7 +7449,7 @@
     </row>
     <row r="827" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B827">
-        <v>8918</v>
+        <v>8920</v>
       </c>
       <c r="E827">
         <v>0</v>
@@ -7457,7 +7457,7 @@
     </row>
     <row r="828" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B828">
-        <v>8919</v>
+        <v>8921</v>
       </c>
       <c r="E828">
         <v>0</v>
@@ -7465,7 +7465,7 @@
     </row>
     <row r="829" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B829">
-        <v>8920</v>
+        <v>8922</v>
       </c>
       <c r="E829">
         <v>0</v>
@@ -7473,7 +7473,7 @@
     </row>
     <row r="830" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B830">
-        <v>8921</v>
+        <v>8923</v>
       </c>
       <c r="E830">
         <v>0</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="831" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B831">
-        <v>8922</v>
+        <v>8924</v>
       </c>
       <c r="E831">
         <v>0</v>
@@ -7489,7 +7489,7 @@
     </row>
     <row r="832" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B832">
-        <v>8923</v>
+        <v>8925</v>
       </c>
       <c r="E832">
         <v>0</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="833" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B833">
-        <v>8924</v>
+        <v>8926</v>
       </c>
       <c r="E833">
         <v>0</v>
@@ -7505,7 +7505,7 @@
     </row>
     <row r="834" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B834">
-        <v>8925</v>
+        <v>8927</v>
       </c>
       <c r="E834">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     </row>
     <row r="835" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B835">
-        <v>8926</v>
+        <v>8928</v>
       </c>
       <c r="E835">
         <v>0</v>
@@ -7521,7 +7521,7 @@
     </row>
     <row r="836" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B836">
-        <v>8927</v>
+        <v>8929</v>
       </c>
       <c r="E836">
         <v>0</v>
@@ -7529,7 +7529,7 @@
     </row>
     <row r="837" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B837">
-        <v>8928</v>
+        <v>8930</v>
       </c>
       <c r="E837">
         <v>0</v>
@@ -7537,7 +7537,7 @@
     </row>
     <row r="838" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B838">
-        <v>8929</v>
+        <v>8931</v>
       </c>
       <c r="E838">
         <v>0</v>
@@ -7545,7 +7545,7 @@
     </row>
     <row r="839" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B839">
-        <v>8930</v>
+        <v>8932</v>
       </c>
       <c r="E839">
         <v>0</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="840" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B840">
-        <v>8931</v>
+        <v>8933</v>
       </c>
       <c r="E840">
         <v>0</v>
@@ -7561,7 +7561,7 @@
     </row>
     <row r="841" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B841">
-        <v>8932</v>
+        <v>8934</v>
       </c>
       <c r="E841">
         <v>0</v>
@@ -7569,7 +7569,7 @@
     </row>
     <row r="842" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B842">
-        <v>8933</v>
+        <v>8935</v>
       </c>
       <c r="E842">
         <v>0</v>
@@ -7577,7 +7577,7 @@
     </row>
     <row r="843" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B843">
-        <v>8934</v>
+        <v>8936</v>
       </c>
       <c r="E843">
         <v>0</v>
@@ -7585,7 +7585,7 @@
     </row>
     <row r="844" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B844">
-        <v>8935</v>
+        <v>8937</v>
       </c>
       <c r="E844">
         <v>0</v>
@@ -7593,7 +7593,7 @@
     </row>
     <row r="845" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B845">
-        <v>8936</v>
+        <v>8938</v>
       </c>
       <c r="E845">
         <v>0</v>
@@ -7601,7 +7601,7 @@
     </row>
     <row r="846" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B846">
-        <v>8937</v>
+        <v>8939</v>
       </c>
       <c r="E846">
         <v>0</v>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="847" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B847">
-        <v>8938</v>
+        <v>8940</v>
       </c>
       <c r="E847">
         <v>0</v>
@@ -7617,7 +7617,7 @@
     </row>
     <row r="848" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B848">
-        <v>8939</v>
+        <v>8941</v>
       </c>
       <c r="E848">
         <v>0</v>
@@ -7625,7 +7625,7 @@
     </row>
     <row r="849" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B849">
-        <v>8940</v>
+        <v>8942</v>
       </c>
       <c r="E849">
         <v>0</v>
@@ -7633,7 +7633,7 @@
     </row>
     <row r="850" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B850">
-        <v>8941</v>
+        <v>8943</v>
       </c>
       <c r="E850">
         <v>0</v>
@@ -7641,7 +7641,7 @@
     </row>
     <row r="851" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B851">
-        <v>8942</v>
+        <v>8944</v>
       </c>
       <c r="E851">
         <v>0</v>
@@ -7649,7 +7649,7 @@
     </row>
     <row r="852" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B852">
-        <v>8943</v>
+        <v>8945</v>
       </c>
       <c r="E852">
         <v>0</v>
@@ -7657,7 +7657,7 @@
     </row>
     <row r="853" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B853">
-        <v>8944</v>
+        <v>8946</v>
       </c>
       <c r="E853">
         <v>0</v>
@@ -7665,7 +7665,7 @@
     </row>
     <row r="854" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B854">
-        <v>8945</v>
+        <v>8947</v>
       </c>
       <c r="E854">
         <v>0</v>
@@ -7673,7 +7673,7 @@
     </row>
     <row r="855" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B855">
-        <v>8946</v>
+        <v>8948</v>
       </c>
       <c r="E855">
         <v>0</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="856" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B856">
-        <v>8947</v>
+        <v>8949</v>
       </c>
       <c r="E856">
         <v>0</v>
@@ -7689,7 +7689,7 @@
     </row>
     <row r="857" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B857">
-        <v>8948</v>
+        <v>8950</v>
       </c>
       <c r="E857">
         <v>0</v>
@@ -7697,7 +7697,7 @@
     </row>
     <row r="858" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B858">
-        <v>8949</v>
+        <v>8951</v>
       </c>
       <c r="E858">
         <v>0</v>
@@ -7705,7 +7705,7 @@
     </row>
     <row r="859" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B859">
-        <v>8950</v>
+        <v>8952</v>
       </c>
       <c r="E859">
         <v>0</v>
@@ -7713,7 +7713,7 @@
     </row>
     <row r="860" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B860">
-        <v>8951</v>
+        <v>8953</v>
       </c>
       <c r="E860">
         <v>0</v>
@@ -7721,7 +7721,7 @@
     </row>
     <row r="861" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B861">
-        <v>8952</v>
+        <v>8954</v>
       </c>
       <c r="E861">
         <v>0</v>
@@ -7729,7 +7729,7 @@
     </row>
     <row r="862" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B862">
-        <v>8953</v>
+        <v>8955</v>
       </c>
       <c r="E862">
         <v>0</v>
@@ -7737,7 +7737,7 @@
     </row>
     <row r="863" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B863">
-        <v>8954</v>
+        <v>8956</v>
       </c>
       <c r="E863">
         <v>0</v>
@@ -7745,7 +7745,7 @@
     </row>
     <row r="864" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B864">
-        <v>8955</v>
+        <v>8957</v>
       </c>
       <c r="E864">
         <v>0</v>
@@ -7753,7 +7753,7 @@
     </row>
     <row r="865" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B865">
-        <v>8956</v>
+        <v>8958</v>
       </c>
       <c r="E865">
         <v>0</v>
@@ -7761,7 +7761,7 @@
     </row>
     <row r="866" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B866">
-        <v>8957</v>
+        <v>8959</v>
       </c>
       <c r="E866">
         <v>0</v>
@@ -7769,7 +7769,7 @@
     </row>
     <row r="867" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B867">
-        <v>8958</v>
+        <v>8960</v>
       </c>
       <c r="E867">
         <v>0</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="868" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B868">
-        <v>8959</v>
+        <v>8961</v>
       </c>
       <c r="E868">
         <v>0</v>
@@ -7785,7 +7785,7 @@
     </row>
     <row r="869" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B869">
-        <v>8960</v>
+        <v>8962</v>
       </c>
       <c r="E869">
         <v>0</v>
@@ -7793,7 +7793,7 @@
     </row>
     <row r="870" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B870">
-        <v>8961</v>
+        <v>8963</v>
       </c>
       <c r="E870">
         <v>0</v>
@@ -7801,7 +7801,7 @@
     </row>
     <row r="871" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B871">
-        <v>8962</v>
+        <v>8964</v>
       </c>
       <c r="E871">
         <v>0</v>
@@ -7809,7 +7809,7 @@
     </row>
     <row r="872" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B872">
-        <v>8963</v>
+        <v>8965</v>
       </c>
       <c r="E872">
         <v>0</v>
@@ -7817,7 +7817,7 @@
     </row>
     <row r="873" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B873">
-        <v>8964</v>
+        <v>8966</v>
       </c>
       <c r="E873">
         <v>0</v>
@@ -7825,7 +7825,7 @@
     </row>
     <row r="874" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B874">
-        <v>8965</v>
+        <v>8967</v>
       </c>
       <c r="E874">
         <v>0</v>
@@ -7833,7 +7833,7 @@
     </row>
     <row r="875" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B875">
-        <v>8966</v>
+        <v>8968</v>
       </c>
       <c r="E875">
         <v>0</v>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="876" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B876">
-        <v>8967</v>
+        <v>8969</v>
       </c>
       <c r="E876">
         <v>0</v>
@@ -7849,7 +7849,7 @@
     </row>
     <row r="877" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B877">
-        <v>8968</v>
+        <v>8970</v>
       </c>
       <c r="E877">
         <v>0</v>
@@ -7857,7 +7857,7 @@
     </row>
     <row r="878" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B878">
-        <v>8969</v>
+        <v>8971</v>
       </c>
       <c r="E878">
         <v>0</v>
@@ -7865,7 +7865,7 @@
     </row>
     <row r="879" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B879">
-        <v>8970</v>
+        <v>8972</v>
       </c>
       <c r="E879">
         <v>0</v>
@@ -7873,7 +7873,7 @@
     </row>
     <row r="880" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B880">
-        <v>8971</v>
+        <v>8973</v>
       </c>
       <c r="E880">
         <v>0</v>
@@ -7881,7 +7881,7 @@
     </row>
     <row r="881" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B881">
-        <v>8972</v>
+        <v>8974</v>
       </c>
       <c r="E881">
         <v>0</v>
@@ -7889,7 +7889,7 @@
     </row>
     <row r="882" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B882">
-        <v>8973</v>
+        <v>8975</v>
       </c>
       <c r="E882">
         <v>0</v>
@@ -7897,7 +7897,7 @@
     </row>
     <row r="883" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B883">
-        <v>8974</v>
+        <v>8976</v>
       </c>
       <c r="E883">
         <v>0</v>
@@ -7905,7 +7905,7 @@
     </row>
     <row r="884" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B884">
-        <v>8975</v>
+        <v>8977</v>
       </c>
       <c r="E884">
         <v>0</v>
@@ -7913,7 +7913,7 @@
     </row>
     <row r="885" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B885">
-        <v>8976</v>
+        <v>8978</v>
       </c>
       <c r="E885">
         <v>0</v>
@@ -7921,7 +7921,7 @@
     </row>
     <row r="886" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B886">
-        <v>8977</v>
+        <v>8979</v>
       </c>
       <c r="E886">
         <v>0</v>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="887" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B887">
-        <v>8978</v>
+        <v>8980</v>
       </c>
       <c r="E887">
         <v>0</v>
@@ -7937,7 +7937,7 @@
     </row>
     <row r="888" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B888">
-        <v>8979</v>
+        <v>8981</v>
       </c>
       <c r="E888">
         <v>0</v>
@@ -7945,7 +7945,7 @@
     </row>
     <row r="889" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B889">
-        <v>8980</v>
+        <v>8982</v>
       </c>
       <c r="E889">
         <v>0</v>
@@ -7953,7 +7953,7 @@
     </row>
     <row r="890" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B890">
-        <v>8981</v>
+        <v>8983</v>
       </c>
       <c r="E890">
         <v>0</v>
@@ -7961,7 +7961,7 @@
     </row>
     <row r="891" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B891">
-        <v>8982</v>
+        <v>8984</v>
       </c>
       <c r="E891">
         <v>0</v>
@@ -7969,7 +7969,7 @@
     </row>
     <row r="892" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B892">
-        <v>8983</v>
+        <v>8985</v>
       </c>
       <c r="E892">
         <v>0</v>
@@ -7977,7 +7977,7 @@
     </row>
     <row r="893" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B893">
-        <v>8984</v>
+        <v>8986</v>
       </c>
       <c r="E893">
         <v>0</v>
@@ -7985,7 +7985,7 @@
     </row>
     <row r="894" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B894">
-        <v>8985</v>
+        <v>8987</v>
       </c>
       <c r="E894">
         <v>0</v>
@@ -7993,7 +7993,7 @@
     </row>
     <row r="895" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B895">
-        <v>8986</v>
+        <v>8988</v>
       </c>
       <c r="E895">
         <v>0</v>
@@ -8001,7 +8001,7 @@
     </row>
     <row r="896" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B896">
-        <v>8987</v>
+        <v>8989</v>
       </c>
       <c r="E896">
         <v>0</v>
@@ -8009,7 +8009,7 @@
     </row>
     <row r="897" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B897">
-        <v>8988</v>
+        <v>8990</v>
       </c>
       <c r="E897">
         <v>0</v>
@@ -8017,7 +8017,7 @@
     </row>
     <row r="898" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B898">
-        <v>8989</v>
+        <v>8991</v>
       </c>
       <c r="E898">
         <v>0</v>
@@ -8025,7 +8025,7 @@
     </row>
     <row r="899" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B899">
-        <v>8990</v>
+        <v>8992</v>
       </c>
       <c r="E899">
         <v>0</v>
@@ -8033,7 +8033,7 @@
     </row>
     <row r="900" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B900">
-        <v>8991</v>
+        <v>8993</v>
       </c>
       <c r="E900">
         <v>0</v>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="901" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B901">
-        <v>8992</v>
+        <v>8994</v>
       </c>
       <c r="E901">
         <v>0</v>
@@ -8049,7 +8049,7 @@
     </row>
     <row r="902" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B902">
-        <v>8993</v>
+        <v>8995</v>
       </c>
       <c r="E902">
         <v>0</v>
@@ -8057,7 +8057,7 @@
     </row>
     <row r="903" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B903">
-        <v>8994</v>
+        <v>8996</v>
       </c>
       <c r="E903">
         <v>0</v>
@@ -8065,7 +8065,7 @@
     </row>
     <row r="904" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B904">
-        <v>8995</v>
+        <v>8997</v>
       </c>
       <c r="E904">
         <v>0</v>
@@ -8073,7 +8073,7 @@
     </row>
     <row r="905" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B905">
-        <v>8996</v>
+        <v>8998</v>
       </c>
       <c r="E905">
         <v>0</v>
@@ -8081,7 +8081,7 @@
     </row>
     <row r="906" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B906">
-        <v>8997</v>
+        <v>8999</v>
       </c>
       <c r="E906">
         <v>0</v>
@@ -8089,7 +8089,7 @@
     </row>
     <row r="907" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B907">
-        <v>8998</v>
+        <v>9000</v>
       </c>
       <c r="E907">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="908" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B908">
-        <v>8999</v>
+        <v>9001</v>
       </c>
       <c r="E908">
         <v>0</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="909" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B909">
-        <v>9000</v>
+        <v>9002</v>
       </c>
       <c r="E909">
         <v>0</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="910" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B910">
-        <v>9001</v>
+        <v>9003</v>
       </c>
       <c r="E910">
         <v>0</v>
@@ -8121,7 +8121,7 @@
     </row>
     <row r="911" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B911">
-        <v>9002</v>
+        <v>9004</v>
       </c>
       <c r="E911">
         <v>0</v>
@@ -8129,7 +8129,7 @@
     </row>
     <row r="912" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B912">
-        <v>9003</v>
+        <v>9005</v>
       </c>
       <c r="E912">
         <v>0</v>
@@ -8137,7 +8137,7 @@
     </row>
     <row r="913" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B913">
-        <v>9004</v>
+        <v>9006</v>
       </c>
       <c r="E913">
         <v>0</v>
@@ -8145,7 +8145,7 @@
     </row>
     <row r="914" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B914">
-        <v>9005</v>
+        <v>9007</v>
       </c>
       <c r="E914">
         <v>0</v>
@@ -8153,7 +8153,7 @@
     </row>
     <row r="915" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B915">
-        <v>9006</v>
+        <v>9008</v>
       </c>
       <c r="E915">
         <v>0</v>
@@ -8161,7 +8161,7 @@
     </row>
     <row r="916" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B916">
-        <v>9007</v>
+        <v>9009</v>
       </c>
       <c r="E916">
         <v>0</v>
@@ -8169,7 +8169,7 @@
     </row>
     <row r="917" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B917">
-        <v>9008</v>
+        <v>9010</v>
       </c>
       <c r="E917">
         <v>0</v>
@@ -8177,7 +8177,7 @@
     </row>
     <row r="918" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B918">
-        <v>9009</v>
+        <v>9011</v>
       </c>
       <c r="E918">
         <v>0</v>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="919" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B919">
-        <v>9010</v>
+        <v>9012</v>
       </c>
       <c r="E919">
         <v>0</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="920" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B920">
-        <v>9011</v>
+        <v>9013</v>
       </c>
       <c r="E920">
         <v>0</v>
@@ -8201,7 +8201,7 @@
     </row>
     <row r="921" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B921">
-        <v>9012</v>
+        <v>9014</v>
       </c>
       <c r="E921">
         <v>0</v>
@@ -8209,7 +8209,7 @@
     </row>
     <row r="922" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B922">
-        <v>9013</v>
+        <v>9015</v>
       </c>
       <c r="E922">
         <v>0</v>
@@ -8217,7 +8217,7 @@
     </row>
     <row r="923" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B923">
-        <v>9014</v>
+        <v>9016</v>
       </c>
       <c r="E923">
         <v>0</v>
@@ -8225,7 +8225,7 @@
     </row>
     <row r="924" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B924">
-        <v>9015</v>
+        <v>9017</v>
       </c>
       <c r="E924">
         <v>0</v>
@@ -8233,7 +8233,7 @@
     </row>
     <row r="925" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B925">
-        <v>9016</v>
+        <v>9018</v>
       </c>
       <c r="E925">
         <v>0</v>
@@ -8241,7 +8241,7 @@
     </row>
     <row r="926" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B926">
-        <v>9017</v>
+        <v>9019</v>
       </c>
       <c r="E926">
         <v>0</v>
@@ -8249,7 +8249,7 @@
     </row>
     <row r="927" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B927">
-        <v>9018</v>
+        <v>9020</v>
       </c>
       <c r="E927">
         <v>0</v>
@@ -8257,7 +8257,7 @@
     </row>
     <row r="928" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B928">
-        <v>9019</v>
+        <v>9021</v>
       </c>
       <c r="E928">
         <v>0</v>
@@ -8265,7 +8265,7 @@
     </row>
     <row r="929" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B929">
-        <v>9020</v>
+        <v>9022</v>
       </c>
       <c r="E929">
         <v>0</v>
@@ -8273,7 +8273,7 @@
     </row>
     <row r="930" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B930">
-        <v>9021</v>
+        <v>9023</v>
       </c>
       <c r="E930">
         <v>0</v>
@@ -8281,7 +8281,7 @@
     </row>
     <row r="931" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B931">
-        <v>9022</v>
+        <v>9024</v>
       </c>
       <c r="E931">
         <v>0</v>
@@ -8289,7 +8289,7 @@
     </row>
     <row r="932" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B932">
-        <v>9023</v>
+        <v>9025</v>
       </c>
       <c r="E932">
         <v>0</v>
@@ -8297,7 +8297,7 @@
     </row>
     <row r="933" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B933">
-        <v>9024</v>
+        <v>9026</v>
       </c>
       <c r="E933">
         <v>0</v>
@@ -8305,7 +8305,7 @@
     </row>
     <row r="934" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B934">
-        <v>9025</v>
+        <v>9027</v>
       </c>
       <c r="E934">
         <v>0</v>
@@ -8313,7 +8313,7 @@
     </row>
     <row r="935" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B935">
-        <v>9026</v>
+        <v>9028</v>
       </c>
       <c r="E935">
         <v>0</v>
@@ -8321,7 +8321,7 @@
     </row>
     <row r="936" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B936">
-        <v>9027</v>
+        <v>9029</v>
       </c>
       <c r="E936">
         <v>0</v>
@@ -8329,7 +8329,7 @@
     </row>
     <row r="937" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B937">
-        <v>9028</v>
+        <v>9030</v>
       </c>
       <c r="E937">
         <v>0</v>
@@ -8337,7 +8337,7 @@
     </row>
     <row r="938" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B938">
-        <v>9029</v>
+        <v>9031</v>
       </c>
       <c r="E938">
         <v>0</v>
@@ -8345,7 +8345,7 @@
     </row>
     <row r="939" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B939">
-        <v>9030</v>
+        <v>9032</v>
       </c>
       <c r="E939">
         <v>0</v>
@@ -8353,7 +8353,7 @@
     </row>
     <row r="940" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B940">
-        <v>9031</v>
+        <v>9033</v>
       </c>
       <c r="E940">
         <v>0</v>
@@ -8361,7 +8361,7 @@
     </row>
     <row r="941" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B941">
-        <v>9032</v>
+        <v>9034</v>
       </c>
       <c r="E941">
         <v>0</v>
@@ -8369,7 +8369,7 @@
     </row>
     <row r="942" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B942">
-        <v>9033</v>
+        <v>9036</v>
       </c>
       <c r="E942">
         <v>0</v>
@@ -8377,7 +8377,7 @@
     </row>
     <row r="943" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B943">
-        <v>9034</v>
+        <v>9037</v>
       </c>
       <c r="E943">
         <v>0</v>
@@ -8385,7 +8385,7 @@
     </row>
     <row r="944" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B944">
-        <v>9036</v>
+        <v>9038</v>
       </c>
       <c r="E944">
         <v>0</v>
@@ -8393,7 +8393,7 @@
     </row>
     <row r="945" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B945">
-        <v>9037</v>
+        <v>9039</v>
       </c>
       <c r="E945">
         <v>0</v>
@@ -8401,7 +8401,7 @@
     </row>
     <row r="946" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B946">
-        <v>9038</v>
+        <v>9040</v>
       </c>
       <c r="E946">
         <v>0</v>
@@ -8409,7 +8409,7 @@
     </row>
     <row r="947" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B947">
-        <v>9039</v>
+        <v>9041</v>
       </c>
       <c r="E947">
         <v>0</v>
@@ -8417,7 +8417,7 @@
     </row>
     <row r="948" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B948">
-        <v>9040</v>
+        <v>9042</v>
       </c>
       <c r="E948">
         <v>0</v>
@@ -8425,7 +8425,7 @@
     </row>
     <row r="949" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B949">
-        <v>9041</v>
+        <v>9043</v>
       </c>
       <c r="E949">
         <v>0</v>
@@ -8433,7 +8433,7 @@
     </row>
     <row r="950" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B950">
-        <v>9042</v>
+        <v>9044</v>
       </c>
       <c r="E950">
         <v>0</v>
@@ -8441,7 +8441,7 @@
     </row>
     <row r="951" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B951">
-        <v>9043</v>
+        <v>9045</v>
       </c>
       <c r="E951">
         <v>0</v>
@@ -8449,7 +8449,7 @@
     </row>
     <row r="952" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B952">
-        <v>9044</v>
+        <v>9046</v>
       </c>
       <c r="E952">
         <v>0</v>
@@ -8457,7 +8457,7 @@
     </row>
     <row r="953" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B953">
-        <v>9045</v>
+        <v>9047</v>
       </c>
       <c r="E953">
         <v>0</v>
@@ -8465,7 +8465,7 @@
     </row>
     <row r="954" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B954">
-        <v>9046</v>
+        <v>9048</v>
       </c>
       <c r="E954">
         <v>0</v>
@@ -8473,7 +8473,7 @@
     </row>
     <row r="955" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B955">
-        <v>9047</v>
+        <v>9049</v>
       </c>
       <c r="E955">
         <v>0</v>
@@ -8481,7 +8481,7 @@
     </row>
     <row r="956" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B956">
-        <v>9048</v>
+        <v>9050</v>
       </c>
       <c r="E956">
         <v>0</v>
@@ -8489,7 +8489,7 @@
     </row>
     <row r="957" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B957">
-        <v>9049</v>
+        <v>9051</v>
       </c>
       <c r="E957">
         <v>0</v>
@@ -8497,7 +8497,7 @@
     </row>
     <row r="958" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B958">
-        <v>9050</v>
+        <v>9052</v>
       </c>
       <c r="E958">
         <v>0</v>
@@ -8505,7 +8505,7 @@
     </row>
     <row r="959" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B959">
-        <v>9051</v>
+        <v>9053</v>
       </c>
       <c r="E959">
         <v>0</v>
@@ -8513,7 +8513,7 @@
     </row>
     <row r="960" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B960">
-        <v>9052</v>
+        <v>9054</v>
       </c>
       <c r="E960">
         <v>0</v>
@@ -8521,7 +8521,7 @@
     </row>
     <row r="961" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B961">
-        <v>9053</v>
+        <v>9055</v>
       </c>
       <c r="E961">
         <v>0</v>
@@ -8529,7 +8529,7 @@
     </row>
     <row r="962" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B962">
-        <v>9054</v>
+        <v>9056</v>
       </c>
       <c r="E962">
         <v>0</v>
@@ -8537,7 +8537,7 @@
     </row>
     <row r="963" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B963">
-        <v>9055</v>
+        <v>9057</v>
       </c>
       <c r="E963">
         <v>0</v>
@@ -8545,7 +8545,7 @@
     </row>
     <row r="964" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B964">
-        <v>9056</v>
+        <v>9058</v>
       </c>
       <c r="E964">
         <v>0</v>
@@ -8553,7 +8553,7 @@
     </row>
     <row r="965" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B965">
-        <v>9057</v>
+        <v>9059</v>
       </c>
       <c r="E965">
         <v>0</v>
@@ -8561,7 +8561,7 @@
     </row>
     <row r="966" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B966">
-        <v>9058</v>
+        <v>9060</v>
       </c>
       <c r="E966">
         <v>0</v>
@@ -8569,7 +8569,7 @@
     </row>
     <row r="967" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B967">
-        <v>9059</v>
+        <v>9061</v>
       </c>
       <c r="E967">
         <v>0</v>
@@ -8577,7 +8577,7 @@
     </row>
     <row r="968" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B968">
-        <v>9060</v>
+        <v>9068</v>
       </c>
       <c r="E968">
         <v>0</v>
@@ -8585,7 +8585,7 @@
     </row>
     <row r="969" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B969">
-        <v>9061</v>
+        <v>9069</v>
       </c>
       <c r="E969">
         <v>0</v>
@@ -8593,7 +8593,7 @@
     </row>
     <row r="970" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B970">
-        <v>9068</v>
+        <v>9070</v>
       </c>
       <c r="E970">
         <v>0</v>
@@ -8601,7 +8601,7 @@
     </row>
     <row r="971" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B971">
-        <v>9069</v>
+        <v>9071</v>
       </c>
       <c r="E971">
         <v>0</v>
@@ -8609,7 +8609,7 @@
     </row>
     <row r="972" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B972">
-        <v>9070</v>
+        <v>9072</v>
       </c>
       <c r="E972">
         <v>0</v>
@@ -8617,7 +8617,7 @@
     </row>
     <row r="973" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B973">
-        <v>9071</v>
+        <v>9073</v>
       </c>
       <c r="E973">
         <v>0</v>
@@ -8625,7 +8625,7 @@
     </row>
     <row r="974" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B974">
-        <v>9072</v>
+        <v>9074</v>
       </c>
       <c r="E974">
         <v>0</v>
@@ -8633,7 +8633,7 @@
     </row>
     <row r="975" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B975">
-        <v>9073</v>
+        <v>9077</v>
       </c>
       <c r="E975">
         <v>0</v>
@@ -8641,7 +8641,7 @@
     </row>
     <row r="976" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B976">
-        <v>9074</v>
+        <v>9075</v>
       </c>
       <c r="E976">
         <v>0</v>
@@ -8649,7 +8649,7 @@
     </row>
     <row r="977" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B977">
-        <v>9077</v>
+        <v>9078</v>
       </c>
       <c r="E977">
         <v>0</v>
@@ -8657,7 +8657,7 @@
     </row>
     <row r="978" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B978">
-        <v>9075</v>
+        <v>9079</v>
       </c>
       <c r="E978">
         <v>0</v>
@@ -8665,7 +8665,7 @@
     </row>
     <row r="979" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B979">
-        <v>9078</v>
+        <v>9080</v>
       </c>
       <c r="E979">
         <v>0</v>
@@ -8673,7 +8673,7 @@
     </row>
     <row r="980" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B980">
-        <v>9079</v>
+        <v>9081</v>
       </c>
       <c r="E980">
         <v>0</v>
@@ -8681,7 +8681,7 @@
     </row>
     <row r="981" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B981">
-        <v>9080</v>
+        <v>9082</v>
       </c>
       <c r="E981">
         <v>0</v>
@@ -8689,7 +8689,7 @@
     </row>
     <row r="982" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B982">
-        <v>9081</v>
+        <v>9083</v>
       </c>
       <c r="E982">
         <v>0</v>
@@ -8697,7 +8697,7 @@
     </row>
     <row r="983" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B983">
-        <v>9082</v>
+        <v>9084</v>
       </c>
       <c r="E983">
         <v>0</v>
@@ -8705,7 +8705,7 @@
     </row>
     <row r="984" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B984">
-        <v>9083</v>
+        <v>9085</v>
       </c>
       <c r="E984">
         <v>0</v>
@@ -8713,7 +8713,7 @@
     </row>
     <row r="985" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B985">
-        <v>9084</v>
+        <v>9086</v>
       </c>
       <c r="E985">
         <v>0</v>
@@ -8721,7 +8721,7 @@
     </row>
     <row r="986" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B986">
-        <v>9085</v>
+        <v>9087</v>
       </c>
       <c r="E986">
         <v>0</v>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="987" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B987">
-        <v>9086</v>
+        <v>9088</v>
       </c>
       <c r="E987">
         <v>0</v>
@@ -8737,7 +8737,7 @@
     </row>
     <row r="988" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B988">
-        <v>9087</v>
+        <v>9089</v>
       </c>
       <c r="E988">
         <v>0</v>
@@ -8745,7 +8745,7 @@
     </row>
     <row r="989" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B989">
-        <v>9088</v>
+        <v>9090</v>
       </c>
       <c r="E989">
         <v>0</v>
@@ -8753,7 +8753,7 @@
     </row>
     <row r="990" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B990">
-        <v>9089</v>
+        <v>9091</v>
       </c>
       <c r="E990">
         <v>0</v>
@@ -8761,7 +8761,7 @@
     </row>
     <row r="991" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B991">
-        <v>9090</v>
+        <v>9092</v>
       </c>
       <c r="E991">
         <v>0</v>
@@ -8769,7 +8769,7 @@
     </row>
     <row r="992" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B992">
-        <v>9091</v>
+        <v>9093</v>
       </c>
       <c r="E992">
         <v>0</v>
@@ -8777,7 +8777,7 @@
     </row>
     <row r="993" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B993">
-        <v>9092</v>
+        <v>9095</v>
       </c>
       <c r="E993">
         <v>0</v>
@@ -8785,7 +8785,7 @@
     </row>
     <row r="994" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B994">
-        <v>9093</v>
+        <v>9096</v>
       </c>
       <c r="E994">
         <v>0</v>
@@ -8793,7 +8793,7 @@
     </row>
     <row r="995" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B995">
-        <v>9095</v>
+        <v>9097</v>
       </c>
       <c r="E995">
         <v>0</v>
@@ -8801,7 +8801,7 @@
     </row>
     <row r="996" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B996">
-        <v>9096</v>
+        <v>9098</v>
       </c>
       <c r="E996">
         <v>0</v>
@@ -8809,7 +8809,7 @@
     </row>
     <row r="997" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B997">
-        <v>9097</v>
+        <v>9099</v>
       </c>
       <c r="E997">
         <v>0</v>
@@ -8817,7 +8817,7 @@
     </row>
     <row r="998" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B998">
-        <v>9098</v>
+        <v>9100</v>
       </c>
       <c r="E998">
         <v>0</v>
@@ -8825,7 +8825,7 @@
     </row>
     <row r="999" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B999">
-        <v>9099</v>
+        <v>9101</v>
       </c>
       <c r="E999">
         <v>0</v>
@@ -8833,7 +8833,7 @@
     </row>
     <row r="1000" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1000">
-        <v>9100</v>
+        <v>9102</v>
       </c>
       <c r="E1000">
         <v>0</v>
@@ -8841,7 +8841,7 @@
     </row>
     <row r="1001" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1001">
-        <v>9101</v>
+        <v>9103</v>
       </c>
       <c r="E1001">
         <v>0</v>
@@ -8849,7 +8849,7 @@
     </row>
     <row r="1002" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1002">
-        <v>9102</v>
+        <v>9104</v>
       </c>
       <c r="E1002">
         <v>0</v>
@@ -8857,7 +8857,7 @@
     </row>
     <row r="1003" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1003">
-        <v>9103</v>
+        <v>9105</v>
       </c>
       <c r="E1003">
         <v>0</v>
@@ -8865,7 +8865,7 @@
     </row>
     <row r="1004" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1004">
-        <v>9104</v>
+        <v>9106</v>
       </c>
       <c r="E1004">
         <v>0</v>
@@ -8873,7 +8873,7 @@
     </row>
     <row r="1005" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1005">
-        <v>9105</v>
+        <v>9107</v>
       </c>
       <c r="E1005">
         <v>0</v>
@@ -8881,7 +8881,7 @@
     </row>
     <row r="1006" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1006">
-        <v>9106</v>
+        <v>9108</v>
       </c>
       <c r="E1006">
         <v>0</v>
@@ -8889,7 +8889,7 @@
     </row>
     <row r="1007" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1007">
-        <v>9107</v>
+        <v>9109</v>
       </c>
       <c r="E1007">
         <v>0</v>
@@ -8897,7 +8897,7 @@
     </row>
     <row r="1008" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1008">
-        <v>9108</v>
+        <v>9110</v>
       </c>
       <c r="E1008">
         <v>0</v>
@@ -8905,7 +8905,7 @@
     </row>
     <row r="1009" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1009">
-        <v>9109</v>
+        <v>9111</v>
       </c>
       <c r="E1009">
         <v>0</v>
@@ -8913,7 +8913,7 @@
     </row>
     <row r="1010" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1010">
-        <v>9110</v>
+        <v>9112</v>
       </c>
       <c r="E1010">
         <v>0</v>
@@ -8921,7 +8921,7 @@
     </row>
     <row r="1011" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1011">
-        <v>9111</v>
+        <v>9113</v>
       </c>
       <c r="E1011">
         <v>0</v>
@@ -8929,7 +8929,7 @@
     </row>
     <row r="1012" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1012">
-        <v>9112</v>
+        <v>9114</v>
       </c>
       <c r="E1012">
         <v>0</v>
@@ -8937,7 +8937,7 @@
     </row>
     <row r="1013" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1013">
-        <v>9113</v>
+        <v>9115</v>
       </c>
       <c r="E1013">
         <v>0</v>
@@ -8945,7 +8945,7 @@
     </row>
     <row r="1014" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1014">
-        <v>9114</v>
+        <v>9116</v>
       </c>
       <c r="E1014">
         <v>0</v>
@@ -8953,7 +8953,7 @@
     </row>
     <row r="1015" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1015">
-        <v>9115</v>
+        <v>9117</v>
       </c>
       <c r="E1015">
         <v>0</v>
@@ -8961,7 +8961,7 @@
     </row>
     <row r="1016" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1016">
-        <v>9116</v>
+        <v>9118</v>
       </c>
       <c r="E1016">
         <v>0</v>
@@ -8969,7 +8969,7 @@
     </row>
     <row r="1017" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1017">
-        <v>9117</v>
+        <v>9121</v>
       </c>
       <c r="E1017">
         <v>0</v>
@@ -8977,7 +8977,7 @@
     </row>
     <row r="1018" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1018">
-        <v>9118</v>
+        <v>9122</v>
       </c>
       <c r="E1018">
         <v>0</v>
@@ -8985,7 +8985,7 @@
     </row>
     <row r="1019" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1019">
-        <v>9121</v>
+        <v>9123</v>
       </c>
       <c r="E1019">
         <v>0</v>
@@ -8993,7 +8993,7 @@
     </row>
     <row r="1020" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1020">
-        <v>9122</v>
+        <v>9124</v>
       </c>
       <c r="E1020">
         <v>0</v>
@@ -9001,7 +9001,7 @@
     </row>
     <row r="1021" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1021">
-        <v>9123</v>
+        <v>9125</v>
       </c>
       <c r="E1021">
         <v>0</v>
@@ -9009,7 +9009,7 @@
     </row>
     <row r="1022" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1022">
-        <v>9124</v>
+        <v>9126</v>
       </c>
       <c r="E1022">
         <v>0</v>
@@ -9017,7 +9017,7 @@
     </row>
     <row r="1023" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1023">
-        <v>9125</v>
+        <v>9127</v>
       </c>
       <c r="E1023">
         <v>0</v>
@@ -9025,7 +9025,7 @@
     </row>
     <row r="1024" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1024">
-        <v>9126</v>
+        <v>9128</v>
       </c>
       <c r="E1024">
         <v>0</v>
@@ -9033,7 +9033,7 @@
     </row>
     <row r="1025" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1025">
-        <v>9127</v>
+        <v>9131</v>
       </c>
       <c r="E1025">
         <v>0</v>
@@ -9041,7 +9041,7 @@
     </row>
     <row r="1026" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1026">
-        <v>9128</v>
+        <v>9136</v>
       </c>
       <c r="E1026">
         <v>0</v>
@@ -9049,7 +9049,7 @@
     </row>
     <row r="1027" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1027">
-        <v>9131</v>
+        <v>9137</v>
       </c>
       <c r="E1027">
         <v>0</v>
@@ -9057,7 +9057,7 @@
     </row>
     <row r="1028" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1028">
-        <v>9136</v>
+        <v>9141</v>
       </c>
       <c r="E1028">
         <v>0</v>
@@ -9065,7 +9065,7 @@
     </row>
     <row r="1029" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1029">
-        <v>9137</v>
+        <v>9142</v>
       </c>
       <c r="E1029">
         <v>0</v>
@@ -9073,7 +9073,7 @@
     </row>
     <row r="1030" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1030">
-        <v>9141</v>
+        <v>9153</v>
       </c>
       <c r="E1030">
         <v>0</v>
@@ -9081,24 +9081,18 @@
     </row>
     <row r="1031" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1031">
-        <v>9142</v>
+        <v>9165</v>
       </c>
       <c r="E1031">
         <v>0</v>
       </c>
     </row>
     <row r="1032" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B1032">
-        <v>9153</v>
-      </c>
       <c r="E1032">
         <v>0</v>
       </c>
     </row>
     <row r="1033" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B1033">
-        <v>9165</v>
-      </c>
       <c r="E1033">
         <v>0</v>
       </c>
@@ -9124,18 +9118,24 @@
       </c>
     </row>
     <row r="1038" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1038">
+        <v>9263</v>
+      </c>
       <c r="E1038">
         <v>0</v>
       </c>
     </row>
     <row r="1039" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1039">
+        <v>9264</v>
+      </c>
       <c r="E1039">
         <v>0</v>
       </c>
     </row>
     <row r="1040" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1040">
-        <v>9263</v>
+        <v>9265</v>
       </c>
       <c r="E1040">
         <v>0</v>
@@ -9143,7 +9143,7 @@
     </row>
     <row r="1041" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1041">
-        <v>9264</v>
+        <v>9266</v>
       </c>
       <c r="E1041">
         <v>0</v>
@@ -9151,36 +9151,36 @@
     </row>
     <row r="1042" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1042">
-        <v>9265</v>
+        <v>9268</v>
       </c>
       <c r="E1042">
         <v>0</v>
       </c>
     </row>
     <row r="1043" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B1043">
-        <v>9266</v>
-      </c>
       <c r="E1043">
         <v>0</v>
       </c>
     </row>
     <row r="1044" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1044">
-        <v>9268</v>
+        <v>9322</v>
       </c>
       <c r="E1044">
         <v>0</v>
       </c>
     </row>
     <row r="1045" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1045">
+        <v>9323</v>
+      </c>
       <c r="E1045">
         <v>0</v>
       </c>
     </row>
     <row r="1046" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1046">
-        <v>9322</v>
+        <v>9324</v>
       </c>
       <c r="E1046">
         <v>0</v>
@@ -9188,7 +9188,7 @@
     </row>
     <row r="1047" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1047">
-        <v>9323</v>
+        <v>9325</v>
       </c>
       <c r="E1047">
         <v>0</v>
@@ -9196,7 +9196,7 @@
     </row>
     <row r="1048" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1048">
-        <v>9324</v>
+        <v>9326</v>
       </c>
       <c r="E1048">
         <v>0</v>
@@ -9204,7 +9204,7 @@
     </row>
     <row r="1049" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1049">
-        <v>9325</v>
+        <v>9327</v>
       </c>
       <c r="E1049">
         <v>0</v>
@@ -9212,7 +9212,7 @@
     </row>
     <row r="1050" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1050">
-        <v>9326</v>
+        <v>9330</v>
       </c>
       <c r="E1050">
         <v>0</v>
@@ -9220,7 +9220,7 @@
     </row>
     <row r="1051" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1051">
-        <v>9327</v>
+        <v>9331</v>
       </c>
       <c r="E1051">
         <v>0</v>
@@ -9228,7 +9228,7 @@
     </row>
     <row r="1052" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1052">
-        <v>9330</v>
+        <v>9332</v>
       </c>
       <c r="E1052">
         <v>0</v>
@@ -9236,7 +9236,7 @@
     </row>
     <row r="1053" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1053">
-        <v>9331</v>
+        <v>9338</v>
       </c>
       <c r="E1053">
         <v>0</v>
@@ -9244,23 +9244,23 @@
     </row>
     <row r="1054" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1054">
-        <v>9332</v>
+        <v>12752</v>
       </c>
       <c r="E1054">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1055" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1055">
-        <v>9338</v>
+        <v>12753</v>
       </c>
       <c r="E1055">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1056" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1056">
-        <v>12752</v>
+        <v>12772</v>
       </c>
       <c r="E1056">
         <v>2</v>
@@ -9268,7 +9268,7 @@
     </row>
     <row r="1057" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1057">
-        <v>12753</v>
+        <v>12775</v>
       </c>
       <c r="E1057">
         <v>2</v>
@@ -9276,7 +9276,7 @@
     </row>
     <row r="1058" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1058">
-        <v>12772</v>
+        <v>12776</v>
       </c>
       <c r="E1058">
         <v>2</v>
@@ -9284,7 +9284,7 @@
     </row>
     <row r="1059" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1059">
-        <v>12775</v>
+        <v>12777</v>
       </c>
       <c r="E1059">
         <v>2</v>
@@ -9292,7 +9292,7 @@
     </row>
     <row r="1060" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1060">
-        <v>12776</v>
+        <v>12782</v>
       </c>
       <c r="E1060">
         <v>2</v>
@@ -9300,7 +9300,7 @@
     </row>
     <row r="1061" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1061">
-        <v>12777</v>
+        <v>12783</v>
       </c>
       <c r="E1061">
         <v>2</v>
@@ -9308,7 +9308,7 @@
     </row>
     <row r="1062" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1062">
-        <v>12782</v>
+        <v>12784</v>
       </c>
       <c r="E1062">
         <v>2</v>
@@ -9316,7 +9316,7 @@
     </row>
     <row r="1063" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1063">
-        <v>12783</v>
+        <v>12808</v>
       </c>
       <c r="E1063">
         <v>2</v>
@@ -9324,7 +9324,7 @@
     </row>
     <row r="1064" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1064">
-        <v>12784</v>
+        <v>12811</v>
       </c>
       <c r="E1064">
         <v>2</v>
@@ -9332,7 +9332,7 @@
     </row>
     <row r="1065" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1065">
-        <v>12808</v>
+        <v>13081</v>
       </c>
       <c r="E1065">
         <v>2</v>
@@ -9340,7 +9340,7 @@
     </row>
     <row r="1066" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1066">
-        <v>12811</v>
+        <v>13082</v>
       </c>
       <c r="E1066">
         <v>2</v>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="1067" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1067">
-        <v>13081</v>
+        <v>13405</v>
       </c>
       <c r="E1067">
         <v>2</v>
@@ -9356,7 +9356,7 @@
     </row>
     <row r="1068" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1068">
-        <v>13082</v>
+        <v>13408</v>
       </c>
       <c r="E1068">
         <v>2</v>
@@ -9364,7 +9364,7 @@
     </row>
     <row r="1069" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1069">
-        <v>13405</v>
+        <v>13409</v>
       </c>
       <c r="E1069">
         <v>2</v>
@@ -9372,7 +9372,7 @@
     </row>
     <row r="1070" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1070">
-        <v>13408</v>
+        <v>13410</v>
       </c>
       <c r="E1070">
         <v>2</v>
@@ -9380,7 +9380,7 @@
     </row>
     <row r="1071" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1071">
-        <v>13409</v>
+        <v>13411</v>
       </c>
       <c r="E1071">
         <v>2</v>
@@ -9388,7 +9388,7 @@
     </row>
     <row r="1072" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1072">
-        <v>13410</v>
+        <v>13430</v>
       </c>
       <c r="E1072">
         <v>2</v>
@@ -9396,7 +9396,7 @@
     </row>
     <row r="1073" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1073">
-        <v>13411</v>
+        <v>13432</v>
       </c>
       <c r="E1073">
         <v>2</v>
@@ -9404,7 +9404,7 @@
     </row>
     <row r="1074" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1074">
-        <v>13430</v>
+        <v>13483</v>
       </c>
       <c r="E1074">
         <v>2</v>
@@ -9412,7 +9412,7 @@
     </row>
     <row r="1075" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1075">
-        <v>13432</v>
+        <v>13484</v>
       </c>
       <c r="E1075">
         <v>2</v>
@@ -9420,7 +9420,7 @@
     </row>
     <row r="1076" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1076">
-        <v>13483</v>
+        <v>13932</v>
       </c>
       <c r="E1076">
         <v>2</v>
@@ -9428,7 +9428,7 @@
     </row>
     <row r="1077" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1077">
-        <v>13484</v>
+        <v>14022</v>
       </c>
       <c r="E1077">
         <v>2</v>
@@ -9436,7 +9436,7 @@
     </row>
     <row r="1078" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1078">
-        <v>13932</v>
+        <v>14036</v>
       </c>
       <c r="E1078">
         <v>2</v>
@@ -9444,7 +9444,7 @@
     </row>
     <row r="1079" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1079">
-        <v>14022</v>
+        <v>14081</v>
       </c>
       <c r="E1079">
         <v>2</v>
@@ -9452,7 +9452,7 @@
     </row>
     <row r="1080" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1080">
-        <v>14036</v>
+        <v>14082</v>
       </c>
       <c r="E1080">
         <v>2</v>
@@ -9460,7 +9460,7 @@
     </row>
     <row r="1081" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1081">
-        <v>14081</v>
+        <v>14111</v>
       </c>
       <c r="E1081">
         <v>2</v>
@@ -9468,7 +9468,7 @@
     </row>
     <row r="1082" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1082">
-        <v>14082</v>
+        <v>14179</v>
       </c>
       <c r="E1082">
         <v>2</v>
@@ -9476,7 +9476,7 @@
     </row>
     <row r="1083" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1083">
-        <v>14111</v>
+        <v>14180</v>
       </c>
       <c r="E1083">
         <v>2</v>
@@ -9484,7 +9484,7 @@
     </row>
     <row r="1084" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1084">
-        <v>14179</v>
+        <v>14182</v>
       </c>
       <c r="E1084">
         <v>2</v>
@@ -9492,7 +9492,7 @@
     </row>
     <row r="1085" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1085">
-        <v>14180</v>
+        <v>14183</v>
       </c>
       <c r="E1085">
         <v>2</v>
@@ -9500,7 +9500,7 @@
     </row>
     <row r="1086" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1086">
-        <v>14182</v>
+        <v>24611</v>
       </c>
       <c r="E1086">
         <v>2</v>
@@ -9508,7 +9508,7 @@
     </row>
     <row r="1087" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1087">
-        <v>14183</v>
+        <v>24615</v>
       </c>
       <c r="E1087">
         <v>2</v>
@@ -9516,135 +9516,141 @@
     </row>
     <row r="1088" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1088">
-        <v>24611</v>
+        <v>8371</v>
       </c>
       <c r="E1088">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1089" spans="2:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1089">
-        <v>24615</v>
+        <v>8494</v>
       </c>
       <c r="E1089">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1090" spans="2:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1090">
-        <v>8371</v>
+        <v>8511</v>
       </c>
       <c r="E1090">
         <v>0</v>
       </c>
     </row>
-    <row r="1091" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1091" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1091">
-        <v>8494</v>
+        <v>8513</v>
       </c>
       <c r="E1091">
         <v>0</v>
       </c>
     </row>
-    <row r="1092" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1092" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1092">
-        <v>8511</v>
+        <v>8700</v>
       </c>
       <c r="E1092">
         <v>0</v>
       </c>
     </row>
-    <row r="1093" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1093" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1093">
-        <v>8513</v>
+        <v>8802</v>
       </c>
       <c r="E1093">
         <v>0</v>
       </c>
     </row>
-    <row r="1094" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B1094">
-        <v>8700</v>
-      </c>
+    <row r="1094" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E1094">
         <v>0</v>
       </c>
     </row>
-    <row r="1095" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1095" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1095">
-        <v>8802</v>
+        <v>9267</v>
       </c>
       <c r="E1095">
         <v>0</v>
       </c>
     </row>
-    <row r="1096" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1096" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1096">
+        <v>9813</v>
+      </c>
       <c r="E1096">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1097" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1097">
-        <v>9267</v>
+        <v>11525</v>
       </c>
       <c r="E1097">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1098" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1098">
-        <v>9813</v>
+        <v>11523</v>
       </c>
       <c r="E1098">
         <v>1</v>
       </c>
     </row>
-    <row r="1099" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1099" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1099">
-        <v>11525</v>
+        <v>11488</v>
       </c>
       <c r="E1099">
         <v>1</v>
       </c>
     </row>
-    <row r="1100" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1100">
-        <v>11523</v>
+        <v>11482</v>
       </c>
       <c r="E1100">
         <v>1</v>
       </c>
     </row>
-    <row r="1101" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1101">
-        <v>11488</v>
+        <v>11481</v>
       </c>
       <c r="E1101">
         <v>1</v>
       </c>
     </row>
-    <row r="1102" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1102">
-        <v>11482</v>
+        <v>11492</v>
       </c>
       <c r="E1102">
         <v>1</v>
       </c>
     </row>
-    <row r="1103" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="1103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1103" t="s">
+        <v>88</v>
+      </c>
       <c r="B1103">
-        <v>11481</v>
-      </c>
-      <c r="E1103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1104" spans="2:5" x14ac:dyDescent="0.25">
+        <v>10958</v>
+      </c>
+      <c r="D1103" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1104" t="s">
+        <v>88</v>
+      </c>
       <c r="B1104">
-        <v>11492</v>
-      </c>
-      <c r="E1104">
-        <v>1</v>
+        <v>10806</v>
+      </c>
+      <c r="D1104" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="1105" spans="1:5" x14ac:dyDescent="0.25">
@@ -9652,32 +9658,32 @@
         <v>88</v>
       </c>
       <c r="B1105">
-        <v>10958</v>
+        <v>10191</v>
       </c>
       <c r="D1105" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B1106">
-        <v>10806</v>
+        <v>10191</v>
       </c>
       <c r="D1106" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B1107">
-        <v>10191</v>
+        <v>9541</v>
       </c>
       <c r="D1107" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1108" spans="1:5" x14ac:dyDescent="0.25">
@@ -9685,10 +9691,10 @@
         <v>86</v>
       </c>
       <c r="B1108">
-        <v>10191</v>
+        <v>9542</v>
       </c>
       <c r="D1108" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="1109" spans="1:5" x14ac:dyDescent="0.25">
@@ -9696,21 +9702,18 @@
         <v>86</v>
       </c>
       <c r="B1109">
-        <v>9541</v>
+        <v>1003</v>
       </c>
       <c r="D1109" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1110" t="s">
-        <v>86</v>
-      </c>
       <c r="B1110">
-        <v>9542</v>
-      </c>
-      <c r="D1110" t="s">
-        <v>116</v>
+        <v>1238</v>
+      </c>
+      <c r="E1110">
+        <v>0</v>
       </c>
     </row>
     <row r="1111" spans="1:5" x14ac:dyDescent="0.25">
@@ -9718,18 +9721,21 @@
         <v>86</v>
       </c>
       <c r="B1111">
-        <v>1003</v>
+        <v>663</v>
       </c>
       <c r="D1111" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1112" t="s">
+        <v>88</v>
+      </c>
       <c r="B1112">
-        <v>1238</v>
-      </c>
-      <c r="E1112">
-        <v>0</v>
+        <v>488</v>
+      </c>
+      <c r="D1112" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="1113" spans="1:5" x14ac:dyDescent="0.25">
@@ -9737,67 +9743,64 @@
         <v>86</v>
       </c>
       <c r="B1113">
-        <v>663</v>
+        <v>488</v>
       </c>
       <c r="D1113" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B1114">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D1114" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1115" t="s">
-        <v>86</v>
-      </c>
       <c r="B1115">
-        <v>488</v>
-      </c>
-      <c r="D1115" t="s">
-        <v>122</v>
+        <v>9621</v>
+      </c>
+      <c r="E1115">
+        <v>1</v>
       </c>
     </row>
     <row r="1116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1116" t="s">
-        <v>86</v>
-      </c>
       <c r="B1116">
-        <v>489</v>
-      </c>
-      <c r="D1116" t="s">
-        <v>121</v>
+        <v>9812</v>
+      </c>
+      <c r="E1116">
+        <v>1</v>
       </c>
     </row>
     <row r="1117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1117">
-        <v>9621</v>
+        <v>9180</v>
       </c>
       <c r="E1117">
         <v>1</v>
       </c>
     </row>
     <row r="1118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1118" t="s">
+        <v>88</v>
+      </c>
       <c r="B1118">
-        <v>9812</v>
-      </c>
-      <c r="E1118">
-        <v>1</v>
+        <v>7728</v>
+      </c>
+      <c r="D1118" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="1119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1119">
-        <v>9180</v>
-      </c>
-      <c r="E1119">
-        <v>1</v>
+      <c r="A1119" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1119" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="1120" spans="1:5" x14ac:dyDescent="0.25">
@@ -9805,39 +9808,20 @@
         <v>88</v>
       </c>
       <c r="B1120">
-        <v>7728</v>
+        <v>4501</v>
       </c>
       <c r="D1120" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
-        <v>125</v>
+        <v>88</v>
+      </c>
+      <c r="B1121">
+        <v>4022</v>
       </c>
       <c r="D1121" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="1122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1122" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1122">
-        <v>4501</v>
-      </c>
-      <c r="D1122" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="1123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1123" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1123">
-        <v>4022</v>
-      </c>
-      <c r="D1123" t="s">
         <v>128</v>
       </c>
     </row>
@@ -9845,7 +9829,7 @@
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B486 B488:B1108 B1110:B1113">
+  <conditionalFormatting sqref="B486:B1106 B2:B484 B1108:B1111">
     <cfRule type="duplicateValues" dxfId="5" priority="96"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59:B113 B17:B57">
@@ -9857,7 +9841,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D60A7C4-82C4-4AAF-A00A-127D625F91A3}">
-  <dimension ref="A1:H691"/>
+  <dimension ref="A1:H708"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13752,7 +13736,7 @@
         <v>14470</v>
       </c>
       <c r="E458" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
@@ -14572,7 +14556,7 @@
         <v>0</v>
       </c>
       <c r="E559" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
@@ -15610,7 +15594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689">
         <v>15607</v>
       </c>
@@ -15618,7 +15602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690">
         <v>15871</v>
       </c>
@@ -15626,11 +15610,147 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691">
         <v>15580</v>
       </c>
       <c r="B691">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A692">
+        <v>15864</v>
+      </c>
+      <c r="B692">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A693">
+        <v>14354</v>
+      </c>
+      <c r="E693" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A694">
+        <v>9467</v>
+      </c>
+      <c r="E694" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A695">
+        <v>1855</v>
+      </c>
+      <c r="E695" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A696">
+        <v>12126</v>
+      </c>
+      <c r="E696" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A697">
+        <v>16284</v>
+      </c>
+      <c r="B697">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A698">
+        <v>16135</v>
+      </c>
+      <c r="B698">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A699">
+        <v>16134</v>
+      </c>
+      <c r="B699">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A700">
+        <v>16212</v>
+      </c>
+      <c r="B700">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A701">
+        <v>16161</v>
+      </c>
+      <c r="B701">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A702">
+        <v>16115</v>
+      </c>
+      <c r="B702">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A703">
+        <v>16114</v>
+      </c>
+      <c r="B703">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A704">
+        <v>16132</v>
+      </c>
+      <c r="B704">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A705">
+        <v>16131</v>
+      </c>
+      <c r="B705">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A706">
+        <v>16283</v>
+      </c>
+      <c r="B706">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A707">
+        <v>17069</v>
+      </c>
+      <c r="B707">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A708">
+        <v>17072</v>
+      </c>
+      <c r="B708">
         <v>0</v>
       </c>
     </row>

--- a/corrections/corrections.xlsx
+++ b/corrections/corrections.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Desktop\wow_vo_webui\corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8D6992-44B1-4E87-B5BF-E3E57FFAE444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF6A1CE-99B8-4F11-8281-D8418C429E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="quest" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="136">
   <si>
     <t>source</t>
   </si>
@@ -463,6 +463,34 @@
   <si>
     <t>The flight is aware of your work in the Searing Gorge. Show it to me. The molt; imbecile!</t>
   </si>
+  <si>
+    <t>Come closer, mon; Don't be 'fraid, Ven'jashi not gonna hurt you.
+Us Darkspears be mortal enemies of the Amani just like you. Their boss Zul'Marosh is evil troll. He give me the bad poison and leave me in this cage to die.
+I not scared of dyin', mon. I seen death in the eye an' I laugh at her.
+I cannot die in peace yet, mon. Not 'til Zul'Marosh be dead too. You find him 'cross the lake in Zeb'Watha. I hold this poison off 'til you bring me his big ugly head, mon. Only then I die peacefully.</t>
+  </si>
+  <si>
+    <t>Ya, mon;  Zul'Marosh had this comin'.  He burn down Ven'jashi's village;  I kill many Amani before they put me in this cage.  I hide something in the sand, my gift for you now.
+Ah... ah, the poison; it spread now, mon.  Time to rest.</t>
+  </si>
+  <si>
+    <t>Prying open the lid of the crate, you find an assortment of carefully-packed objects. On the top of the crate lies a bundle of maps, yellowing with age, that appear to depict Silverpine Forest and other parts of western Lordaeron.
+Underneath the maps is a mysterious-looking magical pendant.</t>
+  </si>
+  <si>
+    <t>velen</t>
+  </si>
+  <si>
+    <t>So excited I am; Three little cages for three little elves! But what shall we do with our lovely tree-hugging friends? Why, let's give them a taste of... what do they call it; forest magic! I'll need a good mess of Stone-talon sap; From those horrid felines, bring me some twilight whiskers. This calls for plenty of courser eyes, of course; can never have enough eyes. Oh, and lest we forget, a precious scale from a fey dragon.
+Hurry to Stone-talon Peak, &lt;name&gt;, so I can brew some forest magic!</t>
+  </si>
+  <si>
+    <t>felorc_male</t>
+  </si>
+  <si>
+    <t>In my travels across this world I have made several interesting discoveries. For instance, did you know that with the proper amount of encouragement one can extract all the truths that a man dares hide? As luck would have it, I happen to have some encouragement on hand.
+These are my persuaders; Equip them and take to the field, death knight; Apply the pointy ends to the soldiers of New Avalon; Discover the truth about this "Crimson Dawn."</t>
+  </si>
 </sst>
 </file>
 
@@ -497,8 +525,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -850,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56545B79-22C0-4057-A076-1E697524330B}">
-  <dimension ref="A1:F1121"/>
+  <dimension ref="A1:F1104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4964,68 +4993,114 @@
         <v>1</v>
       </c>
     </row>
+    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>88</v>
+      </c>
+      <c r="B504">
+        <v>831</v>
+      </c>
+      <c r="E504">
+        <v>0</v>
+      </c>
+    </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>86</v>
+      </c>
       <c r="B505">
+        <v>831</v>
+      </c>
+      <c r="E505">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B506">
         <v>10592</v>
       </c>
-      <c r="E505">
+      <c r="E506">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B507">
+        <v>2963</v>
+      </c>
+      <c r="E507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B508">
+        <v>1155</v>
+      </c>
+      <c r="E508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B509">
+        <v>11222</v>
+      </c>
+      <c r="E509">
         <v>1</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B510">
-        <v>2963</v>
+        <v>11142</v>
       </c>
       <c r="E510">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B511">
-        <v>1155</v>
+        <v>11141</v>
       </c>
       <c r="E511">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B512">
-        <v>11222</v>
+        <v>11223</v>
       </c>
       <c r="E512">
         <v>1</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>86</v>
+      </c>
       <c r="B513">
-        <v>11142</v>
+        <v>1393</v>
       </c>
       <c r="E513">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B514">
-        <v>11141</v>
+        <v>5924</v>
       </c>
       <c r="E514">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B515">
-        <v>11223</v>
+        <v>5927</v>
       </c>
       <c r="E515">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A516" t="s">
-        <v>86</v>
-      </c>
       <c r="B516">
-        <v>1393</v>
+        <v>7810</v>
       </c>
       <c r="E516">
         <v>0</v>
@@ -5033,7 +5108,7 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B517">
-        <v>5924</v>
+        <v>8183</v>
       </c>
       <c r="E517">
         <v>0</v>
@@ -5041,45 +5116,63 @@
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B518">
-        <v>5927</v>
+        <v>8311</v>
       </c>
       <c r="E518">
         <v>0</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B519">
+        <v>8312</v>
+      </c>
       <c r="E519">
         <v>0</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B520">
+        <v>8367</v>
+      </c>
       <c r="E520">
         <v>0</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B521">
+        <v>8446</v>
+      </c>
       <c r="E521">
         <v>0</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B522">
+        <v>8495</v>
+      </c>
       <c r="E522">
         <v>0</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B523">
+        <v>8493</v>
+      </c>
       <c r="E523">
         <v>0</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B524">
+        <v>8492</v>
+      </c>
       <c r="E524">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B525">
-        <v>7810</v>
+        <v>8498</v>
       </c>
       <c r="E525">
         <v>0</v>
@@ -5087,7 +5180,7 @@
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B526">
-        <v>8183</v>
+        <v>8497</v>
       </c>
       <c r="E526">
         <v>0</v>
@@ -5095,7 +5188,7 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B527">
-        <v>8311</v>
+        <v>8496</v>
       </c>
       <c r="E527">
         <v>0</v>
@@ -5103,33 +5196,47 @@
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B528">
-        <v>8312</v>
+        <v>8499</v>
       </c>
       <c r="E528">
         <v>0</v>
       </c>
     </row>
     <row r="529" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B529">
+        <v>8500</v>
+      </c>
       <c r="E529">
         <v>0</v>
       </c>
     </row>
     <row r="530" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B530">
+        <v>8501</v>
+      </c>
       <c r="E530">
         <v>0</v>
       </c>
     </row>
     <row r="531" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B531">
-        <v>8367</v>
+        <v>8502</v>
       </c>
       <c r="E531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B532">
+        <v>8503</v>
+      </c>
+      <c r="E532">
         <v>0</v>
       </c>
     </row>
     <row r="533" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B533">
-        <v>8446</v>
+        <v>8504</v>
       </c>
       <c r="E533">
         <v>0</v>
@@ -5137,15 +5244,23 @@
     </row>
     <row r="534" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B534">
-        <v>8495</v>
+        <v>8505</v>
       </c>
       <c r="E534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B535">
+        <v>8506</v>
+      </c>
+      <c r="E535">
         <v>0</v>
       </c>
     </row>
     <row r="536" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B536">
-        <v>8493</v>
+        <v>8507</v>
       </c>
       <c r="E536">
         <v>0</v>
@@ -5153,7 +5268,7 @@
     </row>
     <row r="537" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B537">
-        <v>8492</v>
+        <v>8508</v>
       </c>
       <c r="E537">
         <v>0</v>
@@ -5161,7 +5276,7 @@
     </row>
     <row r="538" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B538">
-        <v>8498</v>
+        <v>8509</v>
       </c>
       <c r="E538">
         <v>0</v>
@@ -5169,7 +5284,7 @@
     </row>
     <row r="539" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B539">
-        <v>8497</v>
+        <v>8510</v>
       </c>
       <c r="E539">
         <v>0</v>
@@ -5177,7 +5292,7 @@
     </row>
     <row r="540" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B540">
-        <v>8496</v>
+        <v>8512</v>
       </c>
       <c r="E540">
         <v>0</v>
@@ -5185,7 +5300,7 @@
     </row>
     <row r="541" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B541">
-        <v>8499</v>
+        <v>8514</v>
       </c>
       <c r="E541">
         <v>0</v>
@@ -5193,7 +5308,7 @@
     </row>
     <row r="542" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B542">
-        <v>8500</v>
+        <v>8515</v>
       </c>
       <c r="E542">
         <v>0</v>
@@ -5201,7 +5316,7 @@
     </row>
     <row r="543" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B543">
-        <v>8501</v>
+        <v>8516</v>
       </c>
       <c r="E543">
         <v>0</v>
@@ -5209,7 +5324,7 @@
     </row>
     <row r="544" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B544">
-        <v>8502</v>
+        <v>8517</v>
       </c>
       <c r="E544">
         <v>0</v>
@@ -5217,7 +5332,7 @@
     </row>
     <row r="545" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B545">
-        <v>8503</v>
+        <v>8518</v>
       </c>
       <c r="E545">
         <v>0</v>
@@ -5225,7 +5340,7 @@
     </row>
     <row r="546" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B546">
-        <v>8504</v>
+        <v>8519</v>
       </c>
       <c r="E546">
         <v>0</v>
@@ -5233,7 +5348,7 @@
     </row>
     <row r="547" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B547">
-        <v>8505</v>
+        <v>8520</v>
       </c>
       <c r="E547">
         <v>0</v>
@@ -5241,7 +5356,7 @@
     </row>
     <row r="548" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B548">
-        <v>8506</v>
+        <v>8521</v>
       </c>
       <c r="E548">
         <v>0</v>
@@ -5249,7 +5364,7 @@
     </row>
     <row r="549" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B549">
-        <v>8507</v>
+        <v>8522</v>
       </c>
       <c r="E549">
         <v>0</v>
@@ -5257,7 +5372,7 @@
     </row>
     <row r="550" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B550">
-        <v>8508</v>
+        <v>8523</v>
       </c>
       <c r="E550">
         <v>0</v>
@@ -5265,7 +5380,7 @@
     </row>
     <row r="551" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B551">
-        <v>8509</v>
+        <v>8524</v>
       </c>
       <c r="E551">
         <v>0</v>
@@ -5273,23 +5388,39 @@
     </row>
     <row r="552" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B552">
-        <v>8510</v>
+        <v>8525</v>
       </c>
       <c r="E552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B553">
+        <v>8526</v>
+      </c>
+      <c r="E553">
         <v>0</v>
       </c>
     </row>
     <row r="554" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B554">
-        <v>8512</v>
+        <v>8527</v>
       </c>
       <c r="E554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="555" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B555">
+        <v>8528</v>
+      </c>
+      <c r="E555">
         <v>0</v>
       </c>
     </row>
     <row r="556" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B556">
-        <v>8514</v>
+        <v>8529</v>
       </c>
       <c r="E556">
         <v>0</v>
@@ -5297,7 +5428,7 @@
     </row>
     <row r="557" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B557">
-        <v>8515</v>
+        <v>8530</v>
       </c>
       <c r="E557">
         <v>0</v>
@@ -5305,7 +5436,7 @@
     </row>
     <row r="558" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B558">
-        <v>8516</v>
+        <v>8531</v>
       </c>
       <c r="E558">
         <v>0</v>
@@ -5313,7 +5444,7 @@
     </row>
     <row r="559" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B559">
-        <v>8517</v>
+        <v>8532</v>
       </c>
       <c r="E559">
         <v>0</v>
@@ -5321,7 +5452,7 @@
     </row>
     <row r="560" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B560">
-        <v>8518</v>
+        <v>8533</v>
       </c>
       <c r="E560">
         <v>0</v>
@@ -5329,7 +5460,7 @@
     </row>
     <row r="561" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B561">
-        <v>8519</v>
+        <v>8537</v>
       </c>
       <c r="E561">
         <v>0</v>
@@ -5337,7 +5468,7 @@
     </row>
     <row r="562" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B562">
-        <v>8520</v>
+        <v>8535</v>
       </c>
       <c r="E562">
         <v>0</v>
@@ -5345,7 +5476,7 @@
     </row>
     <row r="563" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B563">
-        <v>8521</v>
+        <v>8538</v>
       </c>
       <c r="E563">
         <v>0</v>
@@ -5353,7 +5484,7 @@
     </row>
     <row r="564" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B564">
-        <v>8522</v>
+        <v>8540</v>
       </c>
       <c r="E564">
         <v>0</v>
@@ -5361,7 +5492,7 @@
     </row>
     <row r="565" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B565">
-        <v>8523</v>
+        <v>8544</v>
       </c>
       <c r="E565">
         <v>0</v>
@@ -5369,7 +5500,7 @@
     </row>
     <row r="566" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B566">
-        <v>8524</v>
+        <v>8545</v>
       </c>
       <c r="E566">
         <v>0</v>
@@ -5377,7 +5508,7 @@
     </row>
     <row r="567" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B567">
-        <v>8525</v>
+        <v>8546</v>
       </c>
       <c r="E567">
         <v>0</v>
@@ -5385,7 +5516,7 @@
     </row>
     <row r="568" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B568">
-        <v>8526</v>
+        <v>8549</v>
       </c>
       <c r="E568">
         <v>0</v>
@@ -5393,7 +5524,7 @@
     </row>
     <row r="569" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B569">
-        <v>8527</v>
+        <v>8550</v>
       </c>
       <c r="E569">
         <v>0</v>
@@ -5401,7 +5532,7 @@
     </row>
     <row r="570" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B570">
-        <v>8528</v>
+        <v>8556</v>
       </c>
       <c r="E570">
         <v>0</v>
@@ -5409,7 +5540,7 @@
     </row>
     <row r="571" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B571">
-        <v>8529</v>
+        <v>8557</v>
       </c>
       <c r="E571">
         <v>0</v>
@@ -5417,7 +5548,7 @@
     </row>
     <row r="572" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B572">
-        <v>8530</v>
+        <v>8558</v>
       </c>
       <c r="E572">
         <v>0</v>
@@ -5425,7 +5556,7 @@
     </row>
     <row r="573" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B573">
-        <v>8531</v>
+        <v>8559</v>
       </c>
       <c r="E573">
         <v>0</v>
@@ -5433,7 +5564,7 @@
     </row>
     <row r="574" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B574">
-        <v>8532</v>
+        <v>8560</v>
       </c>
       <c r="E574">
         <v>0</v>
@@ -5441,7 +5572,7 @@
     </row>
     <row r="575" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B575">
-        <v>8533</v>
+        <v>8561</v>
       </c>
       <c r="E575">
         <v>0</v>
@@ -5449,7 +5580,7 @@
     </row>
     <row r="576" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B576">
-        <v>8537</v>
+        <v>8562</v>
       </c>
       <c r="E576">
         <v>0</v>
@@ -5457,7 +5588,7 @@
     </row>
     <row r="577" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B577">
-        <v>8535</v>
+        <v>8575</v>
       </c>
       <c r="E577">
         <v>0</v>
@@ -5465,7 +5596,7 @@
     </row>
     <row r="578" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B578">
-        <v>8538</v>
+        <v>8580</v>
       </c>
       <c r="E578">
         <v>0</v>
@@ -5473,7 +5604,7 @@
     </row>
     <row r="579" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B579">
-        <v>8540</v>
+        <v>8581</v>
       </c>
       <c r="E579">
         <v>0</v>
@@ -5481,7 +5612,7 @@
     </row>
     <row r="580" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B580">
-        <v>8544</v>
+        <v>8582</v>
       </c>
       <c r="E580">
         <v>0</v>
@@ -5489,7 +5620,7 @@
     </row>
     <row r="581" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B581">
-        <v>8545</v>
+        <v>8583</v>
       </c>
       <c r="E581">
         <v>0</v>
@@ -5497,7 +5628,7 @@
     </row>
     <row r="582" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B582">
-        <v>8546</v>
+        <v>8588</v>
       </c>
       <c r="E582">
         <v>0</v>
@@ -5505,7 +5636,7 @@
     </row>
     <row r="583" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B583">
-        <v>8549</v>
+        <v>8589</v>
       </c>
       <c r="E583">
         <v>0</v>
@@ -5513,7 +5644,7 @@
     </row>
     <row r="584" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B584">
-        <v>8550</v>
+        <v>8590</v>
       </c>
       <c r="E584">
         <v>0</v>
@@ -5521,7 +5652,7 @@
     </row>
     <row r="585" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B585">
-        <v>8556</v>
+        <v>8591</v>
       </c>
       <c r="E585">
         <v>0</v>
@@ -5529,7 +5660,7 @@
     </row>
     <row r="586" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B586">
-        <v>8557</v>
+        <v>8592</v>
       </c>
       <c r="E586">
         <v>0</v>
@@ -5537,7 +5668,7 @@
     </row>
     <row r="587" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B587">
-        <v>8558</v>
+        <v>8593</v>
       </c>
       <c r="E587">
         <v>0</v>
@@ -5545,7 +5676,7 @@
     </row>
     <row r="588" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B588">
-        <v>8559</v>
+        <v>8594</v>
       </c>
       <c r="E588">
         <v>0</v>
@@ -5553,7 +5684,7 @@
     </row>
     <row r="589" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B589">
-        <v>8560</v>
+        <v>8595</v>
       </c>
       <c r="E589">
         <v>0</v>
@@ -5561,7 +5692,7 @@
     </row>
     <row r="590" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B590">
-        <v>8561</v>
+        <v>8596</v>
       </c>
       <c r="E590">
         <v>0</v>
@@ -5569,7 +5700,7 @@
     </row>
     <row r="591" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B591">
-        <v>8562</v>
+        <v>8600</v>
       </c>
       <c r="E591">
         <v>0</v>
@@ -5577,7 +5708,7 @@
     </row>
     <row r="592" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B592">
-        <v>8575</v>
+        <v>8601</v>
       </c>
       <c r="E592">
         <v>0</v>
@@ -5585,7 +5716,7 @@
     </row>
     <row r="593" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B593">
-        <v>8580</v>
+        <v>8602</v>
       </c>
       <c r="E593">
         <v>0</v>
@@ -5593,7 +5724,7 @@
     </row>
     <row r="594" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B594">
-        <v>8581</v>
+        <v>8603</v>
       </c>
       <c r="E594">
         <v>0</v>
@@ -5601,7 +5732,7 @@
     </row>
     <row r="595" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B595">
-        <v>8582</v>
+        <v>8604</v>
       </c>
       <c r="E595">
         <v>0</v>
@@ -5609,7 +5740,7 @@
     </row>
     <row r="596" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B596">
-        <v>8583</v>
+        <v>8605</v>
       </c>
       <c r="E596">
         <v>0</v>
@@ -5617,7 +5748,7 @@
     </row>
     <row r="597" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B597">
-        <v>8588</v>
+        <v>8607</v>
       </c>
       <c r="E597">
         <v>0</v>
@@ -5625,7 +5756,7 @@
     </row>
     <row r="598" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B598">
-        <v>8589</v>
+        <v>8608</v>
       </c>
       <c r="E598">
         <v>0</v>
@@ -5633,7 +5764,7 @@
     </row>
     <row r="599" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B599">
-        <v>8590</v>
+        <v>8609</v>
       </c>
       <c r="E599">
         <v>0</v>
@@ -5641,7 +5772,7 @@
     </row>
     <row r="600" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B600">
-        <v>8591</v>
+        <v>8610</v>
       </c>
       <c r="E600">
         <v>0</v>
@@ -5649,7 +5780,7 @@
     </row>
     <row r="601" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B601">
-        <v>8592</v>
+        <v>8611</v>
       </c>
       <c r="E601">
         <v>0</v>
@@ -5657,7 +5788,7 @@
     </row>
     <row r="602" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B602">
-        <v>8593</v>
+        <v>8612</v>
       </c>
       <c r="E602">
         <v>0</v>
@@ -5665,7 +5796,7 @@
     </row>
     <row r="603" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B603">
-        <v>8594</v>
+        <v>8613</v>
       </c>
       <c r="E603">
         <v>0</v>
@@ -5673,7 +5804,7 @@
     </row>
     <row r="604" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B604">
-        <v>8595</v>
+        <v>8614</v>
       </c>
       <c r="E604">
         <v>0</v>
@@ -5681,7 +5812,7 @@
     </row>
     <row r="605" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B605">
-        <v>8596</v>
+        <v>8615</v>
       </c>
       <c r="E605">
         <v>0</v>
@@ -5689,7 +5820,7 @@
     </row>
     <row r="606" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B606">
-        <v>8600</v>
+        <v>8616</v>
       </c>
       <c r="E606">
         <v>0</v>
@@ -5697,7 +5828,7 @@
     </row>
     <row r="607" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B607">
-        <v>8601</v>
+        <v>8619</v>
       </c>
       <c r="E607">
         <v>0</v>
@@ -5705,7 +5836,7 @@
     </row>
     <row r="608" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B608">
-        <v>8602</v>
+        <v>8621</v>
       </c>
       <c r="E608">
         <v>0</v>
@@ -5713,7 +5844,7 @@
     </row>
     <row r="609" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B609">
-        <v>8603</v>
+        <v>8622</v>
       </c>
       <c r="E609">
         <v>0</v>
@@ -5721,7 +5852,7 @@
     </row>
     <row r="610" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B610">
-        <v>8604</v>
+        <v>8623</v>
       </c>
       <c r="E610">
         <v>0</v>
@@ -5729,7 +5860,7 @@
     </row>
     <row r="611" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B611">
-        <v>8605</v>
+        <v>8624</v>
       </c>
       <c r="E611">
         <v>0</v>
@@ -5737,7 +5868,7 @@
     </row>
     <row r="612" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B612">
-        <v>8607</v>
+        <v>8625</v>
       </c>
       <c r="E612">
         <v>0</v>
@@ -5745,7 +5876,7 @@
     </row>
     <row r="613" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B613">
-        <v>8608</v>
+        <v>8626</v>
       </c>
       <c r="E613">
         <v>0</v>
@@ -5753,7 +5884,7 @@
     </row>
     <row r="614" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B614">
-        <v>8609</v>
+        <v>8627</v>
       </c>
       <c r="E614">
         <v>0</v>
@@ -5761,7 +5892,7 @@
     </row>
     <row r="615" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B615">
-        <v>8610</v>
+        <v>8628</v>
       </c>
       <c r="E615">
         <v>0</v>
@@ -5769,7 +5900,7 @@
     </row>
     <row r="616" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B616">
-        <v>8611</v>
+        <v>8629</v>
       </c>
       <c r="E616">
         <v>0</v>
@@ -5777,7 +5908,7 @@
     </row>
     <row r="617" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B617">
-        <v>8612</v>
+        <v>8630</v>
       </c>
       <c r="E617">
         <v>0</v>
@@ -5785,7 +5916,7 @@
     </row>
     <row r="618" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B618">
-        <v>8613</v>
+        <v>8631</v>
       </c>
       <c r="E618">
         <v>0</v>
@@ -5793,7 +5924,7 @@
     </row>
     <row r="619" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B619">
-        <v>8614</v>
+        <v>8632</v>
       </c>
       <c r="E619">
         <v>0</v>
@@ -5801,7 +5932,7 @@
     </row>
     <row r="620" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B620">
-        <v>8615</v>
+        <v>8633</v>
       </c>
       <c r="E620">
         <v>0</v>
@@ -5809,7 +5940,7 @@
     </row>
     <row r="621" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B621">
-        <v>8616</v>
+        <v>8634</v>
       </c>
       <c r="E621">
         <v>0</v>
@@ -5817,7 +5948,7 @@
     </row>
     <row r="622" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B622">
-        <v>8619</v>
+        <v>8635</v>
       </c>
       <c r="E622">
         <v>0</v>
@@ -5825,7 +5956,7 @@
     </row>
     <row r="623" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B623">
-        <v>8621</v>
+        <v>8636</v>
       </c>
       <c r="E623">
         <v>0</v>
@@ -5833,7 +5964,7 @@
     </row>
     <row r="624" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B624">
-        <v>8622</v>
+        <v>8637</v>
       </c>
       <c r="E624">
         <v>0</v>
@@ -5841,7 +5972,7 @@
     </row>
     <row r="625" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B625">
-        <v>8623</v>
+        <v>8638</v>
       </c>
       <c r="E625">
         <v>0</v>
@@ -5849,7 +5980,7 @@
     </row>
     <row r="626" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B626">
-        <v>8624</v>
+        <v>8639</v>
       </c>
       <c r="E626">
         <v>0</v>
@@ -5857,7 +5988,7 @@
     </row>
     <row r="627" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B627">
-        <v>8625</v>
+        <v>8640</v>
       </c>
       <c r="E627">
         <v>0</v>
@@ -5865,7 +5996,7 @@
     </row>
     <row r="628" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B628">
-        <v>8626</v>
+        <v>8641</v>
       </c>
       <c r="E628">
         <v>0</v>
@@ -5873,7 +6004,7 @@
     </row>
     <row r="629" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B629">
-        <v>8627</v>
+        <v>8642</v>
       </c>
       <c r="E629">
         <v>0</v>
@@ -5881,7 +6012,7 @@
     </row>
     <row r="630" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B630">
-        <v>8628</v>
+        <v>8643</v>
       </c>
       <c r="E630">
         <v>0</v>
@@ -5889,7 +6020,7 @@
     </row>
     <row r="631" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B631">
-        <v>8629</v>
+        <v>8644</v>
       </c>
       <c r="E631">
         <v>0</v>
@@ -5897,7 +6028,7 @@
     </row>
     <row r="632" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B632">
-        <v>8630</v>
+        <v>8645</v>
       </c>
       <c r="E632">
         <v>0</v>
@@ -5905,7 +6036,7 @@
     </row>
     <row r="633" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B633">
-        <v>8631</v>
+        <v>8646</v>
       </c>
       <c r="E633">
         <v>0</v>
@@ -5913,7 +6044,7 @@
     </row>
     <row r="634" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B634">
-        <v>8632</v>
+        <v>8647</v>
       </c>
       <c r="E634">
         <v>0</v>
@@ -5921,7 +6052,7 @@
     </row>
     <row r="635" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B635">
-        <v>8633</v>
+        <v>8648</v>
       </c>
       <c r="E635">
         <v>0</v>
@@ -5929,7 +6060,7 @@
     </row>
     <row r="636" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B636">
-        <v>8634</v>
+        <v>8649</v>
       </c>
       <c r="E636">
         <v>0</v>
@@ -5937,7 +6068,7 @@
     </row>
     <row r="637" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B637">
-        <v>8635</v>
+        <v>8650</v>
       </c>
       <c r="E637">
         <v>0</v>
@@ -5945,7 +6076,7 @@
     </row>
     <row r="638" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B638">
-        <v>8636</v>
+        <v>8651</v>
       </c>
       <c r="E638">
         <v>0</v>
@@ -5953,7 +6084,7 @@
     </row>
     <row r="639" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B639">
-        <v>8637</v>
+        <v>8652</v>
       </c>
       <c r="E639">
         <v>0</v>
@@ -5961,7 +6092,7 @@
     </row>
     <row r="640" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B640">
-        <v>8638</v>
+        <v>8653</v>
       </c>
       <c r="E640">
         <v>0</v>
@@ -5969,7 +6100,7 @@
     </row>
     <row r="641" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B641">
-        <v>8639</v>
+        <v>8654</v>
       </c>
       <c r="E641">
         <v>0</v>
@@ -5977,7 +6108,7 @@
     </row>
     <row r="642" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B642">
-        <v>8640</v>
+        <v>8655</v>
       </c>
       <c r="E642">
         <v>0</v>
@@ -5985,7 +6116,7 @@
     </row>
     <row r="643" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B643">
-        <v>8641</v>
+        <v>8656</v>
       </c>
       <c r="E643">
         <v>0</v>
@@ -5993,7 +6124,7 @@
     </row>
     <row r="644" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B644">
-        <v>8642</v>
+        <v>8657</v>
       </c>
       <c r="E644">
         <v>0</v>
@@ -6001,7 +6132,7 @@
     </row>
     <row r="645" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B645">
-        <v>8643</v>
+        <v>8658</v>
       </c>
       <c r="E645">
         <v>0</v>
@@ -6009,7 +6140,7 @@
     </row>
     <row r="646" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B646">
-        <v>8644</v>
+        <v>8659</v>
       </c>
       <c r="E646">
         <v>0</v>
@@ -6017,7 +6148,7 @@
     </row>
     <row r="647" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B647">
-        <v>8645</v>
+        <v>8660</v>
       </c>
       <c r="E647">
         <v>0</v>
@@ -6025,7 +6156,7 @@
     </row>
     <row r="648" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B648">
-        <v>8646</v>
+        <v>8661</v>
       </c>
       <c r="E648">
         <v>0</v>
@@ -6033,7 +6164,7 @@
     </row>
     <row r="649" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B649">
-        <v>8647</v>
+        <v>8662</v>
       </c>
       <c r="E649">
         <v>0</v>
@@ -6041,7 +6172,7 @@
     </row>
     <row r="650" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B650">
-        <v>8648</v>
+        <v>8663</v>
       </c>
       <c r="E650">
         <v>0</v>
@@ -6049,7 +6180,7 @@
     </row>
     <row r="651" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B651">
-        <v>8649</v>
+        <v>8664</v>
       </c>
       <c r="E651">
         <v>0</v>
@@ -6057,7 +6188,7 @@
     </row>
     <row r="652" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B652">
-        <v>8650</v>
+        <v>8665</v>
       </c>
       <c r="E652">
         <v>0</v>
@@ -6065,7 +6196,7 @@
     </row>
     <row r="653" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B653">
-        <v>8651</v>
+        <v>8666</v>
       </c>
       <c r="E653">
         <v>0</v>
@@ -6073,7 +6204,7 @@
     </row>
     <row r="654" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B654">
-        <v>8652</v>
+        <v>8667</v>
       </c>
       <c r="E654">
         <v>0</v>
@@ -6081,7 +6212,7 @@
     </row>
     <row r="655" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B655">
-        <v>8653</v>
+        <v>8668</v>
       </c>
       <c r="E655">
         <v>0</v>
@@ -6089,7 +6220,7 @@
     </row>
     <row r="656" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B656">
-        <v>8654</v>
+        <v>8669</v>
       </c>
       <c r="E656">
         <v>0</v>
@@ -6097,7 +6228,7 @@
     </row>
     <row r="657" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B657">
-        <v>8655</v>
+        <v>8670</v>
       </c>
       <c r="E657">
         <v>0</v>
@@ -6105,7 +6236,7 @@
     </row>
     <row r="658" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B658">
-        <v>8656</v>
+        <v>8671</v>
       </c>
       <c r="E658">
         <v>0</v>
@@ -6113,7 +6244,7 @@
     </row>
     <row r="659" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B659">
-        <v>8657</v>
+        <v>8672</v>
       </c>
       <c r="E659">
         <v>0</v>
@@ -6121,7 +6252,7 @@
     </row>
     <row r="660" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B660">
-        <v>8658</v>
+        <v>8673</v>
       </c>
       <c r="E660">
         <v>0</v>
@@ -6129,7 +6260,7 @@
     </row>
     <row r="661" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B661">
-        <v>8659</v>
+        <v>8674</v>
       </c>
       <c r="E661">
         <v>0</v>
@@ -6137,7 +6268,7 @@
     </row>
     <row r="662" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B662">
-        <v>8660</v>
+        <v>8675</v>
       </c>
       <c r="E662">
         <v>0</v>
@@ -6145,7 +6276,7 @@
     </row>
     <row r="663" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B663">
-        <v>8661</v>
+        <v>8676</v>
       </c>
       <c r="E663">
         <v>0</v>
@@ -6153,7 +6284,7 @@
     </row>
     <row r="664" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B664">
-        <v>8662</v>
+        <v>8677</v>
       </c>
       <c r="E664">
         <v>0</v>
@@ -6161,7 +6292,7 @@
     </row>
     <row r="665" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B665">
-        <v>8663</v>
+        <v>8678</v>
       </c>
       <c r="E665">
         <v>0</v>
@@ -6169,7 +6300,7 @@
     </row>
     <row r="666" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B666">
-        <v>8664</v>
+        <v>8679</v>
       </c>
       <c r="E666">
         <v>0</v>
@@ -6177,7 +6308,7 @@
     </row>
     <row r="667" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B667">
-        <v>8665</v>
+        <v>8680</v>
       </c>
       <c r="E667">
         <v>0</v>
@@ -6185,7 +6316,7 @@
     </row>
     <row r="668" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B668">
-        <v>8666</v>
+        <v>8681</v>
       </c>
       <c r="E668">
         <v>0</v>
@@ -6193,7 +6324,7 @@
     </row>
     <row r="669" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B669">
-        <v>8667</v>
+        <v>8682</v>
       </c>
       <c r="E669">
         <v>0</v>
@@ -6201,7 +6332,7 @@
     </row>
     <row r="670" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B670">
-        <v>8668</v>
+        <v>8683</v>
       </c>
       <c r="E670">
         <v>0</v>
@@ -6209,7 +6340,7 @@
     </row>
     <row r="671" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B671">
-        <v>8669</v>
+        <v>8684</v>
       </c>
       <c r="E671">
         <v>0</v>
@@ -6217,7 +6348,7 @@
     </row>
     <row r="672" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B672">
-        <v>8670</v>
+        <v>8685</v>
       </c>
       <c r="E672">
         <v>0</v>
@@ -6225,7 +6356,7 @@
     </row>
     <row r="673" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B673">
-        <v>8671</v>
+        <v>8686</v>
       </c>
       <c r="E673">
         <v>0</v>
@@ -6233,7 +6364,7 @@
     </row>
     <row r="674" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B674">
-        <v>8672</v>
+        <v>8687</v>
       </c>
       <c r="E674">
         <v>0</v>
@@ -6241,7 +6372,7 @@
     </row>
     <row r="675" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B675">
-        <v>8673</v>
+        <v>8688</v>
       </c>
       <c r="E675">
         <v>0</v>
@@ -6249,7 +6380,7 @@
     </row>
     <row r="676" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B676">
-        <v>8674</v>
+        <v>8689</v>
       </c>
       <c r="E676">
         <v>0</v>
@@ -6257,7 +6388,7 @@
     </row>
     <row r="677" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B677">
-        <v>8675</v>
+        <v>8690</v>
       </c>
       <c r="E677">
         <v>0</v>
@@ -6265,7 +6396,7 @@
     </row>
     <row r="678" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B678">
-        <v>8676</v>
+        <v>8691</v>
       </c>
       <c r="E678">
         <v>0</v>
@@ -6273,7 +6404,7 @@
     </row>
     <row r="679" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B679">
-        <v>8677</v>
+        <v>8692</v>
       </c>
       <c r="E679">
         <v>0</v>
@@ -6281,7 +6412,7 @@
     </row>
     <row r="680" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B680">
-        <v>8678</v>
+        <v>8693</v>
       </c>
       <c r="E680">
         <v>0</v>
@@ -6289,7 +6420,7 @@
     </row>
     <row r="681" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B681">
-        <v>8679</v>
+        <v>8694</v>
       </c>
       <c r="E681">
         <v>0</v>
@@ -6297,7 +6428,7 @@
     </row>
     <row r="682" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B682">
-        <v>8680</v>
+        <v>8695</v>
       </c>
       <c r="E682">
         <v>0</v>
@@ -6305,7 +6436,7 @@
     </row>
     <row r="683" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B683">
-        <v>8681</v>
+        <v>8696</v>
       </c>
       <c r="E683">
         <v>0</v>
@@ -6313,7 +6444,7 @@
     </row>
     <row r="684" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B684">
-        <v>8682</v>
+        <v>8697</v>
       </c>
       <c r="E684">
         <v>0</v>
@@ -6321,7 +6452,7 @@
     </row>
     <row r="685" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B685">
-        <v>8683</v>
+        <v>8698</v>
       </c>
       <c r="E685">
         <v>0</v>
@@ -6329,7 +6460,7 @@
     </row>
     <row r="686" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B686">
-        <v>8684</v>
+        <v>8699</v>
       </c>
       <c r="E686">
         <v>0</v>
@@ -6337,7 +6468,7 @@
     </row>
     <row r="687" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B687">
-        <v>8685</v>
+        <v>8701</v>
       </c>
       <c r="E687">
         <v>0</v>
@@ -6345,7 +6476,7 @@
     </row>
     <row r="688" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B688">
-        <v>8686</v>
+        <v>8702</v>
       </c>
       <c r="E688">
         <v>0</v>
@@ -6353,7 +6484,7 @@
     </row>
     <row r="689" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B689">
-        <v>8687</v>
+        <v>8703</v>
       </c>
       <c r="E689">
         <v>0</v>
@@ -6361,7 +6492,7 @@
     </row>
     <row r="690" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B690">
-        <v>8688</v>
+        <v>8704</v>
       </c>
       <c r="E690">
         <v>0</v>
@@ -6369,7 +6500,7 @@
     </row>
     <row r="691" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B691">
-        <v>8689</v>
+        <v>8705</v>
       </c>
       <c r="E691">
         <v>0</v>
@@ -6377,7 +6508,7 @@
     </row>
     <row r="692" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B692">
-        <v>8690</v>
+        <v>8706</v>
       </c>
       <c r="E692">
         <v>0</v>
@@ -6385,7 +6516,7 @@
     </row>
     <row r="693" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B693">
-        <v>8691</v>
+        <v>8707</v>
       </c>
       <c r="E693">
         <v>0</v>
@@ -6393,7 +6524,7 @@
     </row>
     <row r="694" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B694">
-        <v>8692</v>
+        <v>8708</v>
       </c>
       <c r="E694">
         <v>0</v>
@@ -6401,7 +6532,7 @@
     </row>
     <row r="695" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B695">
-        <v>8693</v>
+        <v>8709</v>
       </c>
       <c r="E695">
         <v>0</v>
@@ -6409,7 +6540,7 @@
     </row>
     <row r="696" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B696">
-        <v>8694</v>
+        <v>8710</v>
       </c>
       <c r="E696">
         <v>0</v>
@@ -6417,7 +6548,7 @@
     </row>
     <row r="697" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B697">
-        <v>8695</v>
+        <v>8711</v>
       </c>
       <c r="E697">
         <v>0</v>
@@ -6425,7 +6556,7 @@
     </row>
     <row r="698" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B698">
-        <v>8696</v>
+        <v>8712</v>
       </c>
       <c r="E698">
         <v>0</v>
@@ -6433,7 +6564,7 @@
     </row>
     <row r="699" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B699">
-        <v>8697</v>
+        <v>8713</v>
       </c>
       <c r="E699">
         <v>0</v>
@@ -6441,7 +6572,7 @@
     </row>
     <row r="700" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B700">
-        <v>8698</v>
+        <v>8714</v>
       </c>
       <c r="E700">
         <v>0</v>
@@ -6449,15 +6580,23 @@
     </row>
     <row r="701" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B701">
-        <v>8699</v>
+        <v>8715</v>
       </c>
       <c r="E701">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B702">
+        <v>8716</v>
+      </c>
+      <c r="E702">
         <v>0</v>
       </c>
     </row>
     <row r="703" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B703">
-        <v>8701</v>
+        <v>8717</v>
       </c>
       <c r="E703">
         <v>0</v>
@@ -6465,7 +6604,7 @@
     </row>
     <row r="704" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B704">
-        <v>8702</v>
+        <v>8718</v>
       </c>
       <c r="E704">
         <v>0</v>
@@ -6473,7 +6612,7 @@
     </row>
     <row r="705" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B705">
-        <v>8703</v>
+        <v>8719</v>
       </c>
       <c r="E705">
         <v>0</v>
@@ -6481,7 +6620,7 @@
     </row>
     <row r="706" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B706">
-        <v>8704</v>
+        <v>8720</v>
       </c>
       <c r="E706">
         <v>0</v>
@@ -6489,7 +6628,7 @@
     </row>
     <row r="707" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B707">
-        <v>8705</v>
+        <v>8721</v>
       </c>
       <c r="E707">
         <v>0</v>
@@ -6497,7 +6636,7 @@
     </row>
     <row r="708" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B708">
-        <v>8706</v>
+        <v>8722</v>
       </c>
       <c r="E708">
         <v>0</v>
@@ -6505,7 +6644,7 @@
     </row>
     <row r="709" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B709">
-        <v>8707</v>
+        <v>8723</v>
       </c>
       <c r="E709">
         <v>0</v>
@@ -6513,7 +6652,7 @@
     </row>
     <row r="710" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B710">
-        <v>8708</v>
+        <v>8724</v>
       </c>
       <c r="E710">
         <v>0</v>
@@ -6521,7 +6660,7 @@
     </row>
     <row r="711" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B711">
-        <v>8709</v>
+        <v>8725</v>
       </c>
       <c r="E711">
         <v>0</v>
@@ -6529,7 +6668,7 @@
     </row>
     <row r="712" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B712">
-        <v>8710</v>
+        <v>8726</v>
       </c>
       <c r="E712">
         <v>0</v>
@@ -6537,7 +6676,7 @@
     </row>
     <row r="713" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B713">
-        <v>8711</v>
+        <v>8727</v>
       </c>
       <c r="E713">
         <v>0</v>
@@ -6545,7 +6684,7 @@
     </row>
     <row r="714" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B714">
-        <v>8712</v>
+        <v>8731</v>
       </c>
       <c r="E714">
         <v>0</v>
@@ -6553,7 +6692,7 @@
     </row>
     <row r="715" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B715">
-        <v>8713</v>
+        <v>8732</v>
       </c>
       <c r="E715">
         <v>0</v>
@@ -6561,7 +6700,7 @@
     </row>
     <row r="716" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B716">
-        <v>8714</v>
+        <v>8740</v>
       </c>
       <c r="E716">
         <v>0</v>
@@ -6569,7 +6708,7 @@
     </row>
     <row r="717" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B717">
-        <v>8715</v>
+        <v>8745</v>
       </c>
       <c r="E717">
         <v>0</v>
@@ -6577,7 +6716,7 @@
     </row>
     <row r="718" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B718">
-        <v>8716</v>
+        <v>8780</v>
       </c>
       <c r="E718">
         <v>0</v>
@@ -6585,7 +6724,7 @@
     </row>
     <row r="719" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B719">
-        <v>8717</v>
+        <v>8789</v>
       </c>
       <c r="E719">
         <v>0</v>
@@ -6593,7 +6732,7 @@
     </row>
     <row r="720" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B720">
-        <v>8718</v>
+        <v>8790</v>
       </c>
       <c r="E720">
         <v>0</v>
@@ -6601,7 +6740,7 @@
     </row>
     <row r="721" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B721">
-        <v>8719</v>
+        <v>8792</v>
       </c>
       <c r="E721">
         <v>0</v>
@@ -6609,7 +6748,7 @@
     </row>
     <row r="722" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B722">
-        <v>8720</v>
+        <v>8793</v>
       </c>
       <c r="E722">
         <v>0</v>
@@ -6617,7 +6756,7 @@
     </row>
     <row r="723" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B723">
-        <v>8721</v>
+        <v>8794</v>
       </c>
       <c r="E723">
         <v>0</v>
@@ -6625,7 +6764,7 @@
     </row>
     <row r="724" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B724">
-        <v>8722</v>
+        <v>8795</v>
       </c>
       <c r="E724">
         <v>0</v>
@@ -6633,7 +6772,7 @@
     </row>
     <row r="725" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B725">
-        <v>8723</v>
+        <v>8796</v>
       </c>
       <c r="E725">
         <v>0</v>
@@ -6641,7 +6780,7 @@
     </row>
     <row r="726" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B726">
-        <v>8724</v>
+        <v>8797</v>
       </c>
       <c r="E726">
         <v>0</v>
@@ -6649,7 +6788,7 @@
     </row>
     <row r="727" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B727">
-        <v>8725</v>
+        <v>8800</v>
       </c>
       <c r="E727">
         <v>0</v>
@@ -6657,7 +6796,7 @@
     </row>
     <row r="728" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B728">
-        <v>8726</v>
+        <v>8811</v>
       </c>
       <c r="E728">
         <v>0</v>
@@ -6665,7 +6804,7 @@
     </row>
     <row r="729" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B729">
-        <v>8727</v>
+        <v>8812</v>
       </c>
       <c r="E729">
         <v>0</v>
@@ -6673,7 +6812,7 @@
     </row>
     <row r="730" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B730">
-        <v>8731</v>
+        <v>8813</v>
       </c>
       <c r="E730">
         <v>0</v>
@@ -6681,7 +6820,7 @@
     </row>
     <row r="731" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B731">
-        <v>8732</v>
+        <v>8814</v>
       </c>
       <c r="E731">
         <v>0</v>
@@ -6689,7 +6828,7 @@
     </row>
     <row r="732" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B732">
-        <v>8740</v>
+        <v>8815</v>
       </c>
       <c r="E732">
         <v>0</v>
@@ -6697,7 +6836,7 @@
     </row>
     <row r="733" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B733">
-        <v>8745</v>
+        <v>8816</v>
       </c>
       <c r="E733">
         <v>0</v>
@@ -6705,7 +6844,7 @@
     </row>
     <row r="734" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B734">
-        <v>8780</v>
+        <v>8817</v>
       </c>
       <c r="E734">
         <v>0</v>
@@ -6713,7 +6852,7 @@
     </row>
     <row r="735" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B735">
-        <v>8789</v>
+        <v>8818</v>
       </c>
       <c r="E735">
         <v>0</v>
@@ -6721,7 +6860,7 @@
     </row>
     <row r="736" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B736">
-        <v>8790</v>
+        <v>8819</v>
       </c>
       <c r="E736">
         <v>0</v>
@@ -6729,7 +6868,7 @@
     </row>
     <row r="737" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B737">
-        <v>8792</v>
+        <v>8820</v>
       </c>
       <c r="E737">
         <v>0</v>
@@ -6737,7 +6876,7 @@
     </row>
     <row r="738" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B738">
-        <v>8793</v>
+        <v>8821</v>
       </c>
       <c r="E738">
         <v>0</v>
@@ -6745,7 +6884,7 @@
     </row>
     <row r="739" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B739">
-        <v>8794</v>
+        <v>8822</v>
       </c>
       <c r="E739">
         <v>0</v>
@@ -6753,7 +6892,7 @@
     </row>
     <row r="740" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B740">
-        <v>8795</v>
+        <v>8823</v>
       </c>
       <c r="E740">
         <v>0</v>
@@ -6761,7 +6900,7 @@
     </row>
     <row r="741" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B741">
-        <v>8796</v>
+        <v>8824</v>
       </c>
       <c r="E741">
         <v>0</v>
@@ -6769,7 +6908,7 @@
     </row>
     <row r="742" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B742">
-        <v>8797</v>
+        <v>8825</v>
       </c>
       <c r="E742">
         <v>0</v>
@@ -6777,7 +6916,7 @@
     </row>
     <row r="743" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B743">
-        <v>8800</v>
+        <v>8826</v>
       </c>
       <c r="E743">
         <v>0</v>
@@ -6785,7 +6924,7 @@
     </row>
     <row r="744" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B744">
-        <v>8811</v>
+        <v>8827</v>
       </c>
       <c r="E744">
         <v>0</v>
@@ -6793,7 +6932,7 @@
     </row>
     <row r="745" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B745">
-        <v>8812</v>
+        <v>8828</v>
       </c>
       <c r="E745">
         <v>0</v>
@@ -6801,7 +6940,7 @@
     </row>
     <row r="746" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B746">
-        <v>8813</v>
+        <v>8829</v>
       </c>
       <c r="E746">
         <v>0</v>
@@ -6809,7 +6948,7 @@
     </row>
     <row r="747" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B747">
-        <v>8814</v>
+        <v>8830</v>
       </c>
       <c r="E747">
         <v>0</v>
@@ -6817,7 +6956,7 @@
     </row>
     <row r="748" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B748">
-        <v>8815</v>
+        <v>8831</v>
       </c>
       <c r="E748">
         <v>0</v>
@@ -6825,7 +6964,7 @@
     </row>
     <row r="749" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B749">
-        <v>8816</v>
+        <v>8832</v>
       </c>
       <c r="E749">
         <v>0</v>
@@ -6833,7 +6972,7 @@
     </row>
     <row r="750" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B750">
-        <v>8817</v>
+        <v>8833</v>
       </c>
       <c r="E750">
         <v>0</v>
@@ -6841,7 +6980,7 @@
     </row>
     <row r="751" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B751">
-        <v>8818</v>
+        <v>8834</v>
       </c>
       <c r="E751">
         <v>0</v>
@@ -6849,7 +6988,7 @@
     </row>
     <row r="752" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B752">
-        <v>8819</v>
+        <v>8835</v>
       </c>
       <c r="E752">
         <v>0</v>
@@ -6857,7 +6996,7 @@
     </row>
     <row r="753" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B753">
-        <v>8820</v>
+        <v>8836</v>
       </c>
       <c r="E753">
         <v>0</v>
@@ -6865,7 +7004,7 @@
     </row>
     <row r="754" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B754">
-        <v>8821</v>
+        <v>8837</v>
       </c>
       <c r="E754">
         <v>0</v>
@@ -6873,7 +7012,7 @@
     </row>
     <row r="755" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B755">
-        <v>8822</v>
+        <v>8838</v>
       </c>
       <c r="E755">
         <v>0</v>
@@ -6881,7 +7020,7 @@
     </row>
     <row r="756" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B756">
-        <v>8823</v>
+        <v>8839</v>
       </c>
       <c r="E756">
         <v>0</v>
@@ -6889,7 +7028,7 @@
     </row>
     <row r="757" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B757">
-        <v>8824</v>
+        <v>8840</v>
       </c>
       <c r="E757">
         <v>0</v>
@@ -6897,7 +7036,7 @@
     </row>
     <row r="758" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B758">
-        <v>8825</v>
+        <v>8841</v>
       </c>
       <c r="E758">
         <v>0</v>
@@ -6905,7 +7044,7 @@
     </row>
     <row r="759" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B759">
-        <v>8826</v>
+        <v>8842</v>
       </c>
       <c r="E759">
         <v>0</v>
@@ -6913,7 +7052,7 @@
     </row>
     <row r="760" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B760">
-        <v>8827</v>
+        <v>8843</v>
       </c>
       <c r="E760">
         <v>0</v>
@@ -6921,7 +7060,7 @@
     </row>
     <row r="761" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B761">
-        <v>8828</v>
+        <v>8844</v>
       </c>
       <c r="E761">
         <v>0</v>
@@ -6929,7 +7068,7 @@
     </row>
     <row r="762" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B762">
-        <v>8829</v>
+        <v>8845</v>
       </c>
       <c r="E762">
         <v>0</v>
@@ -6937,7 +7076,7 @@
     </row>
     <row r="763" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B763">
-        <v>8830</v>
+        <v>8846</v>
       </c>
       <c r="E763">
         <v>0</v>
@@ -6945,7 +7084,7 @@
     </row>
     <row r="764" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B764">
-        <v>8831</v>
+        <v>8857</v>
       </c>
       <c r="E764">
         <v>0</v>
@@ -6953,7 +7092,7 @@
     </row>
     <row r="765" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B765">
-        <v>8832</v>
+        <v>8858</v>
       </c>
       <c r="E765">
         <v>0</v>
@@ -6961,7 +7100,7 @@
     </row>
     <row r="766" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B766">
-        <v>8833</v>
+        <v>8859</v>
       </c>
       <c r="E766">
         <v>0</v>
@@ -6969,7 +7108,7 @@
     </row>
     <row r="767" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B767">
-        <v>8834</v>
+        <v>8860</v>
       </c>
       <c r="E767">
         <v>0</v>
@@ -6977,7 +7116,7 @@
     </row>
     <row r="768" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B768">
-        <v>8835</v>
+        <v>8861</v>
       </c>
       <c r="E768">
         <v>0</v>
@@ -6985,7 +7124,7 @@
     </row>
     <row r="769" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B769">
-        <v>8836</v>
+        <v>8862</v>
       </c>
       <c r="E769">
         <v>0</v>
@@ -6993,7 +7132,7 @@
     </row>
     <row r="770" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B770">
-        <v>8837</v>
+        <v>8863</v>
       </c>
       <c r="E770">
         <v>0</v>
@@ -7001,7 +7140,7 @@
     </row>
     <row r="771" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B771">
-        <v>8838</v>
+        <v>8864</v>
       </c>
       <c r="E771">
         <v>0</v>
@@ -7009,7 +7148,7 @@
     </row>
     <row r="772" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B772">
-        <v>8839</v>
+        <v>8865</v>
       </c>
       <c r="E772">
         <v>0</v>
@@ -7017,7 +7156,7 @@
     </row>
     <row r="773" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B773">
-        <v>8840</v>
+        <v>8866</v>
       </c>
       <c r="E773">
         <v>0</v>
@@ -7025,7 +7164,7 @@
     </row>
     <row r="774" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B774">
-        <v>8841</v>
+        <v>8867</v>
       </c>
       <c r="E774">
         <v>0</v>
@@ -7033,7 +7172,7 @@
     </row>
     <row r="775" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B775">
-        <v>8842</v>
+        <v>8868</v>
       </c>
       <c r="E775">
         <v>0</v>
@@ -7041,7 +7180,7 @@
     </row>
     <row r="776" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B776">
-        <v>8843</v>
+        <v>8870</v>
       </c>
       <c r="E776">
         <v>0</v>
@@ -7049,7 +7188,7 @@
     </row>
     <row r="777" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B777">
-        <v>8844</v>
+        <v>8871</v>
       </c>
       <c r="E777">
         <v>0</v>
@@ -7057,7 +7196,7 @@
     </row>
     <row r="778" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B778">
-        <v>8845</v>
+        <v>8872</v>
       </c>
       <c r="E778">
         <v>0</v>
@@ -7065,7 +7204,7 @@
     </row>
     <row r="779" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B779">
-        <v>8846</v>
+        <v>8873</v>
       </c>
       <c r="E779">
         <v>0</v>
@@ -7073,7 +7212,7 @@
     </row>
     <row r="780" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B780">
-        <v>8857</v>
+        <v>8874</v>
       </c>
       <c r="E780">
         <v>0</v>
@@ -7081,7 +7220,7 @@
     </row>
     <row r="781" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B781">
-        <v>8858</v>
+        <v>8875</v>
       </c>
       <c r="E781">
         <v>0</v>
@@ -7089,7 +7228,7 @@
     </row>
     <row r="782" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B782">
-        <v>8859</v>
+        <v>8876</v>
       </c>
       <c r="E782">
         <v>0</v>
@@ -7097,7 +7236,7 @@
     </row>
     <row r="783" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B783">
-        <v>8860</v>
+        <v>8877</v>
       </c>
       <c r="E783">
         <v>0</v>
@@ -7105,7 +7244,7 @@
     </row>
     <row r="784" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B784">
-        <v>8861</v>
+        <v>8878</v>
       </c>
       <c r="E784">
         <v>0</v>
@@ -7113,7 +7252,7 @@
     </row>
     <row r="785" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B785">
-        <v>8862</v>
+        <v>8879</v>
       </c>
       <c r="E785">
         <v>0</v>
@@ -7121,7 +7260,7 @@
     </row>
     <row r="786" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B786">
-        <v>8863</v>
+        <v>8880</v>
       </c>
       <c r="E786">
         <v>0</v>
@@ -7129,7 +7268,7 @@
     </row>
     <row r="787" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B787">
-        <v>8864</v>
+        <v>8881</v>
       </c>
       <c r="E787">
         <v>0</v>
@@ -7137,7 +7276,7 @@
     </row>
     <row r="788" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B788">
-        <v>8865</v>
+        <v>8882</v>
       </c>
       <c r="E788">
         <v>0</v>
@@ -7145,7 +7284,7 @@
     </row>
     <row r="789" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B789">
-        <v>8866</v>
+        <v>8883</v>
       </c>
       <c r="E789">
         <v>0</v>
@@ -7153,7 +7292,7 @@
     </row>
     <row r="790" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B790">
-        <v>8867</v>
+        <v>8899</v>
       </c>
       <c r="E790">
         <v>0</v>
@@ -7161,7 +7300,7 @@
     </row>
     <row r="791" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B791">
-        <v>8868</v>
+        <v>8900</v>
       </c>
       <c r="E791">
         <v>0</v>
@@ -7169,7 +7308,7 @@
     </row>
     <row r="792" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B792">
-        <v>8870</v>
+        <v>8901</v>
       </c>
       <c r="E792">
         <v>0</v>
@@ -7177,7 +7316,7 @@
     </row>
     <row r="793" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B793">
-        <v>8871</v>
+        <v>8902</v>
       </c>
       <c r="E793">
         <v>0</v>
@@ -7185,7 +7324,7 @@
     </row>
     <row r="794" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B794">
-        <v>8872</v>
+        <v>8903</v>
       </c>
       <c r="E794">
         <v>0</v>
@@ -7193,7 +7332,7 @@
     </row>
     <row r="795" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B795">
-        <v>8873</v>
+        <v>8904</v>
       </c>
       <c r="E795">
         <v>0</v>
@@ -7201,7 +7340,7 @@
     </row>
     <row r="796" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B796">
-        <v>8874</v>
+        <v>8905</v>
       </c>
       <c r="E796">
         <v>0</v>
@@ -7209,7 +7348,7 @@
     </row>
     <row r="797" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B797">
-        <v>8875</v>
+        <v>8906</v>
       </c>
       <c r="E797">
         <v>0</v>
@@ -7217,7 +7356,7 @@
     </row>
     <row r="798" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B798">
-        <v>8876</v>
+        <v>8907</v>
       </c>
       <c r="E798">
         <v>0</v>
@@ -7225,7 +7364,7 @@
     </row>
     <row r="799" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B799">
-        <v>8877</v>
+        <v>8908</v>
       </c>
       <c r="E799">
         <v>0</v>
@@ -7233,7 +7372,7 @@
     </row>
     <row r="800" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B800">
-        <v>8878</v>
+        <v>8909</v>
       </c>
       <c r="E800">
         <v>0</v>
@@ -7241,7 +7380,7 @@
     </row>
     <row r="801" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B801">
-        <v>8879</v>
+        <v>8910</v>
       </c>
       <c r="E801">
         <v>0</v>
@@ -7249,7 +7388,7 @@
     </row>
     <row r="802" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B802">
-        <v>8880</v>
+        <v>8911</v>
       </c>
       <c r="E802">
         <v>0</v>
@@ -7257,7 +7396,7 @@
     </row>
     <row r="803" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B803">
-        <v>8881</v>
+        <v>8912</v>
       </c>
       <c r="E803">
         <v>0</v>
@@ -7265,7 +7404,7 @@
     </row>
     <row r="804" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B804">
-        <v>8882</v>
+        <v>8913</v>
       </c>
       <c r="E804">
         <v>0</v>
@@ -7273,7 +7412,7 @@
     </row>
     <row r="805" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B805">
-        <v>8883</v>
+        <v>8914</v>
       </c>
       <c r="E805">
         <v>0</v>
@@ -7281,7 +7420,7 @@
     </row>
     <row r="806" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B806">
-        <v>8899</v>
+        <v>8915</v>
       </c>
       <c r="E806">
         <v>0</v>
@@ -7289,7 +7428,7 @@
     </row>
     <row r="807" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B807">
-        <v>8900</v>
+        <v>8916</v>
       </c>
       <c r="E807">
         <v>0</v>
@@ -7297,7 +7436,7 @@
     </row>
     <row r="808" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B808">
-        <v>8901</v>
+        <v>8917</v>
       </c>
       <c r="E808">
         <v>0</v>
@@ -7305,7 +7444,7 @@
     </row>
     <row r="809" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B809">
-        <v>8902</v>
+        <v>8918</v>
       </c>
       <c r="E809">
         <v>0</v>
@@ -7313,7 +7452,7 @@
     </row>
     <row r="810" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B810">
-        <v>8903</v>
+        <v>8919</v>
       </c>
       <c r="E810">
         <v>0</v>
@@ -7321,7 +7460,7 @@
     </row>
     <row r="811" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B811">
-        <v>8904</v>
+        <v>8920</v>
       </c>
       <c r="E811">
         <v>0</v>
@@ -7329,7 +7468,7 @@
     </row>
     <row r="812" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B812">
-        <v>8905</v>
+        <v>8921</v>
       </c>
       <c r="E812">
         <v>0</v>
@@ -7337,7 +7476,7 @@
     </row>
     <row r="813" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B813">
-        <v>8906</v>
+        <v>8922</v>
       </c>
       <c r="E813">
         <v>0</v>
@@ -7345,7 +7484,7 @@
     </row>
     <row r="814" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B814">
-        <v>8907</v>
+        <v>8923</v>
       </c>
       <c r="E814">
         <v>0</v>
@@ -7353,7 +7492,7 @@
     </row>
     <row r="815" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B815">
-        <v>8908</v>
+        <v>8924</v>
       </c>
       <c r="E815">
         <v>0</v>
@@ -7361,7 +7500,7 @@
     </row>
     <row r="816" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B816">
-        <v>8909</v>
+        <v>8925</v>
       </c>
       <c r="E816">
         <v>0</v>
@@ -7369,7 +7508,7 @@
     </row>
     <row r="817" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B817">
-        <v>8910</v>
+        <v>8926</v>
       </c>
       <c r="E817">
         <v>0</v>
@@ -7377,7 +7516,7 @@
     </row>
     <row r="818" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B818">
-        <v>8911</v>
+        <v>8927</v>
       </c>
       <c r="E818">
         <v>0</v>
@@ -7385,7 +7524,7 @@
     </row>
     <row r="819" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B819">
-        <v>8912</v>
+        <v>8928</v>
       </c>
       <c r="E819">
         <v>0</v>
@@ -7393,7 +7532,7 @@
     </row>
     <row r="820" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B820">
-        <v>8913</v>
+        <v>8929</v>
       </c>
       <c r="E820">
         <v>0</v>
@@ -7401,7 +7540,7 @@
     </row>
     <row r="821" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B821">
-        <v>8914</v>
+        <v>8930</v>
       </c>
       <c r="E821">
         <v>0</v>
@@ -7409,7 +7548,7 @@
     </row>
     <row r="822" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B822">
-        <v>8915</v>
+        <v>8931</v>
       </c>
       <c r="E822">
         <v>0</v>
@@ -7417,7 +7556,7 @@
     </row>
     <row r="823" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B823">
-        <v>8916</v>
+        <v>8932</v>
       </c>
       <c r="E823">
         <v>0</v>
@@ -7425,7 +7564,7 @@
     </row>
     <row r="824" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B824">
-        <v>8917</v>
+        <v>8933</v>
       </c>
       <c r="E824">
         <v>0</v>
@@ -7433,7 +7572,7 @@
     </row>
     <row r="825" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B825">
-        <v>8918</v>
+        <v>8934</v>
       </c>
       <c r="E825">
         <v>0</v>
@@ -7441,7 +7580,7 @@
     </row>
     <row r="826" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B826">
-        <v>8919</v>
+        <v>8935</v>
       </c>
       <c r="E826">
         <v>0</v>
@@ -7449,7 +7588,7 @@
     </row>
     <row r="827" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B827">
-        <v>8920</v>
+        <v>8936</v>
       </c>
       <c r="E827">
         <v>0</v>
@@ -7457,7 +7596,7 @@
     </row>
     <row r="828" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B828">
-        <v>8921</v>
+        <v>8937</v>
       </c>
       <c r="E828">
         <v>0</v>
@@ -7465,7 +7604,7 @@
     </row>
     <row r="829" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B829">
-        <v>8922</v>
+        <v>8938</v>
       </c>
       <c r="E829">
         <v>0</v>
@@ -7473,7 +7612,7 @@
     </row>
     <row r="830" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B830">
-        <v>8923</v>
+        <v>8939</v>
       </c>
       <c r="E830">
         <v>0</v>
@@ -7481,7 +7620,7 @@
     </row>
     <row r="831" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B831">
-        <v>8924</v>
+        <v>8940</v>
       </c>
       <c r="E831">
         <v>0</v>
@@ -7489,7 +7628,7 @@
     </row>
     <row r="832" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B832">
-        <v>8925</v>
+        <v>8941</v>
       </c>
       <c r="E832">
         <v>0</v>
@@ -7497,7 +7636,7 @@
     </row>
     <row r="833" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B833">
-        <v>8926</v>
+        <v>8942</v>
       </c>
       <c r="E833">
         <v>0</v>
@@ -7505,7 +7644,7 @@
     </row>
     <row r="834" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B834">
-        <v>8927</v>
+        <v>8943</v>
       </c>
       <c r="E834">
         <v>0</v>
@@ -7513,7 +7652,7 @@
     </row>
     <row r="835" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B835">
-        <v>8928</v>
+        <v>8944</v>
       </c>
       <c r="E835">
         <v>0</v>
@@ -7521,7 +7660,7 @@
     </row>
     <row r="836" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B836">
-        <v>8929</v>
+        <v>8945</v>
       </c>
       <c r="E836">
         <v>0</v>
@@ -7529,7 +7668,7 @@
     </row>
     <row r="837" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B837">
-        <v>8930</v>
+        <v>8946</v>
       </c>
       <c r="E837">
         <v>0</v>
@@ -7537,7 +7676,7 @@
     </row>
     <row r="838" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B838">
-        <v>8931</v>
+        <v>8947</v>
       </c>
       <c r="E838">
         <v>0</v>
@@ -7545,7 +7684,7 @@
     </row>
     <row r="839" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B839">
-        <v>8932</v>
+        <v>8948</v>
       </c>
       <c r="E839">
         <v>0</v>
@@ -7553,7 +7692,7 @@
     </row>
     <row r="840" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B840">
-        <v>8933</v>
+        <v>8949</v>
       </c>
       <c r="E840">
         <v>0</v>
@@ -7561,7 +7700,7 @@
     </row>
     <row r="841" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B841">
-        <v>8934</v>
+        <v>8950</v>
       </c>
       <c r="E841">
         <v>0</v>
@@ -7569,7 +7708,7 @@
     </row>
     <row r="842" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B842">
-        <v>8935</v>
+        <v>8951</v>
       </c>
       <c r="E842">
         <v>0</v>
@@ -7577,7 +7716,7 @@
     </row>
     <row r="843" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B843">
-        <v>8936</v>
+        <v>8952</v>
       </c>
       <c r="E843">
         <v>0</v>
@@ -7585,7 +7724,7 @@
     </row>
     <row r="844" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B844">
-        <v>8937</v>
+        <v>8953</v>
       </c>
       <c r="E844">
         <v>0</v>
@@ -7593,7 +7732,7 @@
     </row>
     <row r="845" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B845">
-        <v>8938</v>
+        <v>8954</v>
       </c>
       <c r="E845">
         <v>0</v>
@@ -7601,7 +7740,7 @@
     </row>
     <row r="846" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B846">
-        <v>8939</v>
+        <v>8955</v>
       </c>
       <c r="E846">
         <v>0</v>
@@ -7609,7 +7748,7 @@
     </row>
     <row r="847" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B847">
-        <v>8940</v>
+        <v>8956</v>
       </c>
       <c r="E847">
         <v>0</v>
@@ -7617,7 +7756,7 @@
     </row>
     <row r="848" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B848">
-        <v>8941</v>
+        <v>8957</v>
       </c>
       <c r="E848">
         <v>0</v>
@@ -7625,7 +7764,7 @@
     </row>
     <row r="849" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B849">
-        <v>8942</v>
+        <v>8958</v>
       </c>
       <c r="E849">
         <v>0</v>
@@ -7633,7 +7772,7 @@
     </row>
     <row r="850" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B850">
-        <v>8943</v>
+        <v>8959</v>
       </c>
       <c r="E850">
         <v>0</v>
@@ -7641,7 +7780,7 @@
     </row>
     <row r="851" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B851">
-        <v>8944</v>
+        <v>8960</v>
       </c>
       <c r="E851">
         <v>0</v>
@@ -7649,7 +7788,7 @@
     </row>
     <row r="852" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B852">
-        <v>8945</v>
+        <v>8961</v>
       </c>
       <c r="E852">
         <v>0</v>
@@ -7657,7 +7796,7 @@
     </row>
     <row r="853" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B853">
-        <v>8946</v>
+        <v>8962</v>
       </c>
       <c r="E853">
         <v>0</v>
@@ -7665,7 +7804,7 @@
     </row>
     <row r="854" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B854">
-        <v>8947</v>
+        <v>8963</v>
       </c>
       <c r="E854">
         <v>0</v>
@@ -7673,7 +7812,7 @@
     </row>
     <row r="855" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B855">
-        <v>8948</v>
+        <v>8964</v>
       </c>
       <c r="E855">
         <v>0</v>
@@ -7681,7 +7820,7 @@
     </row>
     <row r="856" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B856">
-        <v>8949</v>
+        <v>8965</v>
       </c>
       <c r="E856">
         <v>0</v>
@@ -7689,7 +7828,7 @@
     </row>
     <row r="857" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B857">
-        <v>8950</v>
+        <v>8966</v>
       </c>
       <c r="E857">
         <v>0</v>
@@ -7697,7 +7836,7 @@
     </row>
     <row r="858" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B858">
-        <v>8951</v>
+        <v>8967</v>
       </c>
       <c r="E858">
         <v>0</v>
@@ -7705,7 +7844,7 @@
     </row>
     <row r="859" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B859">
-        <v>8952</v>
+        <v>8968</v>
       </c>
       <c r="E859">
         <v>0</v>
@@ -7713,7 +7852,7 @@
     </row>
     <row r="860" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B860">
-        <v>8953</v>
+        <v>8969</v>
       </c>
       <c r="E860">
         <v>0</v>
@@ -7721,7 +7860,7 @@
     </row>
     <row r="861" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B861">
-        <v>8954</v>
+        <v>8970</v>
       </c>
       <c r="E861">
         <v>0</v>
@@ -7729,7 +7868,7 @@
     </row>
     <row r="862" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B862">
-        <v>8955</v>
+        <v>8971</v>
       </c>
       <c r="E862">
         <v>0</v>
@@ -7737,7 +7876,7 @@
     </row>
     <row r="863" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B863">
-        <v>8956</v>
+        <v>8972</v>
       </c>
       <c r="E863">
         <v>0</v>
@@ -7745,7 +7884,7 @@
     </row>
     <row r="864" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B864">
-        <v>8957</v>
+        <v>8973</v>
       </c>
       <c r="E864">
         <v>0</v>
@@ -7753,7 +7892,7 @@
     </row>
     <row r="865" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B865">
-        <v>8958</v>
+        <v>8974</v>
       </c>
       <c r="E865">
         <v>0</v>
@@ -7761,7 +7900,7 @@
     </row>
     <row r="866" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B866">
-        <v>8959</v>
+        <v>8975</v>
       </c>
       <c r="E866">
         <v>0</v>
@@ -7769,7 +7908,7 @@
     </row>
     <row r="867" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B867">
-        <v>8960</v>
+        <v>8976</v>
       </c>
       <c r="E867">
         <v>0</v>
@@ -7777,7 +7916,7 @@
     </row>
     <row r="868" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B868">
-        <v>8961</v>
+        <v>8977</v>
       </c>
       <c r="E868">
         <v>0</v>
@@ -7785,7 +7924,7 @@
     </row>
     <row r="869" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B869">
-        <v>8962</v>
+        <v>8978</v>
       </c>
       <c r="E869">
         <v>0</v>
@@ -7793,7 +7932,7 @@
     </row>
     <row r="870" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B870">
-        <v>8963</v>
+        <v>8979</v>
       </c>
       <c r="E870">
         <v>0</v>
@@ -7801,7 +7940,7 @@
     </row>
     <row r="871" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B871">
-        <v>8964</v>
+        <v>8980</v>
       </c>
       <c r="E871">
         <v>0</v>
@@ -7809,7 +7948,7 @@
     </row>
     <row r="872" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B872">
-        <v>8965</v>
+        <v>8981</v>
       </c>
       <c r="E872">
         <v>0</v>
@@ -7817,7 +7956,7 @@
     </row>
     <row r="873" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B873">
-        <v>8966</v>
+        <v>8982</v>
       </c>
       <c r="E873">
         <v>0</v>
@@ -7825,7 +7964,7 @@
     </row>
     <row r="874" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B874">
-        <v>8967</v>
+        <v>8983</v>
       </c>
       <c r="E874">
         <v>0</v>
@@ -7833,7 +7972,7 @@
     </row>
     <row r="875" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B875">
-        <v>8968</v>
+        <v>8984</v>
       </c>
       <c r="E875">
         <v>0</v>
@@ -7841,7 +7980,7 @@
     </row>
     <row r="876" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B876">
-        <v>8969</v>
+        <v>8985</v>
       </c>
       <c r="E876">
         <v>0</v>
@@ -7849,7 +7988,7 @@
     </row>
     <row r="877" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B877">
-        <v>8970</v>
+        <v>8986</v>
       </c>
       <c r="E877">
         <v>0</v>
@@ -7857,7 +7996,7 @@
     </row>
     <row r="878" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B878">
-        <v>8971</v>
+        <v>8987</v>
       </c>
       <c r="E878">
         <v>0</v>
@@ -7865,7 +8004,7 @@
     </row>
     <row r="879" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B879">
-        <v>8972</v>
+        <v>8988</v>
       </c>
       <c r="E879">
         <v>0</v>
@@ -7873,7 +8012,7 @@
     </row>
     <row r="880" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B880">
-        <v>8973</v>
+        <v>8989</v>
       </c>
       <c r="E880">
         <v>0</v>
@@ -7881,7 +8020,7 @@
     </row>
     <row r="881" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B881">
-        <v>8974</v>
+        <v>8990</v>
       </c>
       <c r="E881">
         <v>0</v>
@@ -7889,7 +8028,7 @@
     </row>
     <row r="882" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B882">
-        <v>8975</v>
+        <v>8991</v>
       </c>
       <c r="E882">
         <v>0</v>
@@ -7897,7 +8036,7 @@
     </row>
     <row r="883" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B883">
-        <v>8976</v>
+        <v>8992</v>
       </c>
       <c r="E883">
         <v>0</v>
@@ -7905,7 +8044,7 @@
     </row>
     <row r="884" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B884">
-        <v>8977</v>
+        <v>8993</v>
       </c>
       <c r="E884">
         <v>0</v>
@@ -7913,7 +8052,7 @@
     </row>
     <row r="885" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B885">
-        <v>8978</v>
+        <v>8994</v>
       </c>
       <c r="E885">
         <v>0</v>
@@ -7921,7 +8060,7 @@
     </row>
     <row r="886" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B886">
-        <v>8979</v>
+        <v>8995</v>
       </c>
       <c r="E886">
         <v>0</v>
@@ -7929,7 +8068,7 @@
     </row>
     <row r="887" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B887">
-        <v>8980</v>
+        <v>8996</v>
       </c>
       <c r="E887">
         <v>0</v>
@@ -7937,7 +8076,7 @@
     </row>
     <row r="888" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B888">
-        <v>8981</v>
+        <v>8997</v>
       </c>
       <c r="E888">
         <v>0</v>
@@ -7945,7 +8084,7 @@
     </row>
     <row r="889" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B889">
-        <v>8982</v>
+        <v>8998</v>
       </c>
       <c r="E889">
         <v>0</v>
@@ -7953,7 +8092,7 @@
     </row>
     <row r="890" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B890">
-        <v>8983</v>
+        <v>8999</v>
       </c>
       <c r="E890">
         <v>0</v>
@@ -7961,7 +8100,7 @@
     </row>
     <row r="891" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B891">
-        <v>8984</v>
+        <v>9000</v>
       </c>
       <c r="E891">
         <v>0</v>
@@ -7969,7 +8108,7 @@
     </row>
     <row r="892" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B892">
-        <v>8985</v>
+        <v>9001</v>
       </c>
       <c r="E892">
         <v>0</v>
@@ -7977,7 +8116,7 @@
     </row>
     <row r="893" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B893">
-        <v>8986</v>
+        <v>9002</v>
       </c>
       <c r="E893">
         <v>0</v>
@@ -7985,7 +8124,7 @@
     </row>
     <row r="894" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B894">
-        <v>8987</v>
+        <v>9003</v>
       </c>
       <c r="E894">
         <v>0</v>
@@ -7993,7 +8132,7 @@
     </row>
     <row r="895" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B895">
-        <v>8988</v>
+        <v>9004</v>
       </c>
       <c r="E895">
         <v>0</v>
@@ -8001,7 +8140,7 @@
     </row>
     <row r="896" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B896">
-        <v>8989</v>
+        <v>9005</v>
       </c>
       <c r="E896">
         <v>0</v>
@@ -8009,7 +8148,7 @@
     </row>
     <row r="897" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B897">
-        <v>8990</v>
+        <v>9006</v>
       </c>
       <c r="E897">
         <v>0</v>
@@ -8017,7 +8156,7 @@
     </row>
     <row r="898" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B898">
-        <v>8991</v>
+        <v>9007</v>
       </c>
       <c r="E898">
         <v>0</v>
@@ -8025,7 +8164,7 @@
     </row>
     <row r="899" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B899">
-        <v>8992</v>
+        <v>9008</v>
       </c>
       <c r="E899">
         <v>0</v>
@@ -8033,7 +8172,7 @@
     </row>
     <row r="900" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B900">
-        <v>8993</v>
+        <v>9009</v>
       </c>
       <c r="E900">
         <v>0</v>
@@ -8041,7 +8180,7 @@
     </row>
     <row r="901" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B901">
-        <v>8994</v>
+        <v>9010</v>
       </c>
       <c r="E901">
         <v>0</v>
@@ -8049,7 +8188,7 @@
     </row>
     <row r="902" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B902">
-        <v>8995</v>
+        <v>9011</v>
       </c>
       <c r="E902">
         <v>0</v>
@@ -8057,7 +8196,7 @@
     </row>
     <row r="903" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B903">
-        <v>8996</v>
+        <v>9012</v>
       </c>
       <c r="E903">
         <v>0</v>
@@ -8065,7 +8204,7 @@
     </row>
     <row r="904" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B904">
-        <v>8997</v>
+        <v>9013</v>
       </c>
       <c r="E904">
         <v>0</v>
@@ -8073,7 +8212,7 @@
     </row>
     <row r="905" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B905">
-        <v>8998</v>
+        <v>9014</v>
       </c>
       <c r="E905">
         <v>0</v>
@@ -8081,7 +8220,7 @@
     </row>
     <row r="906" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B906">
-        <v>8999</v>
+        <v>9015</v>
       </c>
       <c r="E906">
         <v>0</v>
@@ -8089,7 +8228,7 @@
     </row>
     <row r="907" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B907">
-        <v>9000</v>
+        <v>9016</v>
       </c>
       <c r="E907">
         <v>0</v>
@@ -8097,7 +8236,7 @@
     </row>
     <row r="908" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B908">
-        <v>9001</v>
+        <v>9017</v>
       </c>
       <c r="E908">
         <v>0</v>
@@ -8105,7 +8244,7 @@
     </row>
     <row r="909" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B909">
-        <v>9002</v>
+        <v>9018</v>
       </c>
       <c r="E909">
         <v>0</v>
@@ -8113,7 +8252,7 @@
     </row>
     <row r="910" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B910">
-        <v>9003</v>
+        <v>9019</v>
       </c>
       <c r="E910">
         <v>0</v>
@@ -8121,7 +8260,7 @@
     </row>
     <row r="911" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B911">
-        <v>9004</v>
+        <v>9020</v>
       </c>
       <c r="E911">
         <v>0</v>
@@ -8129,7 +8268,7 @@
     </row>
     <row r="912" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B912">
-        <v>9005</v>
+        <v>9021</v>
       </c>
       <c r="E912">
         <v>0</v>
@@ -8137,7 +8276,7 @@
     </row>
     <row r="913" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B913">
-        <v>9006</v>
+        <v>9022</v>
       </c>
       <c r="E913">
         <v>0</v>
@@ -8145,7 +8284,7 @@
     </row>
     <row r="914" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B914">
-        <v>9007</v>
+        <v>9023</v>
       </c>
       <c r="E914">
         <v>0</v>
@@ -8153,7 +8292,7 @@
     </row>
     <row r="915" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B915">
-        <v>9008</v>
+        <v>9024</v>
       </c>
       <c r="E915">
         <v>0</v>
@@ -8161,7 +8300,7 @@
     </row>
     <row r="916" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B916">
-        <v>9009</v>
+        <v>9025</v>
       </c>
       <c r="E916">
         <v>0</v>
@@ -8169,7 +8308,7 @@
     </row>
     <row r="917" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B917">
-        <v>9010</v>
+        <v>9026</v>
       </c>
       <c r="E917">
         <v>0</v>
@@ -8177,7 +8316,7 @@
     </row>
     <row r="918" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B918">
-        <v>9011</v>
+        <v>9027</v>
       </c>
       <c r="E918">
         <v>0</v>
@@ -8185,7 +8324,7 @@
     </row>
     <row r="919" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B919">
-        <v>9012</v>
+        <v>9028</v>
       </c>
       <c r="E919">
         <v>0</v>
@@ -8193,7 +8332,7 @@
     </row>
     <row r="920" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B920">
-        <v>9013</v>
+        <v>9029</v>
       </c>
       <c r="E920">
         <v>0</v>
@@ -8201,7 +8340,7 @@
     </row>
     <row r="921" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B921">
-        <v>9014</v>
+        <v>9030</v>
       </c>
       <c r="E921">
         <v>0</v>
@@ -8209,7 +8348,7 @@
     </row>
     <row r="922" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B922">
-        <v>9015</v>
+        <v>9031</v>
       </c>
       <c r="E922">
         <v>0</v>
@@ -8217,7 +8356,7 @@
     </row>
     <row r="923" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B923">
-        <v>9016</v>
+        <v>9032</v>
       </c>
       <c r="E923">
         <v>0</v>
@@ -8225,7 +8364,7 @@
     </row>
     <row r="924" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B924">
-        <v>9017</v>
+        <v>9033</v>
       </c>
       <c r="E924">
         <v>0</v>
@@ -8233,7 +8372,7 @@
     </row>
     <row r="925" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B925">
-        <v>9018</v>
+        <v>9034</v>
       </c>
       <c r="E925">
         <v>0</v>
@@ -8241,7 +8380,7 @@
     </row>
     <row r="926" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B926">
-        <v>9019</v>
+        <v>9036</v>
       </c>
       <c r="E926">
         <v>0</v>
@@ -8249,7 +8388,7 @@
     </row>
     <row r="927" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B927">
-        <v>9020</v>
+        <v>9037</v>
       </c>
       <c r="E927">
         <v>0</v>
@@ -8257,7 +8396,7 @@
     </row>
     <row r="928" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B928">
-        <v>9021</v>
+        <v>9038</v>
       </c>
       <c r="E928">
         <v>0</v>
@@ -8265,7 +8404,7 @@
     </row>
     <row r="929" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B929">
-        <v>9022</v>
+        <v>9039</v>
       </c>
       <c r="E929">
         <v>0</v>
@@ -8273,7 +8412,7 @@
     </row>
     <row r="930" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B930">
-        <v>9023</v>
+        <v>9040</v>
       </c>
       <c r="E930">
         <v>0</v>
@@ -8281,7 +8420,7 @@
     </row>
     <row r="931" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B931">
-        <v>9024</v>
+        <v>9041</v>
       </c>
       <c r="E931">
         <v>0</v>
@@ -8289,7 +8428,7 @@
     </row>
     <row r="932" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B932">
-        <v>9025</v>
+        <v>9042</v>
       </c>
       <c r="E932">
         <v>0</v>
@@ -8297,7 +8436,7 @@
     </row>
     <row r="933" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B933">
-        <v>9026</v>
+        <v>9043</v>
       </c>
       <c r="E933">
         <v>0</v>
@@ -8305,7 +8444,7 @@
     </row>
     <row r="934" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B934">
-        <v>9027</v>
+        <v>9044</v>
       </c>
       <c r="E934">
         <v>0</v>
@@ -8313,7 +8452,7 @@
     </row>
     <row r="935" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B935">
-        <v>9028</v>
+        <v>9045</v>
       </c>
       <c r="E935">
         <v>0</v>
@@ -8321,7 +8460,7 @@
     </row>
     <row r="936" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B936">
-        <v>9029</v>
+        <v>9046</v>
       </c>
       <c r="E936">
         <v>0</v>
@@ -8329,7 +8468,7 @@
     </row>
     <row r="937" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B937">
-        <v>9030</v>
+        <v>9047</v>
       </c>
       <c r="E937">
         <v>0</v>
@@ -8337,7 +8476,7 @@
     </row>
     <row r="938" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B938">
-        <v>9031</v>
+        <v>9048</v>
       </c>
       <c r="E938">
         <v>0</v>
@@ -8345,7 +8484,7 @@
     </row>
     <row r="939" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B939">
-        <v>9032</v>
+        <v>9049</v>
       </c>
       <c r="E939">
         <v>0</v>
@@ -8353,7 +8492,7 @@
     </row>
     <row r="940" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B940">
-        <v>9033</v>
+        <v>9050</v>
       </c>
       <c r="E940">
         <v>0</v>
@@ -8361,7 +8500,7 @@
     </row>
     <row r="941" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B941">
-        <v>9034</v>
+        <v>9051</v>
       </c>
       <c r="E941">
         <v>0</v>
@@ -8369,7 +8508,7 @@
     </row>
     <row r="942" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B942">
-        <v>9036</v>
+        <v>9052</v>
       </c>
       <c r="E942">
         <v>0</v>
@@ -8377,7 +8516,7 @@
     </row>
     <row r="943" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B943">
-        <v>9037</v>
+        <v>9053</v>
       </c>
       <c r="E943">
         <v>0</v>
@@ -8385,7 +8524,7 @@
     </row>
     <row r="944" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B944">
-        <v>9038</v>
+        <v>9054</v>
       </c>
       <c r="E944">
         <v>0</v>
@@ -8393,7 +8532,7 @@
     </row>
     <row r="945" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B945">
-        <v>9039</v>
+        <v>9055</v>
       </c>
       <c r="E945">
         <v>0</v>
@@ -8401,7 +8540,7 @@
     </row>
     <row r="946" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B946">
-        <v>9040</v>
+        <v>9056</v>
       </c>
       <c r="E946">
         <v>0</v>
@@ -8409,7 +8548,7 @@
     </row>
     <row r="947" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B947">
-        <v>9041</v>
+        <v>9057</v>
       </c>
       <c r="E947">
         <v>0</v>
@@ -8417,7 +8556,7 @@
     </row>
     <row r="948" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B948">
-        <v>9042</v>
+        <v>9058</v>
       </c>
       <c r="E948">
         <v>0</v>
@@ -8425,7 +8564,7 @@
     </row>
     <row r="949" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B949">
-        <v>9043</v>
+        <v>9059</v>
       </c>
       <c r="E949">
         <v>0</v>
@@ -8433,7 +8572,7 @@
     </row>
     <row r="950" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B950">
-        <v>9044</v>
+        <v>9060</v>
       </c>
       <c r="E950">
         <v>0</v>
@@ -8441,7 +8580,7 @@
     </row>
     <row r="951" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B951">
-        <v>9045</v>
+        <v>9061</v>
       </c>
       <c r="E951">
         <v>0</v>
@@ -8449,7 +8588,7 @@
     </row>
     <row r="952" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B952">
-        <v>9046</v>
+        <v>9068</v>
       </c>
       <c r="E952">
         <v>0</v>
@@ -8457,7 +8596,7 @@
     </row>
     <row r="953" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B953">
-        <v>9047</v>
+        <v>9069</v>
       </c>
       <c r="E953">
         <v>0</v>
@@ -8465,7 +8604,7 @@
     </row>
     <row r="954" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B954">
-        <v>9048</v>
+        <v>9070</v>
       </c>
       <c r="E954">
         <v>0</v>
@@ -8473,7 +8612,7 @@
     </row>
     <row r="955" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B955">
-        <v>9049</v>
+        <v>9071</v>
       </c>
       <c r="E955">
         <v>0</v>
@@ -8481,7 +8620,7 @@
     </row>
     <row r="956" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B956">
-        <v>9050</v>
+        <v>9072</v>
       </c>
       <c r="E956">
         <v>0</v>
@@ -8489,7 +8628,7 @@
     </row>
     <row r="957" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B957">
-        <v>9051</v>
+        <v>9073</v>
       </c>
       <c r="E957">
         <v>0</v>
@@ -8497,7 +8636,7 @@
     </row>
     <row r="958" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B958">
-        <v>9052</v>
+        <v>9074</v>
       </c>
       <c r="E958">
         <v>0</v>
@@ -8505,7 +8644,7 @@
     </row>
     <row r="959" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B959">
-        <v>9053</v>
+        <v>9077</v>
       </c>
       <c r="E959">
         <v>0</v>
@@ -8513,7 +8652,7 @@
     </row>
     <row r="960" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B960">
-        <v>9054</v>
+        <v>9075</v>
       </c>
       <c r="E960">
         <v>0</v>
@@ -8521,7 +8660,7 @@
     </row>
     <row r="961" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B961">
-        <v>9055</v>
+        <v>9078</v>
       </c>
       <c r="E961">
         <v>0</v>
@@ -8529,7 +8668,7 @@
     </row>
     <row r="962" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B962">
-        <v>9056</v>
+        <v>9079</v>
       </c>
       <c r="E962">
         <v>0</v>
@@ -8537,7 +8676,7 @@
     </row>
     <row r="963" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B963">
-        <v>9057</v>
+        <v>9080</v>
       </c>
       <c r="E963">
         <v>0</v>
@@ -8545,7 +8684,7 @@
     </row>
     <row r="964" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B964">
-        <v>9058</v>
+        <v>9081</v>
       </c>
       <c r="E964">
         <v>0</v>
@@ -8553,7 +8692,7 @@
     </row>
     <row r="965" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B965">
-        <v>9059</v>
+        <v>9082</v>
       </c>
       <c r="E965">
         <v>0</v>
@@ -8561,7 +8700,7 @@
     </row>
     <row r="966" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B966">
-        <v>9060</v>
+        <v>9083</v>
       </c>
       <c r="E966">
         <v>0</v>
@@ -8569,7 +8708,7 @@
     </row>
     <row r="967" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B967">
-        <v>9061</v>
+        <v>9084</v>
       </c>
       <c r="E967">
         <v>0</v>
@@ -8577,7 +8716,7 @@
     </row>
     <row r="968" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B968">
-        <v>9068</v>
+        <v>9085</v>
       </c>
       <c r="E968">
         <v>0</v>
@@ -8585,7 +8724,7 @@
     </row>
     <row r="969" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B969">
-        <v>9069</v>
+        <v>9086</v>
       </c>
       <c r="E969">
         <v>0</v>
@@ -8593,7 +8732,7 @@
     </row>
     <row r="970" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B970">
-        <v>9070</v>
+        <v>9087</v>
       </c>
       <c r="E970">
         <v>0</v>
@@ -8601,7 +8740,7 @@
     </row>
     <row r="971" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B971">
-        <v>9071</v>
+        <v>9088</v>
       </c>
       <c r="E971">
         <v>0</v>
@@ -8609,7 +8748,7 @@
     </row>
     <row r="972" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B972">
-        <v>9072</v>
+        <v>9089</v>
       </c>
       <c r="E972">
         <v>0</v>
@@ -8617,7 +8756,7 @@
     </row>
     <row r="973" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B973">
-        <v>9073</v>
+        <v>9090</v>
       </c>
       <c r="E973">
         <v>0</v>
@@ -8625,7 +8764,7 @@
     </row>
     <row r="974" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B974">
-        <v>9074</v>
+        <v>9091</v>
       </c>
       <c r="E974">
         <v>0</v>
@@ -8633,7 +8772,7 @@
     </row>
     <row r="975" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B975">
-        <v>9077</v>
+        <v>9092</v>
       </c>
       <c r="E975">
         <v>0</v>
@@ -8641,7 +8780,7 @@
     </row>
     <row r="976" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B976">
-        <v>9075</v>
+        <v>9093</v>
       </c>
       <c r="E976">
         <v>0</v>
@@ -8649,7 +8788,7 @@
     </row>
     <row r="977" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B977">
-        <v>9078</v>
+        <v>9095</v>
       </c>
       <c r="E977">
         <v>0</v>
@@ -8657,7 +8796,7 @@
     </row>
     <row r="978" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B978">
-        <v>9079</v>
+        <v>9096</v>
       </c>
       <c r="E978">
         <v>0</v>
@@ -8665,7 +8804,7 @@
     </row>
     <row r="979" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B979">
-        <v>9080</v>
+        <v>9097</v>
       </c>
       <c r="E979">
         <v>0</v>
@@ -8673,7 +8812,7 @@
     </row>
     <row r="980" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B980">
-        <v>9081</v>
+        <v>9098</v>
       </c>
       <c r="E980">
         <v>0</v>
@@ -8681,7 +8820,7 @@
     </row>
     <row r="981" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B981">
-        <v>9082</v>
+        <v>9099</v>
       </c>
       <c r="E981">
         <v>0</v>
@@ -8689,7 +8828,7 @@
     </row>
     <row r="982" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B982">
-        <v>9083</v>
+        <v>9100</v>
       </c>
       <c r="E982">
         <v>0</v>
@@ -8697,7 +8836,7 @@
     </row>
     <row r="983" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B983">
-        <v>9084</v>
+        <v>9101</v>
       </c>
       <c r="E983">
         <v>0</v>
@@ -8705,7 +8844,7 @@
     </row>
     <row r="984" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B984">
-        <v>9085</v>
+        <v>9102</v>
       </c>
       <c r="E984">
         <v>0</v>
@@ -8713,7 +8852,7 @@
     </row>
     <row r="985" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B985">
-        <v>9086</v>
+        <v>9103</v>
       </c>
       <c r="E985">
         <v>0</v>
@@ -8721,7 +8860,7 @@
     </row>
     <row r="986" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B986">
-        <v>9087</v>
+        <v>9104</v>
       </c>
       <c r="E986">
         <v>0</v>
@@ -8729,7 +8868,7 @@
     </row>
     <row r="987" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B987">
-        <v>9088</v>
+        <v>9105</v>
       </c>
       <c r="E987">
         <v>0</v>
@@ -8737,7 +8876,7 @@
     </row>
     <row r="988" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B988">
-        <v>9089</v>
+        <v>9106</v>
       </c>
       <c r="E988">
         <v>0</v>
@@ -8745,7 +8884,7 @@
     </row>
     <row r="989" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B989">
-        <v>9090</v>
+        <v>9107</v>
       </c>
       <c r="E989">
         <v>0</v>
@@ -8753,7 +8892,7 @@
     </row>
     <row r="990" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B990">
-        <v>9091</v>
+        <v>9108</v>
       </c>
       <c r="E990">
         <v>0</v>
@@ -8761,7 +8900,7 @@
     </row>
     <row r="991" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B991">
-        <v>9092</v>
+        <v>9109</v>
       </c>
       <c r="E991">
         <v>0</v>
@@ -8769,7 +8908,7 @@
     </row>
     <row r="992" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B992">
-        <v>9093</v>
+        <v>9110</v>
       </c>
       <c r="E992">
         <v>0</v>
@@ -8777,7 +8916,7 @@
     </row>
     <row r="993" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B993">
-        <v>9095</v>
+        <v>9111</v>
       </c>
       <c r="E993">
         <v>0</v>
@@ -8785,7 +8924,7 @@
     </row>
     <row r="994" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B994">
-        <v>9096</v>
+        <v>9112</v>
       </c>
       <c r="E994">
         <v>0</v>
@@ -8793,7 +8932,7 @@
     </row>
     <row r="995" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B995">
-        <v>9097</v>
+        <v>9113</v>
       </c>
       <c r="E995">
         <v>0</v>
@@ -8801,7 +8940,7 @@
     </row>
     <row r="996" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B996">
-        <v>9098</v>
+        <v>9114</v>
       </c>
       <c r="E996">
         <v>0</v>
@@ -8809,7 +8948,7 @@
     </row>
     <row r="997" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B997">
-        <v>9099</v>
+        <v>9115</v>
       </c>
       <c r="E997">
         <v>0</v>
@@ -8817,7 +8956,7 @@
     </row>
     <row r="998" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B998">
-        <v>9100</v>
+        <v>9116</v>
       </c>
       <c r="E998">
         <v>0</v>
@@ -8825,7 +8964,7 @@
     </row>
     <row r="999" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B999">
-        <v>9101</v>
+        <v>9117</v>
       </c>
       <c r="E999">
         <v>0</v>
@@ -8833,7 +8972,7 @@
     </row>
     <row r="1000" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1000">
-        <v>9102</v>
+        <v>9118</v>
       </c>
       <c r="E1000">
         <v>0</v>
@@ -8841,7 +8980,7 @@
     </row>
     <row r="1001" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1001">
-        <v>9103</v>
+        <v>9121</v>
       </c>
       <c r="E1001">
         <v>0</v>
@@ -8849,7 +8988,7 @@
     </row>
     <row r="1002" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1002">
-        <v>9104</v>
+        <v>9122</v>
       </c>
       <c r="E1002">
         <v>0</v>
@@ -8857,7 +8996,7 @@
     </row>
     <row r="1003" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1003">
-        <v>9105</v>
+        <v>9123</v>
       </c>
       <c r="E1003">
         <v>0</v>
@@ -8865,7 +9004,7 @@
     </row>
     <row r="1004" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1004">
-        <v>9106</v>
+        <v>9124</v>
       </c>
       <c r="E1004">
         <v>0</v>
@@ -8873,7 +9012,7 @@
     </row>
     <row r="1005" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1005">
-        <v>9107</v>
+        <v>9125</v>
       </c>
       <c r="E1005">
         <v>0</v>
@@ -8881,7 +9020,7 @@
     </row>
     <row r="1006" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1006">
-        <v>9108</v>
+        <v>9126</v>
       </c>
       <c r="E1006">
         <v>0</v>
@@ -8889,7 +9028,7 @@
     </row>
     <row r="1007" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1007">
-        <v>9109</v>
+        <v>9127</v>
       </c>
       <c r="E1007">
         <v>0</v>
@@ -8897,7 +9036,7 @@
     </row>
     <row r="1008" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1008">
-        <v>9110</v>
+        <v>9128</v>
       </c>
       <c r="E1008">
         <v>0</v>
@@ -8905,7 +9044,7 @@
     </row>
     <row r="1009" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1009">
-        <v>9111</v>
+        <v>9131</v>
       </c>
       <c r="E1009">
         <v>0</v>
@@ -8913,7 +9052,7 @@
     </row>
     <row r="1010" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1010">
-        <v>9112</v>
+        <v>9136</v>
       </c>
       <c r="E1010">
         <v>0</v>
@@ -8921,7 +9060,7 @@
     </row>
     <row r="1011" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1011">
-        <v>9113</v>
+        <v>9137</v>
       </c>
       <c r="E1011">
         <v>0</v>
@@ -8929,7 +9068,7 @@
     </row>
     <row r="1012" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1012">
-        <v>9114</v>
+        <v>9141</v>
       </c>
       <c r="E1012">
         <v>0</v>
@@ -8937,7 +9076,7 @@
     </row>
     <row r="1013" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1013">
-        <v>9115</v>
+        <v>9142</v>
       </c>
       <c r="E1013">
         <v>0</v>
@@ -8945,7 +9084,7 @@
     </row>
     <row r="1014" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1014">
-        <v>9116</v>
+        <v>9153</v>
       </c>
       <c r="E1014">
         <v>0</v>
@@ -8953,7 +9092,7 @@
     </row>
     <row r="1015" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1015">
-        <v>9117</v>
+        <v>9165</v>
       </c>
       <c r="E1015">
         <v>0</v>
@@ -8961,7 +9100,7 @@
     </row>
     <row r="1016" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1016">
-        <v>9118</v>
+        <v>9263</v>
       </c>
       <c r="E1016">
         <v>0</v>
@@ -8969,7 +9108,7 @@
     </row>
     <row r="1017" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1017">
-        <v>9121</v>
+        <v>9264</v>
       </c>
       <c r="E1017">
         <v>0</v>
@@ -8977,7 +9116,7 @@
     </row>
     <row r="1018" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1018">
-        <v>9122</v>
+        <v>9265</v>
       </c>
       <c r="E1018">
         <v>0</v>
@@ -8985,7 +9124,7 @@
     </row>
     <row r="1019" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1019">
-        <v>9123</v>
+        <v>9266</v>
       </c>
       <c r="E1019">
         <v>0</v>
@@ -8993,7 +9132,7 @@
     </row>
     <row r="1020" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1020">
-        <v>9124</v>
+        <v>9268</v>
       </c>
       <c r="E1020">
         <v>0</v>
@@ -9001,7 +9140,7 @@
     </row>
     <row r="1021" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1021">
-        <v>9125</v>
+        <v>9322</v>
       </c>
       <c r="E1021">
         <v>0</v>
@@ -9009,7 +9148,7 @@
     </row>
     <row r="1022" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1022">
-        <v>9126</v>
+        <v>9323</v>
       </c>
       <c r="E1022">
         <v>0</v>
@@ -9017,7 +9156,7 @@
     </row>
     <row r="1023" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1023">
-        <v>9127</v>
+        <v>9324</v>
       </c>
       <c r="E1023">
         <v>0</v>
@@ -9025,7 +9164,7 @@
     </row>
     <row r="1024" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1024">
-        <v>9128</v>
+        <v>9325</v>
       </c>
       <c r="E1024">
         <v>0</v>
@@ -9033,7 +9172,7 @@
     </row>
     <row r="1025" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1025">
-        <v>9131</v>
+        <v>9326</v>
       </c>
       <c r="E1025">
         <v>0</v>
@@ -9041,7 +9180,7 @@
     </row>
     <row r="1026" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1026">
-        <v>9136</v>
+        <v>9327</v>
       </c>
       <c r="E1026">
         <v>0</v>
@@ -9049,7 +9188,7 @@
     </row>
     <row r="1027" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1027">
-        <v>9137</v>
+        <v>9330</v>
       </c>
       <c r="E1027">
         <v>0</v>
@@ -9057,7 +9196,7 @@
     </row>
     <row r="1028" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1028">
-        <v>9141</v>
+        <v>9331</v>
       </c>
       <c r="E1028">
         <v>0</v>
@@ -9065,7 +9204,7 @@
     </row>
     <row r="1029" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1029">
-        <v>9142</v>
+        <v>9332</v>
       </c>
       <c r="E1029">
         <v>0</v>
@@ -9073,7 +9212,7 @@
     </row>
     <row r="1030" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1030">
-        <v>9153</v>
+        <v>9338</v>
       </c>
       <c r="E1030">
         <v>0</v>
@@ -9081,170 +9220,191 @@
     </row>
     <row r="1031" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1031">
-        <v>9165</v>
+        <v>12752</v>
       </c>
       <c r="E1031">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1032" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1032">
+        <v>12753</v>
+      </c>
       <c r="E1032">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1033" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1033">
+        <v>12772</v>
+      </c>
       <c r="E1033">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1034" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1034">
+        <v>12775</v>
+      </c>
       <c r="E1034">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1035" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1035">
+        <v>12776</v>
+      </c>
       <c r="E1035">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1036" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1036">
+        <v>12777</v>
+      </c>
       <c r="E1036">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1037" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1037">
+        <v>12782</v>
+      </c>
       <c r="E1037">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1038" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1038">
-        <v>9263</v>
+        <v>12783</v>
       </c>
       <c r="E1038">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1039" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1039">
-        <v>9264</v>
+        <v>12784</v>
       </c>
       <c r="E1039">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1040" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1040">
-        <v>9265</v>
+        <v>12808</v>
       </c>
       <c r="E1040">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1041" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1041">
-        <v>9266</v>
+        <v>12811</v>
       </c>
       <c r="E1041">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1042" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1042">
-        <v>9268</v>
+        <v>13081</v>
       </c>
       <c r="E1042">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1043" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1043">
+        <v>13082</v>
+      </c>
       <c r="E1043">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1044" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1044">
-        <v>9322</v>
+        <v>13405</v>
       </c>
       <c r="E1044">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1045" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1045">
-        <v>9323</v>
+        <v>13408</v>
       </c>
       <c r="E1045">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1046" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1046">
-        <v>9324</v>
+        <v>13409</v>
       </c>
       <c r="E1046">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1047" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1047">
-        <v>9325</v>
+        <v>13410</v>
       </c>
       <c r="E1047">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1048" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1048">
-        <v>9326</v>
+        <v>13411</v>
       </c>
       <c r="E1048">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1049" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1049">
-        <v>9327</v>
+        <v>13430</v>
       </c>
       <c r="E1049">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1050" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1050">
-        <v>9330</v>
+        <v>13432</v>
       </c>
       <c r="E1050">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1051" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1051">
-        <v>9331</v>
+        <v>13483</v>
       </c>
       <c r="E1051">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1052" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1052">
-        <v>9332</v>
+        <v>13484</v>
       </c>
       <c r="E1052">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1053" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1053">
-        <v>9338</v>
+        <v>13932</v>
       </c>
       <c r="E1053">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1054" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1054">
-        <v>12752</v>
+        <v>14022</v>
       </c>
       <c r="E1054">
         <v>2</v>
@@ -9252,7 +9412,7 @@
     </row>
     <row r="1055" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1055">
-        <v>12753</v>
+        <v>14036</v>
       </c>
       <c r="E1055">
         <v>2</v>
@@ -9260,7 +9420,7 @@
     </row>
     <row r="1056" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1056">
-        <v>12772</v>
+        <v>14081</v>
       </c>
       <c r="E1056">
         <v>2</v>
@@ -9268,7 +9428,7 @@
     </row>
     <row r="1057" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1057">
-        <v>12775</v>
+        <v>14082</v>
       </c>
       <c r="E1057">
         <v>2</v>
@@ -9276,7 +9436,7 @@
     </row>
     <row r="1058" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1058">
-        <v>12776</v>
+        <v>14111</v>
       </c>
       <c r="E1058">
         <v>2</v>
@@ -9284,7 +9444,7 @@
     </row>
     <row r="1059" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1059">
-        <v>12777</v>
+        <v>14179</v>
       </c>
       <c r="E1059">
         <v>2</v>
@@ -9292,7 +9452,7 @@
     </row>
     <row r="1060" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1060">
-        <v>12782</v>
+        <v>14180</v>
       </c>
       <c r="E1060">
         <v>2</v>
@@ -9300,7 +9460,7 @@
     </row>
     <row r="1061" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1061">
-        <v>12783</v>
+        <v>14182</v>
       </c>
       <c r="E1061">
         <v>2</v>
@@ -9308,7 +9468,7 @@
     </row>
     <row r="1062" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1062">
-        <v>12784</v>
+        <v>14183</v>
       </c>
       <c r="E1062">
         <v>2</v>
@@ -9316,7 +9476,7 @@
     </row>
     <row r="1063" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1063">
-        <v>12808</v>
+        <v>24611</v>
       </c>
       <c r="E1063">
         <v>2</v>
@@ -9324,7 +9484,7 @@
     </row>
     <row r="1064" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1064">
-        <v>12811</v>
+        <v>24615</v>
       </c>
       <c r="E1064">
         <v>2</v>
@@ -9332,314 +9492,365 @@
     </row>
     <row r="1065" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1065">
-        <v>13081</v>
+        <v>8371</v>
       </c>
       <c r="E1065">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1066" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1066">
-        <v>13082</v>
+        <v>8494</v>
       </c>
       <c r="E1066">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1067" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1067">
-        <v>13405</v>
+        <v>8511</v>
       </c>
       <c r="E1067">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1068" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1068">
-        <v>13408</v>
+        <v>8513</v>
       </c>
       <c r="E1068">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1069" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1069">
-        <v>13409</v>
+        <v>8700</v>
       </c>
       <c r="E1069">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1070" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1070">
-        <v>13410</v>
+        <v>8802</v>
       </c>
       <c r="E1070">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1071" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B1071">
-        <v>13411</v>
-      </c>
       <c r="E1071">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1072" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1072">
-        <v>13430</v>
+        <v>9267</v>
       </c>
       <c r="E1072">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1073" spans="2:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1073">
-        <v>13432</v>
+        <v>9813</v>
       </c>
       <c r="E1073">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1074" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1074">
-        <v>13483</v>
+        <v>11525</v>
       </c>
       <c r="E1074">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1075" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1075">
-        <v>13484</v>
+        <v>11523</v>
       </c>
       <c r="E1075">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1076" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1076">
-        <v>13932</v>
+        <v>11488</v>
       </c>
       <c r="E1076">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1077" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1077">
-        <v>14022</v>
+        <v>11482</v>
       </c>
       <c r="E1077">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1078" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1078">
-        <v>14036</v>
+        <v>11481</v>
       </c>
       <c r="E1078">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1079" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1079">
-        <v>14081</v>
+        <v>11492</v>
       </c>
       <c r="E1079">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1080" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1080" t="s">
+        <v>88</v>
+      </c>
       <c r="B1080">
-        <v>14082</v>
-      </c>
-      <c r="E1080">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1081" spans="2:5" x14ac:dyDescent="0.25">
+        <v>10958</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1081" t="s">
+        <v>88</v>
+      </c>
       <c r="B1081">
-        <v>14111</v>
-      </c>
-      <c r="E1081">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1082" spans="2:5" x14ac:dyDescent="0.25">
+        <v>10806</v>
+      </c>
+      <c r="D1081" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1082" t="s">
+        <v>88</v>
+      </c>
       <c r="B1082">
-        <v>14179</v>
-      </c>
-      <c r="E1082">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1083" spans="2:5" x14ac:dyDescent="0.25">
+        <v>10191</v>
+      </c>
+      <c r="D1082" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1083" t="s">
+        <v>86</v>
+      </c>
       <c r="B1083">
-        <v>14180</v>
-      </c>
-      <c r="E1083">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1084" spans="2:5" x14ac:dyDescent="0.25">
+        <v>10191</v>
+      </c>
+      <c r="D1083" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1084" t="s">
+        <v>86</v>
+      </c>
       <c r="B1084">
-        <v>14182</v>
-      </c>
-      <c r="E1084">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1085" spans="2:5" x14ac:dyDescent="0.25">
+        <v>9541</v>
+      </c>
+      <c r="D1084" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1085" t="s">
+        <v>86</v>
+      </c>
       <c r="B1085">
-        <v>14183</v>
-      </c>
-      <c r="E1085">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1086" spans="2:5" x14ac:dyDescent="0.25">
+        <v>9542</v>
+      </c>
+      <c r="D1085" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1086" t="s">
+        <v>86</v>
+      </c>
       <c r="B1086">
-        <v>24611</v>
-      </c>
-      <c r="E1086">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1087" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1003</v>
+      </c>
+      <c r="D1086" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1087">
-        <v>24615</v>
+        <v>1238</v>
       </c>
       <c r="E1087">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="1088" spans="2:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1088" t="s">
+        <v>86</v>
+      </c>
       <c r="B1088">
-        <v>8371</v>
-      </c>
-      <c r="E1088">
-        <v>0</v>
+        <v>663</v>
+      </c>
+      <c r="D1088" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="1089" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1089" t="s">
+        <v>88</v>
+      </c>
       <c r="B1089">
-        <v>8494</v>
-      </c>
-      <c r="E1089">
-        <v>0</v>
+        <v>488</v>
+      </c>
+      <c r="D1089" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="1090" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1090" t="s">
+        <v>86</v>
+      </c>
       <c r="B1090">
-        <v>8511</v>
-      </c>
-      <c r="E1090">
-        <v>0</v>
+        <v>488</v>
+      </c>
+      <c r="D1090" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="1091" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1091" t="s">
+        <v>86</v>
+      </c>
       <c r="B1091">
-        <v>8513</v>
-      </c>
-      <c r="E1091">
-        <v>0</v>
+        <v>489</v>
+      </c>
+      <c r="D1091" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="1092" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1092">
-        <v>8700</v>
+        <v>9621</v>
       </c>
       <c r="E1092">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1093" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1093">
-        <v>8802</v>
+        <v>9812</v>
       </c>
       <c r="E1093">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1094" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1094">
+        <v>9180</v>
+      </c>
       <c r="E1094">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1095" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1095" t="s">
+        <v>88</v>
+      </c>
       <c r="B1095">
-        <v>9267</v>
-      </c>
-      <c r="E1095">
-        <v>0</v>
+        <v>7728</v>
+      </c>
+      <c r="D1095" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="1096" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1096">
-        <v>9813</v>
-      </c>
-      <c r="E1096">
-        <v>1</v>
+      <c r="A1096" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1096" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="1097" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1097" t="s">
+        <v>88</v>
+      </c>
       <c r="B1097">
-        <v>11525</v>
-      </c>
-      <c r="E1097">
-        <v>1</v>
+        <v>4501</v>
+      </c>
+      <c r="D1097" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="1098" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1098" t="s">
+        <v>88</v>
+      </c>
       <c r="B1098">
-        <v>11523</v>
-      </c>
-      <c r="E1098">
-        <v>1</v>
+        <v>4022</v>
+      </c>
+      <c r="D1098" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="1099" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1099" t="s">
+        <v>88</v>
+      </c>
       <c r="B1099">
-        <v>11488</v>
-      </c>
-      <c r="E1099">
-        <v>1</v>
+        <v>8479</v>
+      </c>
+      <c r="D1099" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="1100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1100" t="s">
+        <v>86</v>
+      </c>
       <c r="B1100">
-        <v>11482</v>
-      </c>
-      <c r="E1100">
-        <v>1</v>
+        <v>8479</v>
+      </c>
+      <c r="D1100" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="1101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1101" t="s">
+        <v>86</v>
+      </c>
       <c r="B1101">
-        <v>11481</v>
-      </c>
-      <c r="E1101">
-        <v>1</v>
+        <v>477</v>
+      </c>
+      <c r="D1101" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="1102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1102" t="s">
+        <v>88</v>
+      </c>
       <c r="B1102">
-        <v>11492</v>
-      </c>
-      <c r="E1102">
-        <v>1</v>
+        <v>1058</v>
+      </c>
+      <c r="D1102" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="1103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1103" t="s">
-        <v>88</v>
-      </c>
       <c r="B1103">
-        <v>10958</v>
-      </c>
-      <c r="D1103" t="s">
-        <v>111</v>
+        <v>10593</v>
+      </c>
+      <c r="E1103">
+        <v>1</v>
       </c>
     </row>
     <row r="1104" spans="1:5" x14ac:dyDescent="0.25">
@@ -9647,193 +9858,21 @@
         <v>88</v>
       </c>
       <c r="B1104">
-        <v>10806</v>
-      </c>
-      <c r="D1104" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="1105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1105" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1105">
-        <v>10191</v>
-      </c>
-      <c r="D1105" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="1106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1106" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1106">
-        <v>10191</v>
-      </c>
-      <c r="D1106" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="1107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1107" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1107">
-        <v>9541</v>
-      </c>
-      <c r="D1107" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="1108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1108" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1108">
-        <v>9542</v>
-      </c>
-      <c r="D1108" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="1109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1109" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1109">
-        <v>1003</v>
-      </c>
-      <c r="D1109" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="1110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1110">
-        <v>1238</v>
-      </c>
-      <c r="E1110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1111" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1111">
-        <v>663</v>
-      </c>
-      <c r="D1111" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="1112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1112" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1112">
-        <v>488</v>
-      </c>
-      <c r="D1112" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="1113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1113" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1113">
-        <v>488</v>
-      </c>
-      <c r="D1113" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="1114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1114" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1114">
-        <v>489</v>
-      </c>
-      <c r="D1114" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="1115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1115">
-        <v>9621</v>
-      </c>
-      <c r="E1115">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1116">
-        <v>9812</v>
-      </c>
-      <c r="E1116">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1117">
-        <v>9180</v>
-      </c>
-      <c r="E1117">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1118" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1118">
-        <v>7728</v>
-      </c>
-      <c r="D1118" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="1119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1119" t="s">
-        <v>125</v>
-      </c>
-      <c r="D1119" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="1120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1120" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1120">
-        <v>4501</v>
-      </c>
-      <c r="D1120" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="1121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1121" t="s">
-        <v>88</v>
-      </c>
-      <c r="B1121">
-        <v>4022</v>
-      </c>
-      <c r="D1121" t="s">
-        <v>128</v>
+        <v>12720</v>
+      </c>
+      <c r="D1104" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B486:B1106 B2:B484 B1108:B1111">
-    <cfRule type="duplicateValues" dxfId="5" priority="96"/>
+  <conditionalFormatting sqref="B59:B113 B17:B57">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B59:B113 B17:B57">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+  <conditionalFormatting sqref="B1085:B1088 B486:B1083 B2:B484">
+    <cfRule type="duplicateValues" dxfId="4" priority="96"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9841,7 +9880,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D60A7C4-82C4-4AAF-A00A-127D625F91A3}">
-  <dimension ref="A1:H708"/>
+  <dimension ref="A1:H729"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13416,7 +13455,7 @@
         <v>5398</v>
       </c>
       <c r="E418" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
@@ -15722,7 +15761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="705" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A705">
         <v>16131</v>
       </c>
@@ -15730,7 +15769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="706" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A706">
         <v>16283</v>
       </c>
@@ -15738,7 +15777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="707" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A707">
         <v>17069</v>
       </c>
@@ -15746,12 +15785,180 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A708">
         <v>17072</v>
       </c>
       <c r="B708">
         <v>0</v>
+      </c>
+    </row>
+    <row r="709" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A709">
+        <v>25200</v>
+      </c>
+      <c r="B709">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="710" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A710">
+        <v>25207</v>
+      </c>
+      <c r="B710">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="711" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A711">
+        <v>23988</v>
+      </c>
+      <c r="B711">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="712" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A712">
+        <v>28209</v>
+      </c>
+      <c r="B712">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="713" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A713">
+        <v>25202</v>
+      </c>
+      <c r="B713">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="714" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A714">
+        <v>28210</v>
+      </c>
+      <c r="B714">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="715" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A715">
+        <v>23618</v>
+      </c>
+      <c r="E715" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="716" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A716">
+        <v>30562</v>
+      </c>
+      <c r="E716" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="717" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A717">
+        <v>28760</v>
+      </c>
+      <c r="E717" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="718" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A718">
+        <v>28500</v>
+      </c>
+      <c r="E718" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="719" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A719">
+        <v>28471</v>
+      </c>
+      <c r="E719" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="720" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A720">
+        <v>29195</v>
+      </c>
+      <c r="E720" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="721" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A721">
+        <v>29196</v>
+      </c>
+      <c r="E721" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="722" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A722">
+        <v>28474</v>
+      </c>
+      <c r="E722" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="723" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A723">
+        <v>29194</v>
+      </c>
+      <c r="E723" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="724" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A724">
+        <v>23951</v>
+      </c>
+      <c r="B724">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="725" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A725">
+        <v>50961</v>
+      </c>
+      <c r="B725">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="726" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A726">
+        <v>17468</v>
+      </c>
+      <c r="E726" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="727" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A727">
+        <v>24208</v>
+      </c>
+      <c r="E727" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="728" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A728">
+        <v>28908</v>
+      </c>
+      <c r="E728" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="729" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A729">
+        <v>28943</v>
+      </c>
+      <c r="E729" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/corrections/corrections.xlsx
+++ b/corrections/corrections.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Desktop\wow_vo_webui\corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF6A1CE-99B8-4F11-8281-D8418C429E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784CA0AC-AC1B-4D17-8648-2FB606D3C093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="quest" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="143">
   <si>
     <t>source</t>
   </si>
@@ -491,6 +491,31 @@
     <t>In my travels across this world I have made several interesting discoveries. For instance, did you know that with the proper amount of encouragement one can extract all the truths that a man dares hide? As luck would have it, I happen to have some encouragement on hand.
 These are my persuaders; Equip them and take to the field, death knight; Apply the pointy ends to the soldiers of New Avalon; Discover the truth about this "Crimson Dawn."</t>
   </si>
+  <si>
+    <t>Your beliefs are alien to us, heathen. Ancient Zandalar were once branded as heretics. This was when the Gurubashi Empire was strong. Heathens dared to challenge the priest of Hakkar. Heathens then were hunted and killed as vermin. Those heathens never wavered in their fight against the Blood God. We honor the price they paid. They are the freethinkers.
+Destroy the minions of Hakkar in Zul'Gurub; Bring me the Paragons of Power I seek; Success will be greatly rewarded.
+Go.</t>
+  </si>
+  <si>
+    <t>pirate</t>
+  </si>
+  <si>
+    <t>What's this? With the four sigils brought together, they have formed together to create one sigil. There can be no doubt that this will be able to break the wardings placed upon Trollbane's tomb.
+Trollbane's remains are entombed in the Sanctum behind the chapel in Stromgarde; Retrieve Trol'kalar.</t>
+  </si>
+  <si>
+    <t>The light slowly fades; the sword Trol'kalar, held within a stone sheath has been released.</t>
+  </si>
+  <si>
+    <t>Well done, adventurer; That's one less forge camp we'll need to worry about. It'll take the Legion a while to get that facility back up and running. You've just bought us the one thing we'd run out of; time.</t>
+  </si>
+  <si>
+    <t>You are an honor to us, But now we must strike before the Legion recovers! To the north of Thrallmar lies Invasion Point Annihilator; It houses a warp-portal through which the Legion draws its reinforcements.
+You must overload that portal - and blast it back to the abyss it came from. The portal's activation key will be held by the Point's commander - Warbringer Arix'Amal. Slay him. Take the key. Use it on the portal and do what must be done. May the warchief's blessings be with you.</t>
+  </si>
+  <si>
+    <t>Greetings, adventurer; I've deciphered the Legion missive and uncovered the demons' strategic plans for this Peninsula. Apparently, there is a large group of hellish terrorfiends gathering near the Pools of Aggonar in the west. We cannot allow such a force to go unchallenged. You must go there and decimate their cursed numbers.</t>
+  </si>
 </sst>
 </file>
 
@@ -879,7 +904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56545B79-22C0-4057-A076-1E697524330B}">
-  <dimension ref="A1:F1104"/>
+  <dimension ref="A1:F1110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9860,8 +9885,74 @@
       <c r="B1104">
         <v>12720</v>
       </c>
-      <c r="D1104" s="1" t="s">
+      <c r="D1104" t="s">
         <v>135</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1105" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1105">
+        <v>8054</v>
+      </c>
+      <c r="D1105" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1106" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1106">
+        <v>645</v>
+      </c>
+      <c r="D1106" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1107" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1107">
+        <v>646</v>
+      </c>
+      <c r="D1107" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1108" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1108">
+        <v>10390</v>
+      </c>
+      <c r="D1108" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1109" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1109">
+        <v>10392</v>
+      </c>
+      <c r="D1109" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1110" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1110">
+        <v>10389</v>
+      </c>
+      <c r="D1110" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -9880,7 +9971,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D60A7C4-82C4-4AAF-A00A-127D625F91A3}">
-  <dimension ref="A1:H729"/>
+  <dimension ref="A1:H734"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -12575,7 +12666,7 @@
         <v>17877</v>
       </c>
       <c r="E308" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
@@ -13295,7 +13386,7 @@
         <v>2610</v>
       </c>
       <c r="E398" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
@@ -15959,6 +16050,46 @@
       </c>
       <c r="E729" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="730" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A730">
+        <v>23995</v>
+      </c>
+      <c r="B730">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="731" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A731">
+        <v>29590</v>
+      </c>
+      <c r="B731">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="732" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A732">
+        <v>28552</v>
+      </c>
+      <c r="B732">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="733" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A733">
+        <v>24975</v>
+      </c>
+      <c r="B733">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="734" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A734">
+        <v>18063</v>
+      </c>
+      <c r="E734" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/corrections/corrections.xlsx
+++ b/corrections/corrections.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Desktop\wow_vo_webui\corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E193BF-E080-4324-9DA8-CBFB6B69A8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F0F9D6-FC09-45EF-8920-F717AB567297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">npc!$A$1:$H$780</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">quest!$A$1:$F$1345</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="350">
   <si>
     <t>source</t>
   </si>
@@ -191,9 +192,6 @@
   </si>
   <si>
     <t>nightelf_female</t>
-  </si>
-  <si>
-    <t>big_creature</t>
   </si>
   <si>
     <t>human_female</t>
@@ -460,10 +458,6 @@
   </si>
   <si>
     <t>velen</t>
-  </si>
-  <si>
-    <t>So excited I am; Three little cages for three little elves! But what shall we do with our lovely tree-hugging friends? Why, let's give them a taste of... what do they call it; forest magic! I'll need a good mess of Stone-talon sap; From those horrid felines, bring me some twilight whiskers. This calls for plenty of courser eyes, of course; can never have enough eyes. Oh, and lest we forget, a precious scale from a fey dragon.
-Hurry to Stone-talon Peak, &lt;name&gt;, so I can brew some forest magic!</t>
   </si>
   <si>
     <t>felorc_male</t>
@@ -1414,6 +1408,9 @@
 Because of the protection Blackrock mountain affords Nefarian, it has become increasingly difficult for us to intercede.
 We can, however, empower you, mortal - should you so choose.
 The path before you is one full of peril; You must decide whether to accept our help; Ponder this and speak with me again when a decision has been made.</t>
+  </si>
+  <si>
+    <t>So excited I am; Three little cages for three little elves! But what shall we do with our lovely tree-hugging friends? Why, let's give them a taste of... what do they call it; forest magic! I'll need a good mess of Stone-talon sap; From those horrid felines, bring me some twilight whiskers. This calls for plenty of courser eyes, of course; can never have enough eyes. Oh, and lest we forget, a precious scale from a fey dragon. Hurry to Stone-talon Peak,  so I can brew some forest magic!</t>
   </si>
 </sst>
 </file>
@@ -1449,9 +1446,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1813,7 +1809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56545B79-22C0-4057-A076-1E697524330B}">
-  <dimension ref="A1:F1337"/>
+  <dimension ref="A1:F1345"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5622,51 +5618,51 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B475">
         <v>9538</v>
       </c>
       <c r="D475" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B476">
         <v>10428</v>
       </c>
       <c r="D476" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B477">
         <v>9539</v>
       </c>
       <c r="D477" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B478">
         <v>9540</v>
       </c>
       <c r="D478" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B479">
         <v>6564</v>
@@ -5677,7 +5673,7 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B480">
         <v>9438</v>
@@ -5688,62 +5684,62 @@
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B481">
         <v>10294</v>
       </c>
       <c r="D481" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B482">
         <v>10838</v>
       </c>
       <c r="D482" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B483">
         <v>9820</v>
       </c>
       <c r="D483" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B484">
         <v>10210</v>
       </c>
       <c r="D484" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B485">
         <v>9544</v>
       </c>
       <c r="D485" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B486">
         <v>9576</v>
@@ -5757,134 +5753,134 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B487">
         <v>10216</v>
       </c>
       <c r="D487" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B488">
         <v>10845</v>
       </c>
       <c r="D488" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B489">
         <v>9870</v>
       </c>
       <c r="D489" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B490">
         <v>9859</v>
       </c>
       <c r="D490" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B491">
         <v>9865</v>
       </c>
       <c r="D491" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B492">
         <v>10134</v>
       </c>
       <c r="D492" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B493">
         <v>9636</v>
       </c>
       <c r="D493" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B494">
         <v>9923</v>
       </c>
       <c r="D494" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B495">
         <v>9869</v>
       </c>
       <c r="D495" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B496">
         <v>10009</v>
       </c>
       <c r="D496" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B497">
         <v>10010</v>
       </c>
       <c r="D497" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B498">
         <v>10703</v>
       </c>
       <c r="D498" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
@@ -5929,7 +5925,7 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B504">
         <v>831</v>
@@ -5940,7 +5936,7 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B505">
         <v>831</v>
@@ -6007,7 +6003,7 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B513">
         <v>1393</v>
@@ -10543,79 +10539,79 @@
     </row>
     <row r="1080" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1080">
         <v>10958</v>
       </c>
       <c r="D1080" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1081" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1081">
         <v>10806</v>
       </c>
       <c r="D1081" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1082" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1082">
         <v>10191</v>
       </c>
       <c r="D1082" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1083" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1083">
         <v>10191</v>
       </c>
       <c r="D1083" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="1084" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1084">
         <v>9541</v>
       </c>
       <c r="D1084" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1085" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1085">
         <v>9542</v>
       </c>
       <c r="D1085" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="1086" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1086">
         <v>1003</v>
       </c>
       <c r="D1086" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1087" spans="1:5" x14ac:dyDescent="0.25">
@@ -10628,46 +10624,46 @@
     </row>
     <row r="1088" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1088">
         <v>663</v>
       </c>
       <c r="D1088" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1089" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1089">
         <v>488</v>
       </c>
       <c r="D1089" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="1090" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1090">
         <v>488</v>
       </c>
       <c r="D1090" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1091" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1091">
         <v>489</v>
       </c>
       <c r="D1091" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1092" spans="1:5" x14ac:dyDescent="0.25">
@@ -10696,87 +10692,87 @@
     </row>
     <row r="1095" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1095">
         <v>7728</v>
       </c>
       <c r="D1095" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1096" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1096" t="s">
         <v>119</v>
-      </c>
-      <c r="D1096" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="1097" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1097">
         <v>4501</v>
       </c>
       <c r="D1097" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1098" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1098">
         <v>4022</v>
       </c>
       <c r="D1098" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1099" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1099">
         <v>8479</v>
       </c>
       <c r="D1099" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1100">
         <v>8479</v>
       </c>
       <c r="D1100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1101">
         <v>477</v>
       </c>
       <c r="D1101" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="1102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1102" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1102">
         <v>1058</v>
       </c>
       <c r="D1102" t="s">
-        <v>127</v>
+        <v>349</v>
       </c>
     </row>
     <row r="1103" spans="1:5" x14ac:dyDescent="0.25">
@@ -10789,128 +10785,128 @@
     </row>
     <row r="1104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1104">
         <v>12720</v>
       </c>
       <c r="D1104" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1105">
         <v>8054</v>
       </c>
       <c r="D1105" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="1106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1106">
         <v>645</v>
       </c>
       <c r="D1106" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1107">
         <v>646</v>
       </c>
       <c r="D1107" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="1108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1108">
         <v>10390</v>
       </c>
       <c r="D1108" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1109">
         <v>10392</v>
       </c>
       <c r="D1109" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1110">
         <v>10389</v>
       </c>
       <c r="D1110" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1111" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1111">
         <v>10231</v>
       </c>
       <c r="D1111" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="1112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1112" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1112">
         <v>10983</v>
       </c>
       <c r="D1112" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1113" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B1113">
         <v>9826</v>
       </c>
       <c r="D1113" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1114" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1114">
         <v>9826</v>
       </c>
       <c r="D1114" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="1115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1115" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1115">
         <v>349</v>
@@ -10921,57 +10917,57 @@
     </row>
     <row r="1116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1116" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1116">
         <v>9644</v>
       </c>
       <c r="D1116" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="1117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1117" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1117">
         <v>11007</v>
       </c>
       <c r="D1117" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1118">
         <v>10560</v>
       </c>
       <c r="D1118" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1119" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1119">
         <v>1522</v>
       </c>
       <c r="D1119" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1120">
         <v>586</v>
       </c>
       <c r="D1120" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F1120" t="s">
         <v>33</v>
@@ -10979,7 +10975,7 @@
     </row>
     <row r="1121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1121">
         <v>586</v>
@@ -10998,7 +10994,7 @@
     </row>
     <row r="1123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1123" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1123">
         <v>588</v>
@@ -11009,7 +11005,7 @@
     </row>
     <row r="1124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1124" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1124">
         <v>1261</v>
@@ -11020,513 +11016,513 @@
     </row>
     <row r="1125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1125" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1125">
         <v>11585</v>
       </c>
       <c r="D1125" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="1126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1126">
         <v>11615</v>
       </c>
       <c r="D1126" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1127">
         <v>11636</v>
       </c>
       <c r="D1127" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="1128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1128" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1128">
         <v>11686</v>
       </c>
       <c r="D1128" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1129" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1129">
         <v>11574</v>
       </c>
       <c r="D1129" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1130">
         <v>11716</v>
       </c>
       <c r="D1130" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="1131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1131">
         <v>11717</v>
       </c>
       <c r="D1131" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1132" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1132">
         <v>11620</v>
       </c>
       <c r="D1132" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1133" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1133">
         <v>11706</v>
       </c>
       <c r="D1133" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1134" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1134">
         <v>11871</v>
       </c>
       <c r="D1134" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1135" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1135">
         <v>11680</v>
       </c>
       <c r="D1135" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="1136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1136" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1136">
         <v>11576</v>
       </c>
       <c r="D1136" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1137">
         <v>11679</v>
       </c>
       <c r="D1137" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="1138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1138" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1138">
         <v>11680</v>
       </c>
       <c r="D1138" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="1139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1139" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1139">
         <v>11424</v>
       </c>
       <c r="D1139" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="1140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1140" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1140">
         <v>11508</v>
       </c>
       <c r="D1140" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="1141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1141" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1141">
         <v>11479</v>
       </c>
       <c r="D1141" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="1142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1142" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1142">
         <v>11473</v>
       </c>
       <c r="D1142" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="1143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1143" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1143">
         <v>11459</v>
       </c>
       <c r="D1143" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1144" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1144">
         <v>11458</v>
       </c>
       <c r="D1144" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="1145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1145" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1145">
         <v>11422</v>
       </c>
       <c r="D1145" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="1146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1146">
         <v>11422</v>
       </c>
       <c r="D1146" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="1147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1147">
         <v>11367</v>
       </c>
       <c r="D1147" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1148" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1148">
         <v>12273</v>
       </c>
       <c r="D1148" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1149" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1149">
         <v>12089</v>
       </c>
       <c r="D1149" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1150" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1150">
         <v>12090</v>
       </c>
       <c r="D1150" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="1151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1151" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1151">
         <v>12091</v>
       </c>
       <c r="D1151" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1152" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1152">
         <v>12008</v>
       </c>
       <c r="D1152" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="1153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1153" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1153">
         <v>12125</v>
       </c>
       <c r="D1153" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="1154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1154" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1154">
         <v>12097</v>
       </c>
       <c r="D1154" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="1155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1155" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1155">
         <v>12085</v>
       </c>
       <c r="D1155" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="1156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1156" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1156">
         <v>12085</v>
       </c>
       <c r="D1156" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1157" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1157">
         <v>12144</v>
       </c>
       <c r="D1157" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1158" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1158">
         <v>12435</v>
       </c>
       <c r="D1158" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1159" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1159">
         <v>12447</v>
       </c>
       <c r="D1159" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1160" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1160">
         <v>12454</v>
       </c>
       <c r="D1160" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1161" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1161">
         <v>12262</v>
       </c>
       <c r="D1161" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1162" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1162">
         <v>12043</v>
       </c>
       <c r="D1162" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="1163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1163">
         <v>12080</v>
       </c>
       <c r="D1163" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="1164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1164" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1164">
         <v>12079</v>
       </c>
       <c r="D1164" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="1165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1165">
         <v>12545</v>
       </c>
       <c r="D1165" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1166" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1166">
         <v>12470</v>
       </c>
       <c r="D1166" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1167">
         <v>13242</v>
       </c>
       <c r="D1167" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="1168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1168">
         <v>13257</v>
       </c>
       <c r="D1168" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1169" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1169">
         <v>11984</v>
       </c>
       <c r="D1169" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1170" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1170">
         <v>12042</v>
       </c>
       <c r="D1170" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="1171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1171" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1171">
         <v>12802</v>
@@ -11537,271 +11533,271 @@
     </row>
     <row r="1172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1172" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1172">
         <v>12411</v>
       </c>
       <c r="D1172" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1173">
         <v>12113</v>
       </c>
       <c r="D1173" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1174" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1174">
         <v>12113</v>
       </c>
       <c r="D1174" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="1175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1175" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1175">
         <v>12082</v>
       </c>
       <c r="D1175" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="1176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1176" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1176">
         <v>12238</v>
       </c>
       <c r="F1176" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1177" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1177">
         <v>11592</v>
       </c>
       <c r="D1177" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="1178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1178" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1178">
         <v>12902</v>
       </c>
       <c r="D1178" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1179" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1179">
         <v>12690</v>
       </c>
       <c r="D1179" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="1180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1180" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1180">
         <v>12710</v>
       </c>
       <c r="D1180" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="1181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1181" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1181">
         <v>12710</v>
       </c>
       <c r="D1181" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="1182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1182">
         <v>12904</v>
       </c>
       <c r="D1182" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="1183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1183" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1183">
         <v>12596</v>
       </c>
       <c r="D1183" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="1184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1184" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B1184">
         <v>12567</v>
       </c>
       <c r="D1184" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="1185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1185" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1185">
         <v>12615</v>
       </c>
       <c r="D1185" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="1186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1186" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1186">
         <v>12655</v>
       </c>
       <c r="D1186" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1187" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1187">
         <v>12591</v>
       </c>
       <c r="D1187" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="1188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1188">
         <v>12555</v>
       </c>
       <c r="D1188" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="1189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1189" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1189">
         <v>12555</v>
       </c>
       <c r="D1189" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="1190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1190" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1190">
         <v>12622</v>
       </c>
       <c r="D1190" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="1191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1191" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B1191">
         <v>12656</v>
       </c>
       <c r="D1191" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1192">
         <v>12708</v>
       </c>
       <c r="D1192" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="1193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1193" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1193">
         <v>12712</v>
       </c>
       <c r="D1193" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="1194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1194">
         <v>12574</v>
       </c>
       <c r="D1194" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="1195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1195" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1195">
         <v>12608</v>
       </c>
       <c r="D1195" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1196" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1196">
         <v>12548</v>
@@ -11812,7 +11808,7 @@
     </row>
     <row r="1197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1197" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1197">
         <v>12547</v>
@@ -11823,46 +11819,46 @@
     </row>
     <row r="1198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1198" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1198">
         <v>12821</v>
       </c>
       <c r="D1198" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="1199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1199">
         <v>12862</v>
       </c>
       <c r="D1199" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="1200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1200" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1200">
         <v>13060</v>
       </c>
       <c r="D1200" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="1201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1201" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1201">
         <v>12910</v>
       </c>
       <c r="D1201" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F1201" t="s">
         <v>12</v>
@@ -11870,13 +11866,13 @@
     </row>
     <row r="1202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1202" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1202">
         <v>12913</v>
       </c>
       <c r="D1202" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F1202" t="s">
         <v>12</v>
@@ -11884,46 +11880,46 @@
     </row>
     <row r="1203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1203" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1203">
         <v>12920</v>
       </c>
       <c r="D1203" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="1204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1204" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1204">
         <v>12928</v>
       </c>
       <c r="D1204" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1205" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1205">
         <v>12872</v>
       </c>
       <c r="D1205" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="1206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1206" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1206">
         <v>13426</v>
       </c>
       <c r="D1206" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="1207" spans="1:6" x14ac:dyDescent="0.25">
@@ -11936,24 +11932,24 @@
     </row>
     <row r="1208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1208" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1208">
         <v>12987</v>
       </c>
       <c r="D1208" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="1209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1209" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1209">
         <v>13224</v>
       </c>
       <c r="D1209" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="1210" spans="1:6" x14ac:dyDescent="0.25">
@@ -11982,194 +11978,194 @@
     </row>
     <row r="1213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1213" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1213">
         <v>13239</v>
       </c>
       <c r="D1213" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="1214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1214">
         <v>911</v>
       </c>
       <c r="D1214" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="1215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1215" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1215">
         <v>10942</v>
       </c>
       <c r="D1215" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1216" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1216">
         <v>13355</v>
       </c>
       <c r="D1216" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1217" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1217">
         <v>12891</v>
       </c>
       <c r="D1217" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="1218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1218" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1218">
         <v>13121</v>
       </c>
       <c r="D1218" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="1219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1219" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1219">
         <v>12815</v>
       </c>
       <c r="D1219" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="1220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1220" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1220">
         <v>13172</v>
       </c>
       <c r="D1220" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="1221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1221" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1221">
         <v>13145</v>
       </c>
       <c r="D1221" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="1222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1222" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1222">
         <v>13710</v>
       </c>
       <c r="D1222" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="1223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1223" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1223">
         <v>9280</v>
       </c>
       <c r="D1223" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1224" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1224">
         <v>9369</v>
       </c>
       <c r="D1224" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="1225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1225" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1225">
         <v>12697</v>
       </c>
       <c r="D1225" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="1226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1226" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1226">
         <v>9595</v>
       </c>
       <c r="D1226" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="1227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1227" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1227">
         <v>9505</v>
       </c>
       <c r="D1227" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="1228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1228" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1228">
         <v>9523</v>
       </c>
       <c r="D1228" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="1229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1229" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1229">
         <v>9512</v>
       </c>
       <c r="D1229" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="1230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1230" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1230">
         <v>9578</v>
@@ -12180,7 +12176,7 @@
     </row>
     <row r="1231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1231" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1231">
         <v>9620</v>
@@ -12191,7 +12187,7 @@
     </row>
     <row r="1232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1232" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1232">
         <v>9628</v>
@@ -12202,7 +12198,7 @@
     </row>
     <row r="1233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1233" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1233">
         <v>9579</v>
@@ -12213,62 +12209,62 @@
     </row>
     <row r="1234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1234" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1234">
         <v>9706</v>
       </c>
       <c r="D1234" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="1235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1235" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1235">
         <v>9759</v>
       </c>
       <c r="D1235" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="1236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1236" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1236">
         <v>9759</v>
       </c>
       <c r="D1236" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="1237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1237" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1237">
         <v>10119</v>
       </c>
       <c r="D1237" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="1238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1238" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1238">
         <v>10382</v>
       </c>
       <c r="D1238" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="1239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1239" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1239">
         <v>9390</v>
@@ -12279,7 +12275,7 @@
     </row>
     <row r="1240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1240" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1240">
         <v>9423</v>
@@ -12290,101 +12286,101 @@
     </row>
     <row r="1241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1241" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1241">
         <v>11880</v>
       </c>
       <c r="D1241" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="1242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1242" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1242">
         <v>10016</v>
       </c>
       <c r="D1242" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="1243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1243" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1243">
         <v>10634</v>
       </c>
       <c r="D1243" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1244" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1244">
         <v>10648</v>
       </c>
       <c r="D1244" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="1245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1245" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1245">
         <v>10572</v>
       </c>
       <c r="D1245" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="1246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1246" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1246">
         <v>10513</v>
       </c>
       <c r="D1246" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="1247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1247" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1247">
         <v>10670</v>
       </c>
       <c r="D1247" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="1248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1248" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1248">
         <v>10670</v>
       </c>
       <c r="D1248" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="1249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1249" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1249">
         <v>10568</v>
       </c>
       <c r="D1249" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1250" spans="1:6" x14ac:dyDescent="0.25">
@@ -12413,18 +12409,18 @@
     </row>
     <row r="1253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1253" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1253">
         <v>10628</v>
       </c>
       <c r="D1253" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="1254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1254" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1254">
         <v>10705</v>
@@ -12435,13 +12431,13 @@
     </row>
     <row r="1255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1255" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1255">
         <v>10706</v>
       </c>
       <c r="D1255" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F1255" t="s">
         <v>12</v>
@@ -12449,348 +12445,348 @@
     </row>
     <row r="1256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1256" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1256">
         <v>10708</v>
       </c>
       <c r="D1256" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="1257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1257" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1257">
         <v>10944</v>
       </c>
       <c r="D1257" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="1258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1258" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1258">
         <v>11070</v>
       </c>
       <c r="D1258" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="1259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1259" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1259">
         <v>10816</v>
       </c>
       <c r="D1259" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="1260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1260" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1260">
         <v>10689</v>
       </c>
       <c r="D1260" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="1261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1261" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1261">
         <v>10206</v>
       </c>
       <c r="D1261" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="1262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1262" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1262">
         <v>10226</v>
       </c>
       <c r="D1262" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="1263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1263" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1263">
         <v>10200</v>
       </c>
       <c r="D1263" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="1264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1264" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1264">
         <v>10237</v>
       </c>
       <c r="D1264" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="1265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1265" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1265">
         <v>10247</v>
       </c>
       <c r="D1265" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="1266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1266" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1266">
         <v>10248</v>
       </c>
       <c r="D1266" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="1267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1267" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1267">
         <v>10248</v>
       </c>
       <c r="D1267" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="1268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1268" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1268">
         <v>10434</v>
       </c>
       <c r="D1268" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="1269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1269" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1269">
         <v>10281</v>
       </c>
       <c r="D1269" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1270" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1270">
         <v>11575</v>
       </c>
       <c r="D1270" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="1271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1271" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1271">
         <v>11788</v>
       </c>
       <c r="D1271" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="1272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1272" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1272">
         <v>11798</v>
       </c>
       <c r="D1272" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="1273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1273" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1273">
         <v>11798</v>
       </c>
       <c r="D1273" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1274" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1274">
         <v>11645</v>
       </c>
       <c r="D1274" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="1275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1275" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1275">
         <v>11730</v>
       </c>
       <c r="D1275" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="1276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1276" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1276">
         <v>11650</v>
       </c>
       <c r="D1276" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="1277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1277" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1277">
         <v>11653</v>
       </c>
       <c r="D1277" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="1278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1278" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1278">
         <v>11697</v>
       </c>
       <c r="D1278" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="1279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1279" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1279">
         <v>11701</v>
       </c>
       <c r="D1279" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="1280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1280" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1280">
         <v>11604</v>
       </c>
       <c r="D1280" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="1281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1281" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1281">
         <v>12157</v>
       </c>
       <c r="D1281" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="1282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1282" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1282">
         <v>11878</v>
       </c>
       <c r="D1282" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="1283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1283" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1283">
         <v>12728</v>
       </c>
       <c r="D1283" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1284" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1284">
         <v>11243</v>
       </c>
       <c r="D1284" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1285" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1285">
         <v>11291</v>
       </c>
       <c r="D1285" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1286" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1286">
         <v>11273</v>
       </c>
       <c r="D1286" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="1287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1287" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1287">
         <v>11273</v>
@@ -12809,7 +12805,7 @@
     </row>
     <row r="1289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1289" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1289">
         <v>11276</v>
@@ -12820,7 +12816,7 @@
     </row>
     <row r="1290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1290" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1290">
         <v>11288</v>
@@ -12831,95 +12827,95 @@
     </row>
     <row r="1291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1291" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1291">
         <v>11436</v>
       </c>
       <c r="D1291" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="1292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1292" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1292">
         <v>11448</v>
       </c>
       <c r="D1292" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="1293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1293" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1293">
         <v>11474</v>
       </c>
       <c r="D1293" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="1294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1294" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1294">
         <v>11483</v>
       </c>
       <c r="D1294" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1295" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1295">
         <v>11224</v>
       </c>
       <c r="D1295" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1296" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1296">
         <v>11182</v>
       </c>
       <c r="D1296" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1297" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1297">
         <v>11330</v>
       </c>
       <c r="D1297" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1298" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1298">
         <v>11175</v>
       </c>
       <c r="D1298" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1299" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1299">
         <v>12098</v>
@@ -12930,7 +12926,7 @@
     </row>
     <row r="1300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1300" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1300">
         <v>12107</v>
@@ -12941,7 +12937,7 @@
     </row>
     <row r="1301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1301" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1301">
         <v>12110</v>
@@ -12952,7 +12948,7 @@
     </row>
     <row r="1302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1302" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1302">
         <v>12106</v>
@@ -12963,46 +12959,46 @@
     </row>
     <row r="1303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1303" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1303">
         <v>26034</v>
       </c>
       <c r="D1303" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1304" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1304">
         <v>13372</v>
       </c>
       <c r="D1304" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="1305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1305" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1305">
         <v>12272</v>
       </c>
       <c r="D1305" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1306" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1306">
         <v>12276</v>
       </c>
       <c r="D1306" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F1306" t="s">
         <v>12</v>
@@ -13010,13 +13006,13 @@
     </row>
     <row r="1307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1307" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1307">
         <v>12277</v>
       </c>
       <c r="D1307" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F1307" t="s">
         <v>12</v>
@@ -13024,35 +13020,35 @@
     </row>
     <row r="1308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1308" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1308">
         <v>12478</v>
       </c>
       <c r="D1308" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="1309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1309" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1309">
         <v>12320</v>
       </c>
       <c r="D1309" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="1310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1310" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1310">
         <v>12463</v>
       </c>
       <c r="D1310" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F1310" t="s">
         <v>12</v>
@@ -13060,7 +13056,7 @@
     </row>
     <row r="1311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1311" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1311">
         <v>12465</v>
@@ -13071,18 +13067,18 @@
     </row>
     <row r="1312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1312" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1312">
         <v>12473</v>
       </c>
       <c r="D1312" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="1313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1313" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1313">
         <v>12469</v>
@@ -13093,51 +13089,51 @@
     </row>
     <row r="1314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1314" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1314">
         <v>12495</v>
       </c>
       <c r="D1314" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="1315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1315" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1315">
         <v>24743</v>
       </c>
       <c r="D1315" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="1316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1316" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1316">
         <v>24547</v>
       </c>
       <c r="D1316" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="1317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1317" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1317">
         <v>12302</v>
       </c>
       <c r="D1317" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="1318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1318" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1318">
         <v>24500</v>
@@ -13148,18 +13144,18 @@
     </row>
     <row r="1319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1319" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1319">
         <v>24500</v>
       </c>
       <c r="D1319" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1320" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1320">
         <v>24802</v>
@@ -13170,7 +13166,7 @@
     </row>
     <row r="1321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1321" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1321">
         <v>12010</v>
@@ -13181,7 +13177,7 @@
     </row>
     <row r="1322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1322" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1322">
         <v>12014</v>
@@ -13192,18 +13188,18 @@
     </row>
     <row r="1323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1323" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1323">
         <v>12876</v>
       </c>
       <c r="D1323" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="1324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1324" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1324">
         <v>1098</v>
@@ -13214,7 +13210,7 @@
     </row>
     <row r="1325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1325" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1325">
         <v>5724</v>
@@ -13225,7 +13221,7 @@
     </row>
     <row r="1326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1326" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1326">
         <v>5722</v>
@@ -13236,7 +13232,7 @@
     </row>
     <row r="1327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1327" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1327">
         <v>832</v>
@@ -13247,24 +13243,24 @@
     </row>
     <row r="1328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1328" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1328">
         <v>688</v>
       </c>
       <c r="F1328" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1329" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1329">
         <v>652</v>
       </c>
       <c r="F1329" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1330" spans="1:6" x14ac:dyDescent="0.25">
@@ -13272,7 +13268,7 @@
         <v>651</v>
       </c>
       <c r="F1330" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1331" spans="1:6" x14ac:dyDescent="0.25">
@@ -13280,12 +13276,12 @@
         <v>642</v>
       </c>
       <c r="F1331" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="1332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1332" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1332">
         <v>2341</v>
@@ -13296,7 +13292,7 @@
     </row>
     <row r="1333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1333" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1333">
         <v>2318</v>
@@ -13307,7 +13303,7 @@
     </row>
     <row r="1334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1334" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1334">
         <v>593</v>
@@ -13318,7 +13314,7 @@
     </row>
     <row r="1335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1335" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B1335">
         <v>8733</v>
@@ -13329,27 +13325,98 @@
     </row>
     <row r="1336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1336" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1336">
         <v>5160</v>
       </c>
-      <c r="D1336" s="1" t="s">
-        <v>349</v>
+      <c r="D1336" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="1337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1337" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1337">
         <v>5161</v>
       </c>
-      <c r="D1337" s="1" t="s">
-        <v>350</v>
+      <c r="D1337" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1338" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1338">
+        <v>6661</v>
+      </c>
+      <c r="E1338">
+        <v>-77</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1339" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1339">
+        <v>6662</v>
+      </c>
+      <c r="E1339">
+        <v>-77</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1340">
+        <v>2861</v>
+      </c>
+      <c r="E1340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1341">
+        <v>8250</v>
+      </c>
+      <c r="E1341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1342">
+        <v>8151</v>
+      </c>
+      <c r="E1342">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1343">
+        <v>8254</v>
+      </c>
+      <c r="E1343">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1344">
+        <v>8410</v>
+      </c>
+      <c r="E1344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1345" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B1345">
+        <v>8419</v>
+      </c>
+      <c r="E1345">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1345" xr:uid="{56545B79-22C0-4057-A076-1E697524330B}"/>
   <conditionalFormatting sqref="B1">
     <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
@@ -13365,7 +13432,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D60A7C4-82C4-4AAF-A00A-127D625F91A3}">
-  <dimension ref="A1:H865"/>
+  <dimension ref="A1:H871"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13391,7 +13458,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -13399,7 +13466,7 @@
         <v>22264</v>
       </c>
       <c r="E2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -13407,7 +13474,7 @@
         <v>22271</v>
       </c>
       <c r="E3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -13899,7 +13966,7 @@
         <v>23233</v>
       </c>
       <c r="E45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -13969,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -14248,7 +14315,7 @@
         <v>19880</v>
       </c>
       <c r="E83" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -14360,7 +14427,7 @@
         <v>20341</v>
       </c>
       <c r="E97" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -14368,7 +14435,7 @@
         <v>20471</v>
       </c>
       <c r="E98" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -14384,7 +14451,7 @@
         <v>20448</v>
       </c>
       <c r="E100" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -14408,7 +14475,7 @@
         <v>20552</v>
       </c>
       <c r="E103" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -14416,7 +14483,7 @@
         <v>20482</v>
       </c>
       <c r="E104" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -14480,7 +14547,7 @@
         <v>21700</v>
       </c>
       <c r="E112" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -14536,7 +14603,7 @@
         <v>22112</v>
       </c>
       <c r="E119" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -14624,7 +14691,7 @@
         <v>22899</v>
       </c>
       <c r="E130" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -14664,7 +14731,7 @@
         <v>22941</v>
       </c>
       <c r="E135" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -14680,7 +14747,7 @@
         <v>23253</v>
       </c>
       <c r="E137" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -14696,7 +14763,7 @@
         <v>23316</v>
       </c>
       <c r="E139" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -14768,7 +14835,7 @@
         <v>24261</v>
       </c>
       <c r="E148" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -14790,7 +14857,7 @@
         <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -14806,7 +14873,7 @@
         <v>24537</v>
       </c>
       <c r="E152" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -14814,7 +14881,7 @@
         <v>24729</v>
       </c>
       <c r="E153" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -14825,7 +14892,7 @@
         <v>1</v>
       </c>
       <c r="E154" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -14833,7 +14900,7 @@
         <v>24910</v>
       </c>
       <c r="E155" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -14849,7 +14916,7 @@
         <v>25199</v>
       </c>
       <c r="E157" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -14857,7 +14924,7 @@
         <v>25205</v>
       </c>
       <c r="E158" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -14865,7 +14932,7 @@
         <v>25211</v>
       </c>
       <c r="E159" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -14873,7 +14940,7 @@
         <v>28375</v>
       </c>
       <c r="E160" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -14881,7 +14948,7 @@
         <v>25208</v>
       </c>
       <c r="E161" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -14897,7 +14964,7 @@
         <v>25376</v>
       </c>
       <c r="E163" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -14937,7 +15004,7 @@
         <v>25862</v>
       </c>
       <c r="E168" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -14952,8 +15019,11 @@
       <c r="A170">
         <v>25324</v>
       </c>
+      <c r="B170">
+        <v>1</v>
+      </c>
       <c r="E170" t="s">
-        <v>54</v>
+        <v>169</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -14977,7 +15047,7 @@
         <v>26085</v>
       </c>
       <c r="E173" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -15001,7 +15071,7 @@
         <v>26260</v>
       </c>
       <c r="E176" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -15025,7 +15095,7 @@
         <v>26473</v>
       </c>
       <c r="E179" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -15041,7 +15111,7 @@
         <v>26420</v>
       </c>
       <c r="E181" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -15065,7 +15135,7 @@
         <v>27337</v>
       </c>
       <c r="E184" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -15081,7 +15151,7 @@
         <v>26917</v>
       </c>
       <c r="E186" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -15089,7 +15159,7 @@
         <v>26949</v>
       </c>
       <c r="E187" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -15097,7 +15167,7 @@
         <v>28095</v>
       </c>
       <c r="E188" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -15105,7 +15175,7 @@
         <v>28082</v>
       </c>
       <c r="E189" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -15113,7 +15183,7 @@
         <v>28214</v>
       </c>
       <c r="E190" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -15121,7 +15191,7 @@
         <v>28138</v>
       </c>
       <c r="E191" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -15129,7 +15199,7 @@
         <v>28216</v>
       </c>
       <c r="E192" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -15145,7 +15215,7 @@
         <v>27801</v>
       </c>
       <c r="E194" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -15153,7 +15223,7 @@
         <v>28092</v>
       </c>
       <c r="E195" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -15201,7 +15271,7 @@
         <v>25462</v>
       </c>
       <c r="E201" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
@@ -15209,7 +15279,7 @@
         <v>28401</v>
       </c>
       <c r="E202" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
@@ -15217,7 +15287,7 @@
         <v>28561</v>
       </c>
       <c r="E203" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
@@ -15225,7 +15295,7 @@
         <v>28589</v>
       </c>
       <c r="E204" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -15233,7 +15303,7 @@
         <v>28030</v>
       </c>
       <c r="E205" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -15241,7 +15311,7 @@
         <v>28377</v>
       </c>
       <c r="E206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
@@ -15249,7 +15319,7 @@
         <v>28653</v>
       </c>
       <c r="E207" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -15257,7 +15327,7 @@
         <v>28668</v>
       </c>
       <c r="E208" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
@@ -15273,7 +15343,7 @@
         <v>28658</v>
       </c>
       <c r="E210" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -15281,7 +15351,7 @@
         <v>29146</v>
       </c>
       <c r="E211" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
@@ -15297,7 +15367,7 @@
         <v>28907</v>
       </c>
       <c r="E213" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -15305,7 +15375,7 @@
         <v>28911</v>
       </c>
       <c r="E214" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -15313,7 +15383,7 @@
         <v>28910</v>
       </c>
       <c r="E215" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -15329,7 +15399,7 @@
         <v>29043</v>
       </c>
       <c r="E217" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
@@ -15337,7 +15407,7 @@
         <v>29047</v>
       </c>
       <c r="E218" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
@@ -15345,7 +15415,7 @@
         <v>29110</v>
       </c>
       <c r="E219" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
@@ -15353,7 +15423,7 @@
         <v>29481</v>
       </c>
       <c r="E220" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
@@ -15361,7 +15431,7 @@
         <v>29592</v>
       </c>
       <c r="E221" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
@@ -15369,7 +15439,7 @@
         <v>29733</v>
       </c>
       <c r="E222" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
@@ -15377,7 +15447,7 @@
         <v>29690</v>
       </c>
       <c r="E223" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
@@ -15385,7 +15455,7 @@
         <v>30052</v>
       </c>
       <c r="E224" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
@@ -15401,7 +15471,7 @@
         <v>30082</v>
       </c>
       <c r="E226" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
@@ -15409,7 +15479,7 @@
         <v>29796</v>
       </c>
       <c r="E227" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
@@ -15425,7 +15495,7 @@
         <v>29839</v>
       </c>
       <c r="E229" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -15433,7 +15503,7 @@
         <v>29885</v>
       </c>
       <c r="E230" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
@@ -15441,7 +15511,7 @@
         <v>29647</v>
       </c>
       <c r="E231" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
@@ -15449,7 +15519,7 @@
         <v>29445</v>
       </c>
       <c r="E232" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
@@ -15457,7 +15527,7 @@
         <v>30041</v>
       </c>
       <c r="E233" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
@@ -15473,7 +15543,7 @@
         <v>29997</v>
       </c>
       <c r="E235" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
@@ -15481,7 +15551,7 @@
         <v>30074</v>
       </c>
       <c r="E236" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
@@ -15489,7 +15559,7 @@
         <v>30105</v>
       </c>
       <c r="E237" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.25">
@@ -15497,7 +15567,7 @@
         <v>30099</v>
       </c>
       <c r="E238" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.25">
@@ -15505,7 +15575,7 @@
         <v>29975</v>
       </c>
       <c r="E239" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.25">
@@ -15521,7 +15591,7 @@
         <v>30127</v>
       </c>
       <c r="E241" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
@@ -15529,7 +15599,7 @@
         <v>30216</v>
       </c>
       <c r="E242" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
@@ -15537,7 +15607,7 @@
         <v>30294</v>
       </c>
       <c r="E243" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
@@ -15545,7 +15615,7 @@
         <v>30252</v>
       </c>
       <c r="E244" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
@@ -15553,7 +15623,7 @@
         <v>30295</v>
       </c>
       <c r="E245" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
@@ -15561,7 +15631,7 @@
         <v>30399</v>
       </c>
       <c r="E246" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.25">
@@ -15569,7 +15639,7 @@
         <v>30232</v>
       </c>
       <c r="E247" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.25">
@@ -15577,7 +15647,7 @@
         <v>30390</v>
       </c>
       <c r="E248" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.25">
@@ -15585,7 +15655,7 @@
         <v>30406</v>
       </c>
       <c r="E249" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.25">
@@ -15601,7 +15671,7 @@
         <v>31135</v>
       </c>
       <c r="E251" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -15617,7 +15687,7 @@
         <v>31333</v>
       </c>
       <c r="E253" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
@@ -15689,7 +15759,7 @@
         <v>33532</v>
       </c>
       <c r="E262" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
@@ -15833,7 +15903,7 @@
         <v>17520</v>
       </c>
       <c r="E280" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.25">
@@ -15844,7 +15914,7 @@
         <v>0</v>
       </c>
       <c r="E281" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
@@ -15895,7 +15965,7 @@
         <v>17087</v>
       </c>
       <c r="E287" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.25">
@@ -15903,7 +15973,7 @@
         <v>17205</v>
       </c>
       <c r="E288" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.25">
@@ -15911,7 +15981,7 @@
         <v>17275</v>
       </c>
       <c r="E289" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.25">
@@ -15967,7 +16037,7 @@
         <v>17435</v>
       </c>
       <c r="E296" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
@@ -15975,7 +16045,7 @@
         <v>17114</v>
       </c>
       <c r="E297" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
@@ -15983,7 +16053,7 @@
         <v>17442</v>
       </c>
       <c r="E298" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
@@ -15991,7 +16061,7 @@
         <v>17441</v>
       </c>
       <c r="E299" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
@@ -15999,7 +16069,7 @@
         <v>17440</v>
       </c>
       <c r="E300" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
@@ -16007,7 +16077,7 @@
         <v>17443</v>
       </c>
       <c r="E301" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
@@ -16015,7 +16085,7 @@
         <v>17445</v>
       </c>
       <c r="E302" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
@@ -16023,7 +16093,7 @@
         <v>17682</v>
       </c>
       <c r="E303" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
@@ -16031,7 +16101,7 @@
         <v>17712</v>
       </c>
       <c r="E304" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
@@ -16039,7 +16109,7 @@
         <v>17856</v>
       </c>
       <c r="E305" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
@@ -16047,7 +16117,7 @@
         <v>17857</v>
       </c>
       <c r="E306" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
@@ -16055,7 +16125,7 @@
         <v>17866</v>
       </c>
       <c r="E307" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
@@ -16063,7 +16133,7 @@
         <v>17877</v>
       </c>
       <c r="E308" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
@@ -16071,7 +16141,7 @@
         <v>17923</v>
       </c>
       <c r="E309" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
@@ -16079,7 +16149,7 @@
         <v>17925</v>
       </c>
       <c r="E310" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
@@ -16087,7 +16157,7 @@
         <v>17924</v>
       </c>
       <c r="E311" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
@@ -16103,7 +16173,7 @@
         <v>15608</v>
       </c>
       <c r="E313" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
@@ -16127,7 +16197,7 @@
         <v>18276</v>
       </c>
       <c r="E316" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
@@ -16191,7 +16261,7 @@
         <v>23428</v>
       </c>
       <c r="E324" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
@@ -16223,7 +16293,7 @@
         <v>23461</v>
       </c>
       <c r="E328" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
@@ -16231,7 +16301,7 @@
         <v>23466</v>
       </c>
       <c r="E329" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
@@ -16239,7 +16309,7 @@
         <v>23465</v>
       </c>
       <c r="E330" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
@@ -16247,7 +16317,7 @@
         <v>25206</v>
       </c>
       <c r="E331" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
@@ -16287,7 +16357,7 @@
         <v>28106</v>
       </c>
       <c r="E336" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
@@ -16303,7 +16373,7 @@
         <v>30997</v>
       </c>
       <c r="E338" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
@@ -16319,7 +16389,7 @@
         <v>32594</v>
       </c>
       <c r="E340" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
@@ -16327,7 +16397,7 @@
         <v>32540</v>
       </c>
       <c r="E341" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
@@ -16351,7 +16421,7 @@
         <v>17085</v>
       </c>
       <c r="E344" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
@@ -16359,7 +16429,7 @@
         <v>18803</v>
       </c>
       <c r="E345" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
@@ -16375,7 +16445,7 @@
         <v>28518</v>
       </c>
       <c r="E347" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
@@ -16415,7 +16485,7 @@
         <v>29396</v>
       </c>
       <c r="E352" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
@@ -16423,7 +16493,7 @@
         <v>29405</v>
       </c>
       <c r="E353" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
@@ -16431,7 +16501,7 @@
         <v>33769</v>
       </c>
       <c r="E354" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
@@ -16439,7 +16509,7 @@
         <v>28532</v>
       </c>
       <c r="E355" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
@@ -16447,7 +16517,7 @@
         <v>29804</v>
       </c>
       <c r="E356" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
@@ -16463,7 +16533,7 @@
         <v>30946</v>
       </c>
       <c r="E358" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
@@ -16471,7 +16541,7 @@
         <v>33762</v>
       </c>
       <c r="E359" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
@@ -16479,7 +16549,7 @@
         <v>30056</v>
       </c>
       <c r="E360" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
@@ -16487,7 +16557,7 @@
         <v>33770</v>
       </c>
       <c r="E361" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
@@ -16495,7 +16565,7 @@
         <v>29343</v>
       </c>
       <c r="E362" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
@@ -16503,7 +16573,7 @@
         <v>29344</v>
       </c>
       <c r="E363" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
@@ -16511,7 +16581,7 @@
         <v>29456</v>
       </c>
       <c r="E364" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
@@ -16519,7 +16589,7 @@
         <v>29560</v>
       </c>
       <c r="E365" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
@@ -16527,7 +16597,7 @@
         <v>30218</v>
       </c>
       <c r="E366" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
@@ -16543,7 +16613,7 @@
         <v>30631</v>
       </c>
       <c r="E368" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
@@ -16551,7 +16621,7 @@
         <v>30944</v>
       </c>
       <c r="E369" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
@@ -16575,7 +16645,7 @@
         <v>302</v>
       </c>
       <c r="E372" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
@@ -16583,7 +16653,7 @@
         <v>23256</v>
       </c>
       <c r="E373" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
@@ -16591,7 +16661,7 @@
         <v>22266</v>
       </c>
       <c r="E374" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
@@ -16599,7 +16669,7 @@
         <v>23110</v>
       </c>
       <c r="E375" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
@@ -16607,7 +16677,7 @@
         <v>23362</v>
       </c>
       <c r="E376" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
@@ -16615,7 +16685,7 @@
         <v>23365</v>
       </c>
       <c r="E377" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
@@ -16623,7 +16693,7 @@
         <v>23115</v>
       </c>
       <c r="E378" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
@@ -16631,7 +16701,7 @@
         <v>23347</v>
       </c>
       <c r="E379" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
@@ -16639,7 +16709,7 @@
         <v>22270</v>
       </c>
       <c r="E380" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
@@ -16647,7 +16717,7 @@
         <v>23112</v>
       </c>
       <c r="E381" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
@@ -16674,7 +16744,7 @@
         <v>2</v>
       </c>
       <c r="E384" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
@@ -16709,7 +16779,7 @@
         <v>1</v>
       </c>
       <c r="E388" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
@@ -16741,7 +16811,7 @@
         <v>2227</v>
       </c>
       <c r="E392" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
@@ -16749,7 +16819,7 @@
         <v>2278</v>
       </c>
       <c r="E393" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
@@ -16765,7 +16835,7 @@
         <v>2500</v>
       </c>
       <c r="E395" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
@@ -16773,7 +16843,7 @@
         <v>2546</v>
       </c>
       <c r="E396" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
@@ -16781,7 +16851,7 @@
         <v>2610</v>
       </c>
       <c r="E397" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
@@ -16797,7 +16867,7 @@
         <v>3430</v>
       </c>
       <c r="E399" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
@@ -16829,7 +16899,7 @@
         <v>3897</v>
       </c>
       <c r="E403" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
@@ -16901,7 +16971,7 @@
         <v>4606</v>
       </c>
       <c r="E412" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
@@ -16941,7 +17011,7 @@
         <v>5398</v>
       </c>
       <c r="E417" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
@@ -16949,7 +17019,7 @@
         <v>5891</v>
       </c>
       <c r="E418" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
@@ -16957,7 +17027,7 @@
         <v>5895</v>
       </c>
       <c r="E419" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
@@ -16965,7 +17035,7 @@
         <v>5955</v>
       </c>
       <c r="E420" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
@@ -17021,7 +17091,7 @@
         <v>7918</v>
       </c>
       <c r="E427" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
@@ -17029,7 +17099,7 @@
         <v>8405</v>
       </c>
       <c r="E428" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
@@ -17085,7 +17155,7 @@
         <v>10666</v>
       </c>
       <c r="E435" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
@@ -17093,7 +17163,7 @@
         <v>10684</v>
       </c>
       <c r="E436" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
@@ -17109,7 +17179,7 @@
         <v>10799</v>
       </c>
       <c r="E438" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
@@ -17133,7 +17203,7 @@
         <v>11554</v>
       </c>
       <c r="E441" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
@@ -17141,7 +17211,7 @@
         <v>11555</v>
       </c>
       <c r="E442" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
@@ -17149,7 +17219,7 @@
         <v>11556</v>
       </c>
       <c r="E443" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
@@ -17157,7 +17227,7 @@
         <v>11557</v>
       </c>
       <c r="E444" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
@@ -17181,7 +17251,7 @@
         <v>13278</v>
       </c>
       <c r="E447" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
@@ -17229,7 +17299,7 @@
         <v>13717</v>
       </c>
       <c r="E453" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
@@ -17365,7 +17435,7 @@
         <v>6015</v>
       </c>
       <c r="E470" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
@@ -17381,7 +17451,7 @@
         <v>11558</v>
       </c>
       <c r="E472" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
@@ -17624,7 +17694,7 @@
         <v>28510</v>
       </c>
       <c r="E502" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
@@ -17640,7 +17710,7 @@
         <v>28919</v>
       </c>
       <c r="E504" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
@@ -17648,7 +17718,7 @@
         <v>27928</v>
       </c>
       <c r="E505" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
@@ -17672,7 +17742,7 @@
         <v>28914</v>
       </c>
       <c r="E508" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
@@ -17680,7 +17750,7 @@
         <v>28912</v>
       </c>
       <c r="E509" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
@@ -17688,7 +17758,7 @@
         <v>29053</v>
       </c>
       <c r="E510" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
@@ -17696,7 +17766,7 @@
         <v>28472</v>
       </c>
       <c r="E511" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
@@ -17704,7 +17774,7 @@
         <v>31082</v>
       </c>
       <c r="E512" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
@@ -17878,7 +17948,7 @@
         <v>4566</v>
       </c>
       <c r="E533" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
@@ -17918,7 +17988,7 @@
         <v>7172</v>
       </c>
       <c r="E538" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
@@ -17966,7 +18036,7 @@
         <v>10432</v>
       </c>
       <c r="E544" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
@@ -17974,7 +18044,7 @@
         <v>10475</v>
       </c>
       <c r="E545" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
@@ -18132,7 +18202,7 @@
         <v>19676</v>
       </c>
       <c r="E564" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
@@ -18164,7 +18234,7 @@
         <v>20985</v>
       </c>
       <c r="E568" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
@@ -18204,7 +18274,7 @@
         <v>23191</v>
       </c>
       <c r="E573" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
@@ -18316,7 +18386,7 @@
         <v>21183</v>
       </c>
       <c r="E587" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
@@ -18324,7 +18394,7 @@
         <v>21685</v>
       </c>
       <c r="E588" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
@@ -18332,7 +18402,7 @@
         <v>16841</v>
       </c>
       <c r="E589" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
@@ -18463,7 +18533,7 @@
         <v>1</v>
       </c>
       <c r="E605" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.25">
@@ -18527,7 +18597,7 @@
         <v>16819</v>
       </c>
       <c r="E613" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="614" spans="1:8" x14ac:dyDescent="0.25">
@@ -18594,7 +18664,7 @@
         <v>17446</v>
       </c>
       <c r="E621" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="622" spans="1:8" x14ac:dyDescent="0.25">
@@ -18610,7 +18680,7 @@
         <v>3702</v>
       </c>
       <c r="H623" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="624" spans="1:8" x14ac:dyDescent="0.25">
@@ -18733,7 +18803,7 @@
         <v>1</v>
       </c>
       <c r="E638" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="639" spans="1:5" x14ac:dyDescent="0.25">
@@ -19165,7 +19235,7 @@
         <v>9467</v>
       </c>
       <c r="E692" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
@@ -19333,7 +19403,7 @@
         <v>23618</v>
       </c>
       <c r="E713" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.25">
@@ -19341,7 +19411,7 @@
         <v>30562</v>
       </c>
       <c r="E714" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="715" spans="1:5" x14ac:dyDescent="0.25">
@@ -19349,7 +19419,7 @@
         <v>28760</v>
       </c>
       <c r="E715" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="716" spans="1:5" x14ac:dyDescent="0.25">
@@ -19365,7 +19435,7 @@
         <v>28471</v>
       </c>
       <c r="E717" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="718" spans="1:5" x14ac:dyDescent="0.25">
@@ -19373,7 +19443,7 @@
         <v>29195</v>
       </c>
       <c r="E718" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.25">
@@ -19381,7 +19451,7 @@
         <v>29196</v>
       </c>
       <c r="E719" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.25">
@@ -19389,7 +19459,7 @@
         <v>28474</v>
       </c>
       <c r="E720" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="721" spans="1:5" x14ac:dyDescent="0.25">
@@ -19397,7 +19467,7 @@
         <v>29194</v>
       </c>
       <c r="E721" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
@@ -19421,7 +19491,7 @@
         <v>17468</v>
       </c>
       <c r="E724" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="725" spans="1:5" x14ac:dyDescent="0.25">
@@ -19437,7 +19507,7 @@
         <v>28908</v>
       </c>
       <c r="E726" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.25">
@@ -19445,7 +19515,7 @@
         <v>28943</v>
       </c>
       <c r="E727" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
@@ -19485,7 +19555,7 @@
         <v>18063</v>
       </c>
       <c r="E732" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
@@ -19493,7 +19563,7 @@
         <v>25237</v>
       </c>
       <c r="E733" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.25">
@@ -19501,7 +19571,7 @@
         <v>39372</v>
       </c>
       <c r="E734" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="735" spans="1:5" x14ac:dyDescent="0.25">
@@ -19525,7 +19595,7 @@
         <v>18165</v>
       </c>
       <c r="E737" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="738" spans="1:5" x14ac:dyDescent="0.25">
@@ -19533,7 +19603,7 @@
         <v>16814</v>
       </c>
       <c r="E738" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="739" spans="1:5" x14ac:dyDescent="0.25">
@@ -19549,7 +19619,7 @@
         <v>25272</v>
       </c>
       <c r="E740" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="741" spans="1:5" x14ac:dyDescent="0.25">
@@ -19565,7 +19635,7 @@
         <v>25198</v>
       </c>
       <c r="E742" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="743" spans="1:5" x14ac:dyDescent="0.25">
@@ -19573,7 +19643,7 @@
         <v>24956</v>
       </c>
       <c r="E743" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="744" spans="1:5" x14ac:dyDescent="0.25">
@@ -19589,7 +19659,7 @@
         <v>24713</v>
       </c>
       <c r="E745" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="746" spans="1:5" x14ac:dyDescent="0.25">
@@ -19613,7 +19683,7 @@
         <v>26581</v>
       </c>
       <c r="E748" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="749" spans="1:5" x14ac:dyDescent="0.25">
@@ -19637,7 +19707,7 @@
         <v>28228</v>
       </c>
       <c r="E751" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="752" spans="1:5" x14ac:dyDescent="0.25">
@@ -19645,7 +19715,7 @@
         <v>38017</v>
       </c>
       <c r="E752" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="753" spans="1:5" x14ac:dyDescent="0.25">
@@ -19653,7 +19723,7 @@
         <v>25256</v>
       </c>
       <c r="E753" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="754" spans="1:5" x14ac:dyDescent="0.25">
@@ -19661,7 +19731,7 @@
         <v>36939</v>
       </c>
       <c r="E754" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="755" spans="1:5" x14ac:dyDescent="0.25">
@@ -19669,7 +19739,7 @@
         <v>37187</v>
       </c>
       <c r="E755" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="756" spans="1:5" x14ac:dyDescent="0.25">
@@ -19677,7 +19747,7 @@
         <v>38156</v>
       </c>
       <c r="E756" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="757" spans="1:5" x14ac:dyDescent="0.25">
@@ -19685,7 +19755,7 @@
         <v>38637</v>
       </c>
       <c r="E757" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="758" spans="1:5" x14ac:dyDescent="0.25">
@@ -19693,7 +19763,7 @@
         <v>38638</v>
       </c>
       <c r="E758" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="759" spans="1:5" x14ac:dyDescent="0.25">
@@ -19709,7 +19779,7 @@
         <v>26604</v>
       </c>
       <c r="E760" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="761" spans="1:5" x14ac:dyDescent="0.25">
@@ -19717,7 +19787,7 @@
         <v>27274</v>
       </c>
       <c r="E761" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="762" spans="1:5" x14ac:dyDescent="0.25">
@@ -19725,7 +19795,7 @@
         <v>27275</v>
       </c>
       <c r="E762" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="763" spans="1:5" x14ac:dyDescent="0.25">
@@ -19733,7 +19803,7 @@
         <v>26886</v>
       </c>
       <c r="E763" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="764" spans="1:5" x14ac:dyDescent="0.25">
@@ -19741,7 +19811,7 @@
         <v>28016</v>
       </c>
       <c r="E764" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="765" spans="1:5" x14ac:dyDescent="0.25">
@@ -19749,7 +19819,7 @@
         <v>28503</v>
       </c>
       <c r="E765" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="766" spans="1:5" x14ac:dyDescent="0.25">
@@ -19765,7 +19835,7 @@
         <v>29687</v>
       </c>
       <c r="E767" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="768" spans="1:5" x14ac:dyDescent="0.25">
@@ -19813,7 +19883,7 @@
         <v>28315</v>
       </c>
       <c r="E773" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="774" spans="1:5" x14ac:dyDescent="0.25">
@@ -19829,7 +19899,7 @@
         <v>27328</v>
       </c>
       <c r="E775" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="776" spans="1:5" x14ac:dyDescent="0.25">
@@ -19877,7 +19947,7 @@
         <v>30154</v>
       </c>
       <c r="E781" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="782" spans="1:5" x14ac:dyDescent="0.25">
@@ -19885,7 +19955,7 @@
         <v>29551</v>
       </c>
       <c r="E782" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="783" spans="1:5" x14ac:dyDescent="0.25">
@@ -19893,7 +19963,7 @@
         <v>30012</v>
       </c>
       <c r="E783" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="784" spans="1:5" x14ac:dyDescent="0.25">
@@ -19901,7 +19971,7 @@
         <v>33242</v>
       </c>
       <c r="E784" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="785" spans="1:5" x14ac:dyDescent="0.25">
@@ -19909,7 +19979,7 @@
         <v>4046</v>
       </c>
       <c r="E785" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="786" spans="1:5" x14ac:dyDescent="0.25">
@@ -19917,7 +19987,7 @@
         <v>30226</v>
       </c>
       <c r="E786" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="787" spans="1:5" x14ac:dyDescent="0.25">
@@ -19925,7 +19995,7 @@
         <v>30683</v>
       </c>
       <c r="E787" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="788" spans="1:5" x14ac:dyDescent="0.25">
@@ -19933,7 +20003,7 @@
         <v>29795</v>
       </c>
       <c r="E788" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="789" spans="1:5" x14ac:dyDescent="0.25">
@@ -19957,7 +20027,7 @@
         <v>3057</v>
       </c>
       <c r="E791" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="792" spans="1:5" x14ac:dyDescent="0.25">
@@ -19973,7 +20043,7 @@
         <v>30086</v>
       </c>
       <c r="E793" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="794" spans="1:5" x14ac:dyDescent="0.25">
@@ -19989,7 +20059,7 @@
         <v>31279</v>
       </c>
       <c r="E795" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="796" spans="1:5" x14ac:dyDescent="0.25">
@@ -19997,7 +20067,7 @@
         <v>31306</v>
       </c>
       <c r="E796" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="797" spans="1:5" x14ac:dyDescent="0.25">
@@ -20125,7 +20195,7 @@
         <v>38316</v>
       </c>
       <c r="E812" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="813" spans="1:5" x14ac:dyDescent="0.25">
@@ -20133,7 +20203,7 @@
         <v>17246</v>
       </c>
       <c r="E813" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="814" spans="1:5" x14ac:dyDescent="0.25">
@@ -20165,7 +20235,7 @@
         <v>21797</v>
       </c>
       <c r="E817" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="818" spans="1:5" x14ac:dyDescent="0.25">
@@ -20189,7 +20259,7 @@
         <v>23340</v>
       </c>
       <c r="E820" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="821" spans="1:5" x14ac:dyDescent="0.25">
@@ -20221,7 +20291,7 @@
         <v>25301</v>
       </c>
       <c r="E824" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="825" spans="1:5" x14ac:dyDescent="0.25">
@@ -20232,7 +20302,7 @@
         <v>2</v>
       </c>
       <c r="E825" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="826" spans="1:5" x14ac:dyDescent="0.25">
@@ -20248,7 +20318,7 @@
         <v>24191</v>
       </c>
       <c r="E827" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="828" spans="1:5" x14ac:dyDescent="0.25">
@@ -20264,7 +20334,7 @@
         <v>23888</v>
       </c>
       <c r="E829" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="830" spans="1:5" x14ac:dyDescent="0.25">
@@ -20272,7 +20342,7 @@
         <v>16816</v>
       </c>
       <c r="E830" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="831" spans="1:5" x14ac:dyDescent="0.25">
@@ -20280,7 +20350,7 @@
         <v>27136</v>
       </c>
       <c r="E831" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="832" spans="1:5" x14ac:dyDescent="0.25">
@@ -20288,7 +20358,7 @@
         <v>27872</v>
       </c>
       <c r="E832" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="833" spans="1:5" x14ac:dyDescent="0.25">
@@ -20296,7 +20366,7 @@
         <v>27156</v>
       </c>
       <c r="E833" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="834" spans="1:5" x14ac:dyDescent="0.25">
@@ -20304,7 +20374,7 @@
         <v>27784</v>
       </c>
       <c r="E834" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="835" spans="1:5" x14ac:dyDescent="0.25">
@@ -20312,7 +20382,7 @@
         <v>27224</v>
       </c>
       <c r="E835" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="836" spans="1:5" x14ac:dyDescent="0.25">
@@ -20360,7 +20430,7 @@
         <v>26212</v>
       </c>
       <c r="E841" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="842" spans="1:5" x14ac:dyDescent="0.25">
@@ -20368,7 +20438,7 @@
         <v>28039</v>
       </c>
       <c r="E842" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="843" spans="1:5" x14ac:dyDescent="0.25">
@@ -20376,7 +20446,7 @@
         <v>29732</v>
       </c>
       <c r="E843" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="844" spans="1:5" x14ac:dyDescent="0.25">
@@ -20384,7 +20454,7 @@
         <v>29727</v>
       </c>
       <c r="E844" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="845" spans="1:5" x14ac:dyDescent="0.25">
@@ -20416,7 +20486,7 @@
         <v>13322</v>
       </c>
       <c r="E848" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="849" spans="1:5" x14ac:dyDescent="0.25">
@@ -20432,7 +20502,7 @@
         <v>14822</v>
       </c>
       <c r="E850" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="851" spans="1:5" x14ac:dyDescent="0.25">
@@ -20456,7 +20526,7 @@
         <v>14866</v>
       </c>
       <c r="E853" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="854" spans="1:5" x14ac:dyDescent="0.25">
@@ -20464,7 +20534,7 @@
         <v>29751</v>
       </c>
       <c r="E854" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="855" spans="1:5" x14ac:dyDescent="0.25">
@@ -20480,7 +20550,7 @@
         <v>33244</v>
       </c>
       <c r="E856" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="857" spans="1:5" x14ac:dyDescent="0.25">
@@ -20488,7 +20558,7 @@
         <v>33241</v>
       </c>
       <c r="E857" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="858" spans="1:5" x14ac:dyDescent="0.25">
@@ -20496,7 +20566,7 @@
         <v>33213</v>
       </c>
       <c r="E858" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="859" spans="1:5" x14ac:dyDescent="0.25">
@@ -20520,7 +20590,7 @@
         <v>22421</v>
       </c>
       <c r="E861" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="862" spans="1:5" x14ac:dyDescent="0.25">
@@ -20536,7 +20606,7 @@
         <v>3216</v>
       </c>
       <c r="E863" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="864" spans="1:5" x14ac:dyDescent="0.25">
@@ -20553,6 +20623,54 @@
       </c>
       <c r="E865" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="866" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A866">
+        <v>39396</v>
+      </c>
+      <c r="E866" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="867" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A867">
+        <v>26221</v>
+      </c>
+      <c r="B867">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="868" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A868">
+        <v>23127</v>
+      </c>
+      <c r="B868">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="869" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A869">
+        <v>17490</v>
+      </c>
+      <c r="E869" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="870" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A870">
+        <v>12997</v>
+      </c>
+      <c r="B870">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="871" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A871">
+        <v>26113</v>
+      </c>
+      <c r="B871">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
